--- a/excel-files/atlas-techniques.xlsx
+++ b/excel-files/atlas-techniques.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1341" uniqueCount="806">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="845">
   <si>
     <t>ID</t>
   </si>
@@ -43,6 +43,9 @@
     <t>platforms</t>
   </si>
   <si>
+    <t>AML.T0108</t>
+  </si>
+  <si>
     <t>AML.T0100</t>
   </si>
   <si>
@@ -214,6 +217,9 @@
     <t>AML.T0059</t>
   </si>
   <si>
+    <t>AML.T0105</t>
+  </si>
+  <si>
     <t>AML.T0021</t>
   </si>
   <si>
@@ -232,6 +238,12 @@
     <t>AML.T0049</t>
   </si>
   <si>
+    <t>AML.T0106</t>
+  </si>
+  <si>
+    <t>AML.T0107</t>
+  </si>
+  <si>
     <t>AML.T0048</t>
   </si>
   <si>
@@ -310,6 +322,9 @@
     <t>AML.T0067</t>
   </si>
   <si>
+    <t>AML.T0011.003</t>
+  </si>
+  <si>
     <t>AML.T0011.001</t>
   </si>
   <si>
@@ -361,6 +376,9 @@
     <t>AML.T0020</t>
   </si>
   <si>
+    <t>AML.T0011.002</t>
+  </si>
+  <si>
     <t>AML.T0000.001</t>
   </si>
   <si>
@@ -373,6 +391,9 @@
     <t>AML.T0060</t>
   </si>
   <si>
+    <t>AML.T0104</t>
+  </si>
+  <si>
     <t>AML.T0019</t>
   </si>
   <si>
@@ -487,6 +508,9 @@
     <t>AML.T0043.000</t>
   </si>
   <si>
+    <t>attack-pattern--cf34558d-6970-51aa-a43e-d345b9cf7d38</t>
+  </si>
+  <si>
     <t>attack-pattern--bd74bd28-20ce-5f69-972e-0afe627b7147</t>
   </si>
   <si>
@@ -658,6 +682,9 @@
     <t>attack-pattern--6cc31098-f336-5fd8-932e-0289ff502d16</t>
   </si>
   <si>
+    <t>attack-pattern--8a98b993-8854-5fdd-ae81-4256db9e7a2d</t>
+  </si>
+  <si>
     <t>attack-pattern--d3d7763a-58e1-5e38-84fd-3abea967cb08</t>
   </si>
   <si>
@@ -676,6 +703,12 @@
     <t>attack-pattern--ebeed0c7-c5de-5049-8f27-efcae5f88b00</t>
   </si>
   <si>
+    <t>attack-pattern--61bd1eb1-b526-59aa-9b1c-86a7dc5fa0d8</t>
+  </si>
+  <si>
+    <t>attack-pattern--1f612544-c939-5d60-ad34-2d0644622e1f</t>
+  </si>
+  <si>
     <t>attack-pattern--2093defe-1976-5bca-9c88-f63072c90073</t>
   </si>
   <si>
@@ -754,6 +787,9 @@
     <t>attack-pattern--ab0f8614-31f1-5014-a3e5-4520341c4933</t>
   </si>
   <si>
+    <t>attack-pattern--386bf4df-e7c7-54da-a297-fec4ffd5e1a8</t>
+  </si>
+  <si>
     <t>attack-pattern--08fd47ac-8b5f-5c0b-8b1d-8e915351cdc2</t>
   </si>
   <si>
@@ -805,6 +841,9 @@
     <t>attack-pattern--4f25f684-63f5-5dfa-a286-20dfbd6db4c1</t>
   </si>
   <si>
+    <t>attack-pattern--5010d920-1568-56ee-ae3e-18fcf145fa40</t>
+  </si>
+  <si>
     <t>attack-pattern--02ea7626-0eec-5a4b-98ff-b3f21733b783</t>
   </si>
   <si>
@@ -817,6 +856,9 @@
     <t>attack-pattern--7ef953bd-97c4-5fac-af50-8619601046e2</t>
   </si>
   <si>
+    <t>attack-pattern--04842d98-bb69-586e-9765-6ff1f56ef722</t>
+  </si>
+  <si>
     <t>attack-pattern--c38896b2-974c-5ed5-adeb-c2477b311353</t>
   </si>
   <si>
@@ -931,6 +973,9 @@
     <t>attack-pattern--5f8f898d-1e29-52a7-bf95-2d420313aee8</t>
   </si>
   <si>
+    <t>AI Agent</t>
+  </si>
+  <si>
     <t>AI Agent Clickbait</t>
   </si>
   <si>
@@ -1102,6 +1147,9 @@
     <t>Erode Dataset Integrity</t>
   </si>
   <si>
+    <t>Escape to Host</t>
+  </si>
+  <si>
     <t>Establish Accounts</t>
   </si>
   <si>
@@ -1120,6 +1168,12 @@
     <t>Exploit Public-Facing Application</t>
   </si>
   <si>
+    <t>Exploitation for Credential Access</t>
+  </si>
+  <si>
+    <t>Exploitation for Defense Evasion</t>
+  </si>
+  <si>
     <t>External Harms</t>
   </si>
   <si>
@@ -1198,6 +1252,9 @@
     <t>LLM Trusted Output Components Manipulation</t>
   </si>
   <si>
+    <t>Malicious Link</t>
+  </si>
+  <si>
     <t>Malicious Package</t>
   </si>
   <si>
@@ -1249,6 +1306,9 @@
     <t>Poison Training Data</t>
   </si>
   <si>
+    <t>Poisoned AI Agent Tool</t>
+  </si>
+  <si>
     <t>Pre-Print Repositories</t>
   </si>
   <si>
@@ -1261,6 +1321,9 @@
     <t>Publish Hallucinated Entities</t>
   </si>
   <si>
+    <t>Publish Poisoned AI Agent Tool</t>
+  </si>
+  <si>
     <t>Publish Poisoned Datasets</t>
   </si>
   <si>
@@ -1373,6 +1436,10 @@
   </si>
   <si>
     <t>White-Box Optimization</t>
+  </si>
+  <si>
+    <t>Adversaries may abuse AI agents present on the victim's system for command and control. AI agents are often granted access to tools that can execute shell commands, reach out to the internet, and interact with other services in the victim's environment, making them capable C2 agents.
+The adversary may modify the behavior of an AI agent for C2 via [LLM Prompt Injection](/techniques/AML.T0051) and rely on the agent's ability to invoke tools to retrieve and execute the adversary's commands. They may maintain persistent control of an agent via [Modify AI Agent Configuration](/techniques/AML.T0081) or [AI Agent Context Poisoning](/techniques/AML.T0080). They may instruct the agent to not report their actions to the user in an attempt to remain covert.</t>
   </si>
   <si>
     <t>Adversaries may craft deceptive web content designed to bait Computer-Using AI agents or AI web browsers into taking unintended actions, such as clicking buttons, copying code, or navigating to specific web pages. These attacks exploit the agent's interpretation of UI content, visual cues, or prompt-like language embedded in the site. When successful, they can lead the agent to inadvertently copy and execute malicious code on the user's operating system.</t>
@@ -1671,6 +1738,10 @@
     <t>Adversaries may poison or manipulate portions of a dataset to reduce its usefulness, reduce trust, and cause users to waste resources correcting errors.</t>
   </si>
   <si>
+    <t>Adversaries may break out of a container or virtualized environment to gain access to the underlying host. This can allow an adversary access to other containerized or virtualized resources from the host level or to the host itself. In principle, containerized / virtualized resources should provide a clear separation of application functionality and be isolated from the host environment.
+There are many ways an adversary may escape from a container or sandbox environment via AI Systems. For example, modifying an AI Agent's configuration to disable safety features or user confirmations could allow the adversary to invoke tools to be run on host environments rather than in the sandbox.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adversaries may create accounts with various services for use in targeting, to gain access to resources needed in [AI Attack Staging](/tactics/AML.TA0001), or for victim impersonation.
 </t>
   </si>
@@ -1695,6 +1766,12 @@
   <si>
     <t xml:space="preserve">Adversaries may attempt to take advantage of a weakness in an Internet-facing computer or program using software, data, or commands in order to cause unintended or unanticipated behavior. The weakness in the system can be a bug, a glitch, or a design vulnerability. These applications are often websites, but can include databases (like SQL), standard services (like SMB or SSH), network device administration and management protocols (like SNMP and Smart Install), and any other applications with Internet accessible open sockets, such as web servers and related services.
 </t>
+  </si>
+  <si>
+    <t>Adversaries may exploit software vulnerabilities in an attempt to collect credentials. Exploitation of a software vulnerability occurs when an adversary takes advantage of a programming error in a program, service, or within the operating system software or kernel itself to execute adversary-controlled code.</t>
+  </si>
+  <si>
+    <t>Adversaries may exploit a system or application vulnerability to bypass security features. Exploitation of a vulnerability occurs when an adversary takes advantage of a programming error in a program, service, or within the operating system software or kernel itself to execute adversary-controlled code. Vulnerabilities may exist in defensive security software that can be used to disable or circumvent them.</t>
   </si>
   <si>
     <t xml:space="preserve">Adversaries may abuse their access to a victim system and use its resources or capabilities to further their goals by causing harms external to that system.
@@ -1842,6 +1919,10 @@
 The LLM may be instructed to tailor its language to appear more trustworthy to the user or attempt to manipulate the user to take certain actions. Other response components that could be manipulated include links, recommended follow-up actions, retrieved document metadata, and [Citations](/techniques/AML.T0067.000).</t>
   </si>
   <si>
+    <t>An adversary may rely upon a user clicking a malicious link in order to gain execution. Users may be subjected to social engineering to get them to click on a link that will lead to code execution. This user action will typically be observed as follow-on behavior from Spearphishing Link. Clicking on a link may also lead to other execution techniques such as exploitation of a browser or application vulnerability via Exploitation for Client Execution. Links may also lead users to download files that require execution via Malicious File.
+There are many ways an adversary can leverage malicious links to gain access to a victim system via an AI system. For example, an AI Agent that is configured to not validate website origin headers will accept connections from any website, allowing adversaries the ability to get around previously inaccessible network.</t>
+  </si>
+  <si>
     <t>Adversaries may develop malicious software packages that when imported by a user have a deleterious effect.
 Malicious packages may behave as expected to the user. They may be introduced via [AI Supply Chain Compromise](/techniques/AML.T0010). They may not present as obviously malicious to the user and may appear to be useful for an AI-related task.</t>
   </si>
@@ -1883,7 +1964,8 @@
   </si>
   <si>
     <t>Adversaries may modify the configuration files for AI agents on a system. This allows malicious changes to persist beyond the life of a single agent and affects any agents that share the configuration.
-Configuration changes may include modifications to the system prompt, tampering with or replacing knowledge sources, modification to settings of connected tools, and more. Through those changes, an attacker could redirect outputs or tools to malicious services, embed covert instructions that exfiltrate data, or weaken security controls that normally restrict agent behavior.</t>
+Configuration changes may include modifications to the system prompt, tampering with or replacing knowledge sources, modification to settings of connected tools, and more. Through those changes, an attacker could redirect outputs or tools to malicious services, embed covert instructions that exfiltrate data, or weaken security controls that normally restrict agent behavior.
+Adversaries may modify or disable a configuration setting related to security controls, such as those that would prevent the AI Agent from taking actions that may be harmful to the user's system without human-in-the-loop oversight. Disabling AI agent security features may allow adversaries to achieve their malicious goals and maintain long-term corruption of the AI agent.</t>
   </si>
   <si>
     <t>Adversaries may directly modify an AI model's architecture to re-define it's behavior. This can include adding or removing layers as well as adding pre or post-processing operations.
@@ -1925,6 +2007,10 @@
 Poisoned data can be introduced via [AI Supply Chain Compromise](/techniques/AML.T0010) or the data may be poisoned after the adversary gains [Initial Access](/tactics/AML.TA0004) to the system.</t>
   </si>
   <si>
+    <t>A victim may invoke a poisoned tool when interacting with their AI agent. A poisoned tool may execute an [LLM Prompt Injection](/techniques/AML.T0051) or perform [AI Agent Tool Invocation](/techniques/AML.T0053).
+Poisoned AI agent tools may be introduced into the victim's environment via [AI Software](/techniques/AML.T0010.001), or the user may configure their agent to connect to remote tools.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pre-Print repositories, such as arXiv, contain the latest academic research papers that haven't been peer reviewed.
 They may contain research notes, or technical reports that aren't typically published in journals or conference proceedings.
 Pre-print repositories also serve as a central location to share papers that have been accepted to journals.
@@ -1943,6 +2029,11 @@
   </si>
   <si>
     <t>Adversaries may create an entity they control, such as a software package, website, or email address to a source hallucinated by an LLM. The hallucinations may take the form of package names commands, URLs, company names, or email addresses that point the victim to the entity controlled by the adversary. When the victim interacts with the adversary-controlled entity, the attack can proceed.</t>
+  </si>
+  <si>
+    <t>Adversaries may create and publish poisoned AI agent tools. Poisoned tools may contain an [LLM Prompt Injection](/techniques/AML.T0051), which can lead to a variety of impacts.
+Tools may be published to open source version control repositories (e.g. GitHub, GitLab), to package registries (e.g. npm), or to repositories specifically designed for sharing tools (e.g. OpenClaw Hub). These registries may be largely unregulated and may contain many poisoned tools [\[1\]][1].
+[1]: https://opensourcemalware.com/blog/clawdbot-skills-ganked-your-crypto</t>
   </si>
   <si>
     <t xml:space="preserve">Adversaries may [Poison Training Data](/techniques/AML.T0020) and publish it to a public location.
@@ -2134,6 +2225,9 @@
 </t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0108</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0100</t>
   </si>
   <si>
@@ -2305,6 +2399,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0059</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0105</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0021</t>
   </si>
   <si>
@@ -2323,6 +2420,12 @@
     <t>https://atlas.mitre.org/techniques/AML.T0049</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0106</t>
+  </si>
+  <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0107</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0048</t>
   </si>
   <si>
@@ -2401,6 +2504,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0067</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0011.003</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0011.001</t>
   </si>
   <si>
@@ -2452,6 +2558,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0020</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0011.002</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0000.001</t>
   </si>
   <si>
@@ -2464,6 +2573,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0060</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0104</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0019</t>
   </si>
   <si>
@@ -2578,6 +2690,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0043.000</t>
   </si>
   <si>
+    <t>30 January 2026</t>
+  </si>
+  <si>
     <t>25 November 2025</t>
   </si>
   <si>
@@ -2641,6 +2756,9 @@
     <t>05 November 2025</t>
   </si>
   <si>
+    <t>05 February 2026</t>
+  </si>
+  <si>
     <t>13 October 2025</t>
   </si>
   <si>
@@ -2677,6 +2795,9 @@
     <t>29 April 2024</t>
   </si>
   <si>
+    <t>Command and Control</t>
+  </si>
+  <si>
     <t>Execution</t>
   </si>
   <si>
@@ -2701,9 +2822,6 @@
     <t>AI Model Access</t>
   </si>
   <si>
-    <t>Command and Control</t>
-  </si>
-  <si>
     <t>Initial Access</t>
   </si>
   <si>
@@ -2719,6 +2837,9 @@
     <t>AI Attack Staging</t>
   </si>
   <si>
+    <t>Privilege Escalation</t>
+  </si>
+  <si>
     <t>Defense Evasion, Impact, Initial Access</t>
   </si>
   <si>
@@ -2729,6 +2850,9 @@
   </si>
   <si>
     <t>AI Attack Staging, Persistence</t>
+  </si>
+  <si>
+    <t>Defense Evasion, Persistence</t>
   </si>
   <si>
     <t>Initial Access, Lateral Movement</t>
@@ -2753,16 +2877,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2785,7 +2901,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2793,35 +2909,17 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3117,35 +3215,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I149"/>
+  <dimension ref="A1:I156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3154,28 +3252,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C2" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="D2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>601</v>
+        <v>474</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>629</v>
       </c>
       <c r="F2" t="s">
-        <v>749</v>
+        <v>784</v>
       </c>
       <c r="G2" t="s">
-        <v>749</v>
+        <v>806</v>
       </c>
       <c r="H2" t="s">
-        <v>782</v>
+        <v>819</v>
       </c>
       <c r="I2" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3183,28 +3281,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C3" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="D3" t="s">
-        <v>454</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>602</v>
+        <v>475</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>630</v>
       </c>
       <c r="F3" t="s">
-        <v>750</v>
+        <v>785</v>
       </c>
       <c r="G3" t="s">
-        <v>770</v>
+        <v>785</v>
       </c>
       <c r="H3" t="s">
-        <v>783</v>
+        <v>820</v>
       </c>
       <c r="I3" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3212,28 +3310,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C4" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="D4" t="s">
-        <v>455</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>603</v>
+        <v>476</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>631</v>
       </c>
       <c r="F4" t="s">
-        <v>749</v>
+        <v>786</v>
       </c>
       <c r="G4" t="s">
-        <v>771</v>
+        <v>807</v>
       </c>
       <c r="H4" t="s">
-        <v>784</v>
+        <v>821</v>
       </c>
       <c r="I4" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3241,28 +3339,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C5" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="D5" t="s">
-        <v>456</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>604</v>
+        <v>477</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>632</v>
       </c>
       <c r="F5" t="s">
-        <v>749</v>
+        <v>785</v>
       </c>
       <c r="G5" t="s">
-        <v>749</v>
+        <v>808</v>
       </c>
       <c r="H5" t="s">
-        <v>783</v>
+        <v>822</v>
       </c>
       <c r="I5" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3270,28 +3368,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="D6" t="s">
-        <v>457</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>605</v>
+        <v>478</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>633</v>
       </c>
       <c r="F6" t="s">
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="G6" t="s">
-        <v>760</v>
+        <v>785</v>
       </c>
       <c r="H6" t="s">
-        <v>785</v>
+        <v>821</v>
       </c>
       <c r="I6" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3299,28 +3397,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="D7" t="s">
-        <v>458</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>606</v>
+        <v>479</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>634</v>
       </c>
       <c r="F7" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="G7" t="s">
-        <v>750</v>
+        <v>796</v>
       </c>
       <c r="H7" t="s">
-        <v>786</v>
+        <v>823</v>
       </c>
       <c r="I7" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3328,28 +3426,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C8" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="D8" t="s">
-        <v>459</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>607</v>
+        <v>480</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>635</v>
       </c>
       <c r="F8" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G8" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="H8" t="s">
-        <v>786</v>
+        <v>824</v>
       </c>
       <c r="I8" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3357,28 +3455,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C9" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="D9" t="s">
-        <v>460</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>608</v>
+        <v>481</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>636</v>
       </c>
       <c r="F9" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G9" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H9" t="s">
-        <v>787</v>
+        <v>824</v>
       </c>
       <c r="I9" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3386,28 +3484,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C10" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D10" t="s">
-        <v>461</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>609</v>
+        <v>482</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>637</v>
       </c>
       <c r="F10" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G10" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H10" t="s">
-        <v>788</v>
+        <v>825</v>
       </c>
       <c r="I10" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3415,28 +3513,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C11" t="s">
-        <v>314</v>
+        <v>328</v>
       </c>
       <c r="D11" t="s">
-        <v>462</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>610</v>
+        <v>483</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>638</v>
       </c>
       <c r="F11" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G11" t="s">
-        <v>755</v>
+        <v>799</v>
       </c>
       <c r="H11" t="s">
-        <v>789</v>
+        <v>826</v>
       </c>
       <c r="I11" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3444,28 +3542,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C12" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="D12" t="s">
-        <v>463</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>611</v>
+        <v>484</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>639</v>
       </c>
       <c r="F12" t="s">
-        <v>753</v>
+        <v>788</v>
       </c>
       <c r="G12" t="s">
-        <v>772</v>
+        <v>791</v>
       </c>
       <c r="H12" t="s">
-        <v>790</v>
+        <v>827</v>
       </c>
       <c r="I12" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3473,28 +3571,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C13" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="D13" t="s">
-        <v>464</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>612</v>
+        <v>485</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>640</v>
       </c>
       <c r="F13" t="s">
-        <v>752</v>
+        <v>789</v>
       </c>
       <c r="G13" t="s">
-        <v>773</v>
+        <v>809</v>
       </c>
       <c r="H13" t="s">
-        <v>791</v>
+        <v>819</v>
       </c>
       <c r="I13" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3502,28 +3600,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C14" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="D14" t="s">
-        <v>465</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>613</v>
+        <v>486</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>641</v>
       </c>
       <c r="F14" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G14" t="s">
-        <v>763</v>
+        <v>810</v>
       </c>
       <c r="H14" t="s">
-        <v>791</v>
+        <v>828</v>
       </c>
       <c r="I14" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3531,28 +3629,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C15" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="D15" t="s">
-        <v>466</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>614</v>
+        <v>487</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>642</v>
       </c>
       <c r="F15" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G15" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H15" t="s">
-        <v>789</v>
+        <v>828</v>
       </c>
       <c r="I15" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -3560,28 +3658,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C16" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="D16" t="s">
-        <v>467</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>615</v>
+        <v>488</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>643</v>
       </c>
       <c r="F16" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G16" t="s">
-        <v>755</v>
+        <v>799</v>
       </c>
       <c r="H16" t="s">
-        <v>787</v>
+        <v>827</v>
       </c>
       <c r="I16" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -3589,28 +3687,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C17" t="s">
-        <v>320</v>
+        <v>334</v>
       </c>
       <c r="D17" t="s">
-        <v>468</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>616</v>
+        <v>489</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>644</v>
       </c>
       <c r="F17" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G17" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
       <c r="H17" t="s">
-        <v>787</v>
+        <v>825</v>
       </c>
       <c r="I17" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -3618,28 +3716,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C18" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="D18" t="s">
-        <v>469</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>617</v>
+        <v>490</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>645</v>
       </c>
       <c r="F18" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="G18" t="s">
-        <v>750</v>
+        <v>799</v>
       </c>
       <c r="H18" t="s">
-        <v>792</v>
+        <v>825</v>
       </c>
       <c r="I18" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -3647,28 +3745,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C19" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="D19" t="s">
-        <v>470</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>618</v>
+        <v>491</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>646</v>
       </c>
       <c r="F19" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G19" t="s">
-        <v>760</v>
+        <v>786</v>
       </c>
       <c r="H19" t="s">
-        <v>793</v>
+        <v>829</v>
       </c>
       <c r="I19" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -3676,28 +3774,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C20" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="D20" t="s">
-        <v>471</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>619</v>
+        <v>492</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>647</v>
       </c>
       <c r="F20" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G20" t="s">
-        <v>763</v>
+        <v>796</v>
       </c>
       <c r="H20" t="s">
-        <v>787</v>
+        <v>830</v>
       </c>
       <c r="I20" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -3705,28 +3803,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C21" t="s">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="D21" t="s">
-        <v>472</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>620</v>
+        <v>493</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>648</v>
       </c>
       <c r="F21" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G21" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H21" t="s">
-        <v>787</v>
+        <v>825</v>
       </c>
       <c r="I21" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -3734,28 +3832,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C22" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="D22" t="s">
-        <v>473</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>621</v>
+        <v>494</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>649</v>
       </c>
       <c r="F22" t="s">
-        <v>754</v>
+        <v>787</v>
       </c>
       <c r="G22" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="H22" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
       <c r="I22" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -3763,28 +3861,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C23" t="s">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="D23" t="s">
-        <v>474</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>622</v>
+        <v>495</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>650</v>
       </c>
       <c r="F23" t="s">
-        <v>752</v>
+        <v>790</v>
       </c>
       <c r="G23" t="s">
-        <v>752</v>
+        <v>809</v>
       </c>
       <c r="H23" t="s">
-        <v>795</v>
+        <v>831</v>
       </c>
       <c r="I23" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -3792,28 +3890,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C24" t="s">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="D24" t="s">
-        <v>475</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>623</v>
+        <v>496</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>651</v>
       </c>
       <c r="F24" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G24" t="s">
-        <v>774</v>
+        <v>788</v>
       </c>
       <c r="H24" t="s">
-        <v>795</v>
+        <v>832</v>
       </c>
       <c r="I24" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3821,28 +3919,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C25" t="s">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="D25" t="s">
-        <v>476</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>624</v>
+        <v>497</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>652</v>
       </c>
       <c r="F25" t="s">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="G25" t="s">
-        <v>755</v>
+        <v>811</v>
       </c>
       <c r="H25" t="s">
-        <v>794</v>
+        <v>832</v>
       </c>
       <c r="I25" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3850,28 +3948,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C26" t="s">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="D26" t="s">
-        <v>477</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>625</v>
+        <v>498</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>653</v>
       </c>
       <c r="F26" t="s">
-        <v>756</v>
+        <v>791</v>
       </c>
       <c r="G26" t="s">
-        <v>753</v>
+        <v>791</v>
       </c>
       <c r="H26" t="s">
-        <v>792</v>
+        <v>831</v>
       </c>
       <c r="I26" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3879,28 +3977,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C27" t="s">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="D27" t="s">
-        <v>478</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>626</v>
+        <v>499</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>654</v>
       </c>
       <c r="F27" t="s">
-        <v>757</v>
+        <v>792</v>
       </c>
       <c r="G27" t="s">
-        <v>775</v>
+        <v>789</v>
       </c>
       <c r="H27" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="I27" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -3908,28 +4006,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C28" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="D28" t="s">
-        <v>479</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>627</v>
+        <v>500</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>655</v>
       </c>
       <c r="F28" t="s">
-        <v>752</v>
+        <v>793</v>
       </c>
       <c r="G28" t="s">
-        <v>752</v>
+        <v>812</v>
       </c>
       <c r="H28" t="s">
-        <v>787</v>
+        <v>820</v>
       </c>
       <c r="I28" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3937,28 +4035,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C29" t="s">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="D29" t="s">
-        <v>480</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>628</v>
+        <v>501</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>656</v>
       </c>
       <c r="F29" t="s">
-        <v>758</v>
+        <v>788</v>
       </c>
       <c r="G29" t="s">
-        <v>758</v>
+        <v>788</v>
       </c>
       <c r="H29" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
       <c r="I29" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -3966,28 +4064,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C30" t="s">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="D30" t="s">
-        <v>481</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>629</v>
+        <v>502</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>657</v>
       </c>
       <c r="F30" t="s">
-        <v>756</v>
+        <v>794</v>
       </c>
       <c r="G30" t="s">
-        <v>756</v>
+        <v>794</v>
       </c>
       <c r="H30" t="s">
-        <v>794</v>
+        <v>831</v>
       </c>
       <c r="I30" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -3995,28 +4093,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C31" t="s">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="D31" t="s">
-        <v>482</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>630</v>
+        <v>503</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>658</v>
       </c>
       <c r="F31" t="s">
-        <v>752</v>
+        <v>792</v>
       </c>
       <c r="G31" t="s">
-        <v>763</v>
+        <v>792</v>
       </c>
       <c r="H31" t="s">
-        <v>788</v>
+        <v>831</v>
       </c>
       <c r="I31" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -4024,28 +4122,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="C32" t="s">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="D32" t="s">
-        <v>483</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>631</v>
+        <v>504</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>659</v>
       </c>
       <c r="F32" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G32" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H32" t="s">
-        <v>795</v>
+        <v>826</v>
       </c>
       <c r="I32" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -4053,28 +4151,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C33" t="s">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="D33" t="s">
-        <v>484</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>632</v>
+        <v>505</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>660</v>
       </c>
       <c r="F33" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G33" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H33" t="s">
-        <v>795</v>
+        <v>832</v>
       </c>
       <c r="I33" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -4082,28 +4180,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C34" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D34" t="s">
-        <v>485</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>633</v>
+        <v>506</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>661</v>
       </c>
       <c r="F34" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="G34" t="s">
-        <v>770</v>
+        <v>799</v>
       </c>
       <c r="H34" t="s">
-        <v>784</v>
+        <v>832</v>
       </c>
       <c r="I34" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -4111,28 +4209,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="C35" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="D35" t="s">
-        <v>486</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>634</v>
+        <v>507</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>662</v>
       </c>
       <c r="F35" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G35" t="s">
-        <v>763</v>
+        <v>807</v>
       </c>
       <c r="H35" t="s">
-        <v>791</v>
+        <v>822</v>
       </c>
       <c r="I35" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -4140,28 +4238,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C36" t="s">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="D36" t="s">
-        <v>487</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>635</v>
+        <v>508</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>663</v>
       </c>
       <c r="F36" t="s">
-        <v>749</v>
+        <v>788</v>
       </c>
       <c r="G36" t="s">
-        <v>749</v>
+        <v>799</v>
       </c>
       <c r="H36" t="s">
-        <v>788</v>
+        <v>828</v>
       </c>
       <c r="I36" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -4169,28 +4267,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="C37" t="s">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="D37" t="s">
-        <v>488</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>636</v>
+        <v>509</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>664</v>
       </c>
       <c r="F37" t="s">
-        <v>750</v>
+        <v>785</v>
       </c>
       <c r="G37" t="s">
-        <v>760</v>
+        <v>785</v>
       </c>
       <c r="H37" t="s">
-        <v>786</v>
+        <v>826</v>
       </c>
       <c r="I37" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -4198,28 +4296,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="C38" t="s">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="D38" t="s">
-        <v>489</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>637</v>
+        <v>510</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>665</v>
       </c>
       <c r="F38" t="s">
-        <v>759</v>
+        <v>786</v>
       </c>
       <c r="G38" t="s">
-        <v>776</v>
+        <v>796</v>
       </c>
       <c r="H38" t="s">
-        <v>786</v>
+        <v>824</v>
       </c>
       <c r="I38" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -4227,28 +4325,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C39" t="s">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="D39" t="s">
-        <v>490</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>638</v>
+        <v>511</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>666</v>
       </c>
       <c r="F39" t="s">
-        <v>752</v>
+        <v>795</v>
       </c>
       <c r="G39" t="s">
-        <v>776</v>
+        <v>813</v>
       </c>
       <c r="H39" t="s">
-        <v>786</v>
+        <v>824</v>
       </c>
       <c r="I39" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -4256,28 +4354,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="C40" t="s">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="D40" t="s">
-        <v>491</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>639</v>
+        <v>512</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>667</v>
       </c>
       <c r="F40" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G40" t="s">
-        <v>752</v>
+        <v>813</v>
       </c>
       <c r="H40" t="s">
-        <v>787</v>
+        <v>824</v>
       </c>
       <c r="I40" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -4285,28 +4383,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C41" t="s">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="D41" t="s">
-        <v>492</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>640</v>
+        <v>513</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>668</v>
       </c>
       <c r="F41" t="s">
-        <v>760</v>
+        <v>788</v>
       </c>
       <c r="G41" t="s">
-        <v>769</v>
+        <v>788</v>
       </c>
       <c r="H41" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
       <c r="I41" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -4314,28 +4412,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C42" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="D42" t="s">
-        <v>493</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>641</v>
+        <v>514</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>669</v>
       </c>
       <c r="F42" t="s">
-        <v>752</v>
+        <v>796</v>
       </c>
       <c r="G42" t="s">
-        <v>763</v>
+        <v>805</v>
       </c>
       <c r="H42" t="s">
-        <v>788</v>
+        <v>831</v>
       </c>
       <c r="I42" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -4343,28 +4441,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C43" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="D43" t="s">
-        <v>494</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>642</v>
+        <v>515</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>670</v>
       </c>
       <c r="F43" t="s">
-        <v>761</v>
+        <v>788</v>
       </c>
       <c r="G43" t="s">
-        <v>761</v>
+        <v>799</v>
       </c>
       <c r="H43" t="s">
-        <v>782</v>
+        <v>826</v>
       </c>
       <c r="I43" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -4372,28 +4470,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="C44" t="s">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="D44" t="s">
-        <v>495</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>643</v>
+        <v>516</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>671</v>
       </c>
       <c r="F44" t="s">
-        <v>751</v>
+        <v>797</v>
       </c>
       <c r="G44" t="s">
-        <v>763</v>
+        <v>797</v>
       </c>
       <c r="H44" t="s">
-        <v>787</v>
+        <v>820</v>
       </c>
       <c r="I44" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -4401,28 +4499,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="C45" t="s">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="D45" t="s">
-        <v>496</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>644</v>
+        <v>517</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>672</v>
       </c>
       <c r="F45" t="s">
-        <v>751</v>
+        <v>787</v>
       </c>
       <c r="G45" t="s">
-        <v>751</v>
+        <v>799</v>
       </c>
       <c r="H45" t="s">
-        <v>782</v>
+        <v>825</v>
       </c>
       <c r="I45" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -4430,28 +4528,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="C46" t="s">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="D46" t="s">
-        <v>497</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>645</v>
+        <v>518</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>673</v>
       </c>
       <c r="F46" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="G46" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="H46" t="s">
-        <v>792</v>
+        <v>820</v>
       </c>
       <c r="I46" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -4459,28 +4557,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C47" t="s">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="D47" t="s">
-        <v>498</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>646</v>
+        <v>519</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>674</v>
       </c>
       <c r="F47" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G47" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="H47" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I47" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -4488,28 +4586,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="C48" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="D48" t="s">
-        <v>499</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>647</v>
+        <v>520</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>675</v>
       </c>
       <c r="F48" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G48" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H48" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I48" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -4517,28 +4615,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C49" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="D49" t="s">
-        <v>500</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>648</v>
+        <v>521</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>676</v>
       </c>
       <c r="F49" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G49" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H49" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I49" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -4546,28 +4644,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C50" t="s">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D50" t="s">
-        <v>501</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>649</v>
+        <v>522</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>677</v>
       </c>
       <c r="F50" t="s">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="G50" t="s">
-        <v>755</v>
+        <v>799</v>
       </c>
       <c r="H50" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I50" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -4575,28 +4673,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="C51" t="s">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="D51" t="s">
-        <v>502</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>650</v>
+        <v>523</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>678</v>
       </c>
       <c r="F51" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G51" t="s">
-        <v>765</v>
+        <v>791</v>
       </c>
       <c r="H51" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I51" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -4604,28 +4702,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="C52" t="s">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="D52" t="s">
-        <v>503</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>651</v>
+        <v>524</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>679</v>
       </c>
       <c r="F52" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G52" t="s">
-        <v>755</v>
+        <v>801</v>
       </c>
       <c r="H52" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I52" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -4633,28 +4731,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="C53" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="D53" t="s">
-        <v>504</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>652</v>
+        <v>525</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>680</v>
       </c>
       <c r="F53" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G53" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="H53" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I53" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -4662,28 +4760,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C54" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="D54" t="s">
-        <v>505</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>653</v>
+        <v>526</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>681</v>
       </c>
       <c r="F54" t="s">
-        <v>762</v>
+        <v>791</v>
       </c>
       <c r="G54" t="s">
-        <v>777</v>
+        <v>791</v>
       </c>
       <c r="H54" t="s">
-        <v>791</v>
+        <v>829</v>
       </c>
       <c r="I54" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -4691,28 +4789,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C55" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="D55" t="s">
-        <v>506</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>654</v>
+        <v>527</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>682</v>
       </c>
       <c r="F55" t="s">
-        <v>763</v>
+        <v>798</v>
       </c>
       <c r="G55" t="s">
-        <v>763</v>
+        <v>814</v>
       </c>
       <c r="H55" t="s">
-        <v>794</v>
+        <v>828</v>
       </c>
       <c r="I55" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -4720,28 +4818,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="C56" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="D56" t="s">
-        <v>507</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>655</v>
+        <v>528</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>683</v>
       </c>
       <c r="F56" t="s">
-        <v>750</v>
+        <v>799</v>
       </c>
       <c r="G56" t="s">
-        <v>750</v>
+        <v>799</v>
       </c>
       <c r="H56" t="s">
-        <v>792</v>
+        <v>831</v>
       </c>
       <c r="I56" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -4749,28 +4847,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C57" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="D57" t="s">
-        <v>508</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>656</v>
+        <v>529</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>684</v>
       </c>
       <c r="F57" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G57" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="H57" t="s">
-        <v>788</v>
+        <v>829</v>
       </c>
       <c r="I57" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -4778,28 +4876,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C58" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="D58" t="s">
-        <v>509</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>657</v>
+        <v>530</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>685</v>
       </c>
       <c r="F58" t="s">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="G58" t="s">
-        <v>755</v>
+        <v>799</v>
       </c>
       <c r="H58" t="s">
-        <v>788</v>
+        <v>826</v>
       </c>
       <c r="I58" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -4807,28 +4905,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C59" t="s">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="D59" t="s">
-        <v>510</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>658</v>
+        <v>531</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>686</v>
       </c>
       <c r="F59" t="s">
-        <v>759</v>
+        <v>791</v>
       </c>
       <c r="G59" t="s">
-        <v>776</v>
+        <v>791</v>
       </c>
       <c r="H59" t="s">
-        <v>787</v>
+        <v>826</v>
       </c>
       <c r="I59" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -4836,28 +4934,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C60" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="D60" t="s">
-        <v>511</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>659</v>
+        <v>532</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>687</v>
       </c>
       <c r="F60" t="s">
-        <v>752</v>
+        <v>784</v>
       </c>
       <c r="G60" t="s">
-        <v>760</v>
+        <v>784</v>
       </c>
       <c r="H60" t="s">
-        <v>796</v>
+        <v>833</v>
       </c>
       <c r="I60" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -4865,28 +4963,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="C61" t="s">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="D61" t="s">
-        <v>512</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>660</v>
+        <v>533</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>688</v>
       </c>
       <c r="F61" t="s">
-        <v>750</v>
+        <v>795</v>
       </c>
       <c r="G61" t="s">
-        <v>750</v>
+        <v>813</v>
       </c>
       <c r="H61" t="s">
-        <v>797</v>
+        <v>825</v>
       </c>
       <c r="I61" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -4894,28 +4992,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C62" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="D62" t="s">
-        <v>513</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>661</v>
+        <v>534</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>689</v>
       </c>
       <c r="F62" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G62" t="s">
-        <v>763</v>
+        <v>796</v>
       </c>
       <c r="H62" t="s">
-        <v>797</v>
+        <v>834</v>
       </c>
       <c r="I62" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -4923,28 +5021,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C63" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="D63" t="s">
-        <v>514</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>662</v>
+        <v>535</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>690</v>
       </c>
       <c r="F63" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G63" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="H63" t="s">
-        <v>797</v>
+        <v>835</v>
       </c>
       <c r="I63" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -4952,28 +5050,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C64" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="D64" t="s">
-        <v>515</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>663</v>
+        <v>536</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>691</v>
       </c>
       <c r="F64" t="s">
-        <v>757</v>
+        <v>788</v>
       </c>
       <c r="G64" t="s">
-        <v>757</v>
+        <v>799</v>
       </c>
       <c r="H64" t="s">
-        <v>791</v>
+        <v>835</v>
       </c>
       <c r="I64" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -4981,28 +5079,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="C65" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="D65" t="s">
-        <v>516</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>664</v>
+        <v>537</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>692</v>
       </c>
       <c r="F65" t="s">
-        <v>764</v>
+        <v>788</v>
       </c>
       <c r="G65" t="s">
-        <v>751</v>
+        <v>799</v>
       </c>
       <c r="H65" t="s">
-        <v>788</v>
+        <v>835</v>
       </c>
       <c r="I65" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -5010,28 +5108,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C66" t="s">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="D66" t="s">
-        <v>517</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>665</v>
+        <v>538</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>693</v>
       </c>
       <c r="F66" t="s">
-        <v>752</v>
+        <v>793</v>
       </c>
       <c r="G66" t="s">
-        <v>772</v>
+        <v>793</v>
       </c>
       <c r="H66" t="s">
-        <v>797</v>
+        <v>828</v>
       </c>
       <c r="I66" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -5039,28 +5137,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C67" t="s">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="D67" t="s">
-        <v>518</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>666</v>
+        <v>539</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>694</v>
       </c>
       <c r="F67" t="s">
-        <v>751</v>
+        <v>784</v>
       </c>
       <c r="G67" t="s">
-        <v>755</v>
+        <v>806</v>
       </c>
       <c r="H67" t="s">
-        <v>797</v>
+        <v>822</v>
       </c>
       <c r="I67" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -5068,28 +5166,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="C68" t="s">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="D68" t="s">
-        <v>519</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>667</v>
+        <v>540</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>695</v>
       </c>
       <c r="F68" t="s">
-        <v>755</v>
+        <v>784</v>
       </c>
       <c r="G68" t="s">
-        <v>753</v>
+        <v>806</v>
       </c>
       <c r="H68" t="s">
-        <v>794</v>
+        <v>831</v>
       </c>
       <c r="I68" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -5097,28 +5195,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C69" t="s">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="D69" t="s">
-        <v>520</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>668</v>
+        <v>541</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>696</v>
       </c>
       <c r="F69" t="s">
-        <v>751</v>
+        <v>800</v>
       </c>
       <c r="G69" t="s">
-        <v>751</v>
+        <v>787</v>
       </c>
       <c r="H69" t="s">
-        <v>788</v>
+        <v>826</v>
       </c>
       <c r="I69" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -5126,28 +5224,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C70" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="D70" t="s">
-        <v>521</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>669</v>
+        <v>542</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>697</v>
       </c>
       <c r="F70" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G70" t="s">
-        <v>763</v>
+        <v>809</v>
       </c>
       <c r="H70" t="s">
-        <v>789</v>
+        <v>835</v>
       </c>
       <c r="I70" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -5155,28 +5253,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="C71" t="s">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="D71" t="s">
-        <v>522</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>670</v>
+        <v>543</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>698</v>
       </c>
       <c r="F71" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="G71" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="H71" t="s">
-        <v>793</v>
+        <v>835</v>
       </c>
       <c r="I71" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -5184,28 +5282,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C72" t="s">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="D72" t="s">
-        <v>523</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>671</v>
+        <v>544</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>699</v>
       </c>
       <c r="F72" t="s">
-        <v>765</v>
+        <v>791</v>
       </c>
       <c r="G72" t="s">
-        <v>767</v>
+        <v>789</v>
       </c>
       <c r="H72" t="s">
-        <v>793</v>
+        <v>831</v>
       </c>
       <c r="I72" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -5213,28 +5311,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="C73" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="D73" t="s">
-        <v>524</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>672</v>
+        <v>545</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>700</v>
       </c>
       <c r="F73" t="s">
-        <v>765</v>
+        <v>787</v>
       </c>
       <c r="G73" t="s">
-        <v>760</v>
+        <v>787</v>
       </c>
       <c r="H73" t="s">
-        <v>795</v>
+        <v>826</v>
       </c>
       <c r="I73" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -5242,28 +5340,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C74" t="s">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="D74" t="s">
-        <v>525</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>673</v>
+        <v>546</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>701</v>
       </c>
       <c r="F74" t="s">
-        <v>749</v>
+        <v>788</v>
       </c>
       <c r="G74" t="s">
-        <v>772</v>
+        <v>799</v>
       </c>
       <c r="H74" t="s">
-        <v>795</v>
+        <v>827</v>
       </c>
       <c r="I74" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -5271,28 +5369,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C75" t="s">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="D75" t="s">
-        <v>526</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>674</v>
+        <v>547</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>702</v>
       </c>
       <c r="F75" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G75" t="s">
-        <v>772</v>
+        <v>791</v>
       </c>
       <c r="H75" t="s">
-        <v>792</v>
+        <v>830</v>
       </c>
       <c r="I75" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -5300,28 +5398,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C76" t="s">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="D76" t="s">
-        <v>527</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>675</v>
+        <v>548</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>703</v>
       </c>
       <c r="F76" t="s">
-        <v>752</v>
+        <v>801</v>
       </c>
       <c r="G76" t="s">
-        <v>755</v>
+        <v>803</v>
       </c>
       <c r="H76" t="s">
-        <v>791</v>
+        <v>830</v>
       </c>
       <c r="I76" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -5329,28 +5427,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C77" t="s">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="D77" t="s">
-        <v>528</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>676</v>
+        <v>549</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>704</v>
       </c>
       <c r="F77" t="s">
-        <v>756</v>
+        <v>801</v>
       </c>
       <c r="G77" t="s">
-        <v>756</v>
+        <v>796</v>
       </c>
       <c r="H77" t="s">
-        <v>794</v>
+        <v>832</v>
       </c>
       <c r="I77" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -5358,28 +5456,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C78" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="D78" t="s">
-        <v>529</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>677</v>
+        <v>550</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>705</v>
       </c>
       <c r="F78" t="s">
-        <v>751</v>
+        <v>785</v>
       </c>
       <c r="G78" t="s">
-        <v>751</v>
+        <v>809</v>
       </c>
       <c r="H78" t="s">
-        <v>782</v>
+        <v>832</v>
       </c>
       <c r="I78" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -5387,28 +5485,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="C79" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="D79" t="s">
-        <v>530</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>678</v>
+        <v>551</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>706</v>
       </c>
       <c r="F79" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="G79" t="s">
-        <v>778</v>
+        <v>809</v>
       </c>
       <c r="H79" t="s">
-        <v>797</v>
+        <v>829</v>
       </c>
       <c r="I79" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -5416,28 +5514,28 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C80" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="D80" t="s">
-        <v>531</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>679</v>
+        <v>552</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>707</v>
       </c>
       <c r="F80" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G80" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="H80" t="s">
-        <v>795</v>
+        <v>828</v>
       </c>
       <c r="I80" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -5445,28 +5543,28 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C81" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="D81" t="s">
-        <v>532</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>680</v>
+        <v>553</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>708</v>
       </c>
       <c r="F81" t="s">
-        <v>752</v>
+        <v>792</v>
       </c>
       <c r="G81" t="s">
-        <v>763</v>
+        <v>792</v>
       </c>
       <c r="H81" t="s">
-        <v>797</v>
+        <v>831</v>
       </c>
       <c r="I81" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -5474,28 +5572,28 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C82" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="D82" t="s">
-        <v>533</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>681</v>
+        <v>554</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>709</v>
       </c>
       <c r="F82" t="s">
-        <v>752</v>
+        <v>787</v>
       </c>
       <c r="G82" t="s">
-        <v>763</v>
+        <v>787</v>
       </c>
       <c r="H82" t="s">
-        <v>793</v>
+        <v>820</v>
       </c>
       <c r="I82" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -5503,28 +5601,28 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="C83" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="D83" t="s">
-        <v>534</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>682</v>
+        <v>555</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>710</v>
       </c>
       <c r="F83" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G83" t="s">
-        <v>751</v>
+        <v>815</v>
       </c>
       <c r="H83" t="s">
-        <v>797</v>
+        <v>835</v>
       </c>
       <c r="I83" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -5532,28 +5630,28 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C84" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="D84" t="s">
-        <v>535</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>683</v>
+        <v>556</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>711</v>
       </c>
       <c r="F84" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G84" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="H84" t="s">
-        <v>798</v>
+        <v>832</v>
       </c>
       <c r="I84" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -5561,28 +5659,28 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C85" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="D85" t="s">
-        <v>536</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>684</v>
+        <v>557</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>712</v>
       </c>
       <c r="F85" t="s">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="G85" t="s">
-        <v>755</v>
+        <v>799</v>
       </c>
       <c r="H85" t="s">
-        <v>787</v>
+        <v>835</v>
       </c>
       <c r="I85" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -5590,28 +5688,28 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C86" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="D86" t="s">
-        <v>537</v>
-      </c>
-      <c r="E86" s="2" t="s">
-        <v>685</v>
+        <v>558</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>713</v>
       </c>
       <c r="F86" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G86" t="s">
-        <v>769</v>
+        <v>799</v>
       </c>
       <c r="H86" t="s">
-        <v>782</v>
+        <v>830</v>
       </c>
       <c r="I86" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -5619,28 +5717,28 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="C87" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="D87" t="s">
-        <v>538</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>686</v>
+        <v>559</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>714</v>
       </c>
       <c r="F87" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="G87" t="s">
-        <v>761</v>
+        <v>787</v>
       </c>
       <c r="H87" t="s">
-        <v>794</v>
+        <v>835</v>
       </c>
       <c r="I87" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -5648,28 +5746,28 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C88" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="D88" t="s">
-        <v>539</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>687</v>
+        <v>560</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>715</v>
       </c>
       <c r="F88" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="G88" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="H88" t="s">
-        <v>783</v>
+        <v>836</v>
       </c>
       <c r="I88" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -5677,28 +5775,28 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="C89" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="D89" t="s">
-        <v>540</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>688</v>
+        <v>561</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>716</v>
       </c>
       <c r="F89" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="G89" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="H89" t="s">
-        <v>797</v>
+        <v>825</v>
       </c>
       <c r="I89" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -5706,28 +5804,28 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="C90" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="D90" t="s">
-        <v>541</v>
-      </c>
-      <c r="E90" s="2" t="s">
-        <v>689</v>
+        <v>562</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>717</v>
       </c>
       <c r="F90" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="G90" t="s">
-        <v>755</v>
+        <v>805</v>
       </c>
       <c r="H90" t="s">
-        <v>794</v>
+        <v>820</v>
       </c>
       <c r="I90" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -5735,28 +5833,28 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C91" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="D91" t="s">
-        <v>542</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>690</v>
+        <v>563</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>718</v>
       </c>
       <c r="F91" t="s">
-        <v>755</v>
+        <v>791</v>
       </c>
       <c r="G91" t="s">
-        <v>755</v>
+        <v>797</v>
       </c>
       <c r="H91" t="s">
-        <v>788</v>
+        <v>831</v>
       </c>
       <c r="I91" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -5764,28 +5862,28 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C92" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="D92" t="s">
-        <v>543</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>691</v>
+        <v>564</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>719</v>
       </c>
       <c r="F92" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="G92" t="s">
-        <v>756</v>
+        <v>791</v>
       </c>
       <c r="H92" t="s">
-        <v>799</v>
+        <v>821</v>
       </c>
       <c r="I92" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -5793,28 +5891,28 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C93" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="D93" t="s">
-        <v>544</v>
-      </c>
-      <c r="E93" s="2" t="s">
-        <v>692</v>
+        <v>565</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>720</v>
       </c>
       <c r="F93" t="s">
-        <v>767</v>
+        <v>802</v>
       </c>
       <c r="G93" t="s">
-        <v>760</v>
+        <v>802</v>
       </c>
       <c r="H93" t="s">
-        <v>794</v>
+        <v>835</v>
       </c>
       <c r="I93" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -5822,28 +5920,28 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C94" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="D94" t="s">
-        <v>545</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>693</v>
+        <v>566</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>721</v>
       </c>
       <c r="F94" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="G94" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="H94" t="s">
-        <v>795</v>
+        <v>831</v>
       </c>
       <c r="I94" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -5851,28 +5949,28 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C95" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="D95" t="s">
-        <v>546</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>694</v>
+        <v>567</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>722</v>
       </c>
       <c r="F95" t="s">
-        <v>756</v>
+        <v>784</v>
       </c>
       <c r="G95" t="s">
-        <v>756</v>
+        <v>806</v>
       </c>
       <c r="H95" t="s">
-        <v>794</v>
+        <v>825</v>
       </c>
       <c r="I95" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -5880,28 +5978,28 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="C96" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="D96" t="s">
-        <v>547</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>695</v>
+        <v>568</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>723</v>
       </c>
       <c r="F96" t="s">
-        <v>750</v>
+        <v>791</v>
       </c>
       <c r="G96" t="s">
-        <v>750</v>
+        <v>791</v>
       </c>
       <c r="H96" t="s">
-        <v>783</v>
+        <v>826</v>
       </c>
       <c r="I96" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -5909,28 +6007,28 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="C97" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="D97" t="s">
-        <v>548</v>
-      </c>
-      <c r="E97" s="2" t="s">
-        <v>696</v>
+        <v>569</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>724</v>
       </c>
       <c r="F97" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G97" t="s">
-        <v>763</v>
+        <v>792</v>
       </c>
       <c r="H97" t="s">
-        <v>791</v>
+        <v>837</v>
       </c>
       <c r="I97" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -5938,28 +6036,28 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="C98" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="D98" t="s">
-        <v>549</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>697</v>
+        <v>570</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>725</v>
       </c>
       <c r="F98" t="s">
-        <v>752</v>
+        <v>803</v>
       </c>
       <c r="G98" t="s">
-        <v>757</v>
+        <v>796</v>
       </c>
       <c r="H98" t="s">
-        <v>787</v>
+        <v>831</v>
       </c>
       <c r="I98" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -5967,28 +6065,28 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C99" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="D99" t="s">
-        <v>550</v>
-      </c>
-      <c r="E99" s="2" t="s">
-        <v>698</v>
+        <v>571</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>726</v>
       </c>
       <c r="F99" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="G99" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="H99" t="s">
-        <v>783</v>
+        <v>832</v>
       </c>
       <c r="I99" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -5996,28 +6094,28 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C100" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="D100" t="s">
-        <v>551</v>
-      </c>
-      <c r="E100" s="2" t="s">
-        <v>699</v>
+        <v>572</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>727</v>
       </c>
       <c r="F100" t="s">
-        <v>752</v>
+        <v>792</v>
       </c>
       <c r="G100" t="s">
-        <v>758</v>
+        <v>792</v>
       </c>
       <c r="H100" t="s">
-        <v>799</v>
+        <v>831</v>
       </c>
       <c r="I100" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -6025,28 +6123,28 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C101" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="D101" t="s">
-        <v>552</v>
-      </c>
-      <c r="E101" s="2" t="s">
-        <v>700</v>
+        <v>573</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>728</v>
       </c>
       <c r="F101" t="s">
-        <v>767</v>
+        <v>786</v>
       </c>
       <c r="G101" t="s">
-        <v>760</v>
+        <v>786</v>
       </c>
       <c r="H101" t="s">
-        <v>784</v>
+        <v>821</v>
       </c>
       <c r="I101" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6054,28 +6152,28 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C102" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="D102" t="s">
-        <v>553</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>701</v>
+        <v>574</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>729</v>
       </c>
       <c r="F102" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G102" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H102" t="s">
-        <v>787</v>
+        <v>828</v>
       </c>
       <c r="I102" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -6083,28 +6181,28 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C103" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="D103" t="s">
-        <v>554</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>702</v>
+        <v>575</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>730</v>
       </c>
       <c r="F103" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G103" t="s">
-        <v>779</v>
+        <v>793</v>
       </c>
       <c r="H103" t="s">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="I103" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -6112,28 +6210,28 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C104" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="D104" t="s">
-        <v>555</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>703</v>
+        <v>576</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>731</v>
       </c>
       <c r="F104" t="s">
-        <v>755</v>
+        <v>786</v>
       </c>
       <c r="G104" t="s">
-        <v>755</v>
+        <v>806</v>
       </c>
       <c r="H104" t="s">
-        <v>792</v>
+        <v>838</v>
       </c>
       <c r="I104" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6141,28 +6239,28 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C105" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="D105" t="s">
-        <v>556</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>704</v>
+        <v>577</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>732</v>
       </c>
       <c r="F105" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G105" t="s">
-        <v>752</v>
+        <v>794</v>
       </c>
       <c r="H105" t="s">
-        <v>789</v>
+        <v>837</v>
       </c>
       <c r="I105" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6170,28 +6268,28 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="C106" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="D106" t="s">
-        <v>557</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>705</v>
+        <v>578</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>733</v>
       </c>
       <c r="F106" t="s">
-        <v>752</v>
+        <v>803</v>
       </c>
       <c r="G106" t="s">
-        <v>772</v>
+        <v>796</v>
       </c>
       <c r="H106" t="s">
-        <v>799</v>
+        <v>822</v>
       </c>
       <c r="I106" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6199,28 +6297,28 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="C107" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="D107" t="s">
-        <v>558</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>706</v>
+        <v>579</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>734</v>
       </c>
       <c r="F107" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G107" t="s">
-        <v>763</v>
+        <v>799</v>
       </c>
       <c r="H107" t="s">
-        <v>801</v>
+        <v>825</v>
       </c>
       <c r="I107" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -6228,28 +6326,28 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C108" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="D108" t="s">
-        <v>559</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>707</v>
+        <v>580</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>735</v>
       </c>
       <c r="F108" t="s">
-        <v>752</v>
+        <v>787</v>
       </c>
       <c r="G108" t="s">
-        <v>752</v>
+        <v>816</v>
       </c>
       <c r="H108" t="s">
-        <v>793</v>
+        <v>839</v>
       </c>
       <c r="I108" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -6257,28 +6355,28 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="C109" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="D109" t="s">
-        <v>560</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>708</v>
+        <v>581</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>736</v>
       </c>
       <c r="F109" t="s">
-        <v>767</v>
+        <v>791</v>
       </c>
       <c r="G109" t="s">
-        <v>760</v>
+        <v>791</v>
       </c>
       <c r="H109" t="s">
-        <v>792</v>
+        <v>829</v>
       </c>
       <c r="I109" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -6286,28 +6384,28 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C110" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="D110" t="s">
-        <v>561</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>709</v>
+        <v>582</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>737</v>
       </c>
       <c r="F110" t="s">
-        <v>768</v>
+        <v>788</v>
       </c>
       <c r="G110" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="H110" t="s">
-        <v>802</v>
+        <v>827</v>
       </c>
       <c r="I110" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -6315,28 +6413,28 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="C111" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="D111" t="s">
-        <v>562</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>710</v>
+        <v>583</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>738</v>
       </c>
       <c r="F111" t="s">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="G111" t="s">
-        <v>765</v>
+        <v>809</v>
       </c>
       <c r="H111" t="s">
-        <v>787</v>
+        <v>837</v>
       </c>
       <c r="I111" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -6344,28 +6442,28 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C112" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="D112" t="s">
-        <v>563</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>711</v>
+        <v>584</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>739</v>
       </c>
       <c r="F112" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G112" t="s">
-        <v>752</v>
+        <v>799</v>
       </c>
       <c r="H112" t="s">
-        <v>787</v>
+        <v>840</v>
       </c>
       <c r="I112" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -6373,28 +6471,28 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C113" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="D113" t="s">
-        <v>564</v>
-      </c>
-      <c r="E113" s="2" t="s">
-        <v>712</v>
+        <v>585</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>740</v>
       </c>
       <c r="F113" t="s">
-        <v>755</v>
+        <v>784</v>
       </c>
       <c r="G113" t="s">
-        <v>755</v>
+        <v>806</v>
       </c>
       <c r="H113" t="s">
-        <v>787</v>
+        <v>825</v>
       </c>
       <c r="I113" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -6402,28 +6500,28 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C114" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="D114" t="s">
-        <v>565</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>713</v>
+        <v>586</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>741</v>
       </c>
       <c r="F114" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="G114" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="H114" t="s">
-        <v>784</v>
+        <v>830</v>
       </c>
       <c r="I114" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -6431,28 +6529,28 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C115" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="D115" t="s">
-        <v>566</v>
-      </c>
-      <c r="E115" s="2" t="s">
-        <v>714</v>
+        <v>587</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>742</v>
       </c>
       <c r="F115" t="s">
-        <v>750</v>
+        <v>803</v>
       </c>
       <c r="G115" t="s">
-        <v>750</v>
+        <v>796</v>
       </c>
       <c r="H115" t="s">
-        <v>786</v>
+        <v>829</v>
       </c>
       <c r="I115" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -6460,28 +6558,28 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C116" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="D116" t="s">
-        <v>567</v>
-      </c>
-      <c r="E116" s="2" t="s">
-        <v>715</v>
+        <v>588</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>743</v>
       </c>
       <c r="F116" t="s">
-        <v>755</v>
+        <v>804</v>
       </c>
       <c r="G116" t="s">
-        <v>755</v>
+        <v>817</v>
       </c>
       <c r="H116" t="s">
-        <v>783</v>
+        <v>841</v>
       </c>
       <c r="I116" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -6489,28 +6587,28 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="C117" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="D117" t="s">
-        <v>568</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>716</v>
+        <v>589</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>744</v>
       </c>
       <c r="F117" t="s">
-        <v>751</v>
+        <v>791</v>
       </c>
       <c r="G117" t="s">
-        <v>751</v>
+        <v>801</v>
       </c>
       <c r="H117" t="s">
-        <v>788</v>
+        <v>825</v>
       </c>
       <c r="I117" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -6518,28 +6616,28 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C118" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="D118" t="s">
-        <v>569</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>717</v>
+        <v>590</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>745</v>
       </c>
       <c r="F118" t="s">
-        <v>755</v>
+        <v>784</v>
       </c>
       <c r="G118" t="s">
-        <v>755</v>
+        <v>806</v>
       </c>
       <c r="H118" t="s">
-        <v>787</v>
+        <v>825</v>
       </c>
       <c r="I118" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -6547,28 +6645,28 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C119" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="D119" t="s">
-        <v>570</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>718</v>
+        <v>591</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>746</v>
       </c>
       <c r="F119" t="s">
-        <v>758</v>
+        <v>788</v>
       </c>
       <c r="G119" t="s">
-        <v>756</v>
+        <v>788</v>
       </c>
       <c r="H119" t="s">
-        <v>790</v>
+        <v>825</v>
       </c>
       <c r="I119" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -6576,28 +6674,28 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C120" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="D120" t="s">
-        <v>571</v>
-      </c>
-      <c r="E120" s="2" t="s">
-        <v>719</v>
+        <v>592</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>747</v>
       </c>
       <c r="F120" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="G120" t="s">
-        <v>770</v>
+        <v>791</v>
       </c>
       <c r="H120" t="s">
-        <v>793</v>
+        <v>825</v>
       </c>
       <c r="I120" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -6605,28 +6703,28 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C121" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="D121" t="s">
-        <v>572</v>
-      </c>
-      <c r="E121" s="2" t="s">
-        <v>720</v>
+        <v>593</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>748</v>
       </c>
       <c r="F121" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G121" t="s">
-        <v>777</v>
+        <v>786</v>
       </c>
       <c r="H121" t="s">
-        <v>793</v>
+        <v>822</v>
       </c>
       <c r="I121" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -6634,28 +6732,28 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C122" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="D122" t="s">
-        <v>573</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>721</v>
+        <v>594</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>749</v>
       </c>
       <c r="F122" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G122" t="s">
-        <v>763</v>
+        <v>786</v>
       </c>
       <c r="H122" t="s">
-        <v>793</v>
+        <v>824</v>
       </c>
       <c r="I122" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -6663,28 +6761,28 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C123" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="D123" t="s">
-        <v>574</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>722</v>
+        <v>595</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>750</v>
       </c>
       <c r="F123" t="s">
-        <v>769</v>
+        <v>791</v>
       </c>
       <c r="G123" t="s">
-        <v>778</v>
+        <v>791</v>
       </c>
       <c r="H123" t="s">
-        <v>793</v>
+        <v>821</v>
       </c>
       <c r="I123" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -6692,28 +6790,28 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="C124" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="D124" t="s">
-        <v>575</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>723</v>
+        <v>596</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>751</v>
       </c>
       <c r="F124" t="s">
-        <v>752</v>
+        <v>787</v>
       </c>
       <c r="G124" t="s">
-        <v>763</v>
+        <v>787</v>
       </c>
       <c r="H124" t="s">
-        <v>793</v>
+        <v>826</v>
       </c>
       <c r="I124" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -6721,28 +6819,28 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="C125" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="D125" t="s">
-        <v>576</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>724</v>
+        <v>597</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>752</v>
       </c>
       <c r="F125" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="G125" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
       <c r="H125" t="s">
-        <v>797</v>
+        <v>825</v>
       </c>
       <c r="I125" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -6750,28 +6848,28 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C126" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="D126" t="s">
-        <v>577</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>725</v>
+        <v>598</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>753</v>
       </c>
       <c r="F126" t="s">
-        <v>751</v>
+        <v>794</v>
       </c>
       <c r="G126" t="s">
-        <v>751</v>
+        <v>792</v>
       </c>
       <c r="H126" t="s">
-        <v>788</v>
+        <v>819</v>
       </c>
       <c r="I126" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -6779,28 +6877,28 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C127" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="D127" t="s">
-        <v>578</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>726</v>
+        <v>599</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>754</v>
       </c>
       <c r="F127" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G127" t="s">
-        <v>763</v>
+        <v>807</v>
       </c>
       <c r="H127" t="s">
-        <v>787</v>
+        <v>830</v>
       </c>
       <c r="I127" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -6808,28 +6906,28 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="C128" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="D128" t="s">
-        <v>579</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>727</v>
+        <v>600</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>755</v>
       </c>
       <c r="F128" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G128" t="s">
-        <v>780</v>
+        <v>814</v>
       </c>
       <c r="H128" t="s">
-        <v>788</v>
+        <v>830</v>
       </c>
       <c r="I128" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -6837,28 +6935,28 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="C129" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="D129" t="s">
-        <v>580</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>728</v>
+        <v>601</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>756</v>
       </c>
       <c r="F129" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G129" t="s">
-        <v>751</v>
+        <v>799</v>
       </c>
       <c r="H129" t="s">
-        <v>800</v>
+        <v>830</v>
       </c>
       <c r="I129" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -6866,28 +6964,28 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C130" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="D130" t="s">
-        <v>581</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>729</v>
+        <v>602</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>757</v>
       </c>
       <c r="F130" t="s">
-        <v>755</v>
+        <v>805</v>
       </c>
       <c r="G130" t="s">
-        <v>755</v>
+        <v>815</v>
       </c>
       <c r="H130" t="s">
-        <v>792</v>
+        <v>830</v>
       </c>
       <c r="I130" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -6895,28 +6993,28 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="C131" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="D131" t="s">
-        <v>582</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>730</v>
+        <v>603</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>758</v>
       </c>
       <c r="F131" t="s">
-        <v>762</v>
+        <v>788</v>
       </c>
       <c r="G131" t="s">
-        <v>777</v>
+        <v>799</v>
       </c>
       <c r="H131" t="s">
-        <v>787</v>
+        <v>830</v>
       </c>
       <c r="I131" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -6924,28 +7022,28 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="C132" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="D132" t="s">
-        <v>583</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>731</v>
+        <v>604</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>759</v>
       </c>
       <c r="F132" t="s">
-        <v>755</v>
+        <v>802</v>
       </c>
       <c r="G132" t="s">
-        <v>755</v>
+        <v>802</v>
       </c>
       <c r="H132" t="s">
-        <v>792</v>
+        <v>835</v>
       </c>
       <c r="I132" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -6953,28 +7051,28 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C133" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="D133" t="s">
-        <v>584</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>732</v>
+        <v>605</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>760</v>
       </c>
       <c r="F133" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="G133" t="s">
-        <v>755</v>
+        <v>787</v>
       </c>
       <c r="H133" t="s">
-        <v>792</v>
+        <v>826</v>
       </c>
       <c r="I133" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -6982,28 +7080,28 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="C134" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="D134" t="s">
-        <v>585</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>733</v>
+        <v>606</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>761</v>
       </c>
       <c r="F134" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G134" t="s">
-        <v>770</v>
+        <v>799</v>
       </c>
       <c r="H134" t="s">
-        <v>793</v>
+        <v>825</v>
       </c>
       <c r="I134" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -7011,28 +7109,28 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="C135" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="D135" t="s">
-        <v>586</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>734</v>
+        <v>607</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>762</v>
       </c>
       <c r="F135" t="s">
-        <v>750</v>
+        <v>788</v>
       </c>
       <c r="G135" t="s">
-        <v>750</v>
+        <v>817</v>
       </c>
       <c r="H135" t="s">
-        <v>783</v>
+        <v>826</v>
       </c>
       <c r="I135" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -7040,28 +7138,28 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="C136" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="D136" t="s">
-        <v>587</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>735</v>
+        <v>608</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>763</v>
       </c>
       <c r="F136" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="G136" t="s">
-        <v>750</v>
+        <v>787</v>
       </c>
       <c r="H136" t="s">
-        <v>792</v>
+        <v>839</v>
       </c>
       <c r="I136" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -7069,28 +7167,28 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C137" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="D137" t="s">
-        <v>588</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>736</v>
+        <v>609</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>764</v>
       </c>
       <c r="F137" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="G137" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
       <c r="H137" t="s">
-        <v>795</v>
+        <v>829</v>
       </c>
       <c r="I137" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -7098,28 +7196,28 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C138" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="D138" t="s">
-        <v>589</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>737</v>
+        <v>610</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>765</v>
       </c>
       <c r="F138" t="s">
-        <v>752</v>
+        <v>798</v>
       </c>
       <c r="G138" t="s">
-        <v>752</v>
+        <v>814</v>
       </c>
       <c r="H138" t="s">
-        <v>795</v>
+        <v>825</v>
       </c>
       <c r="I138" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -7127,28 +7225,28 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C139" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="D139" t="s">
-        <v>590</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>738</v>
+        <v>611</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>766</v>
       </c>
       <c r="F139" t="s">
-        <v>760</v>
+        <v>791</v>
       </c>
       <c r="G139" t="s">
-        <v>769</v>
+        <v>791</v>
       </c>
       <c r="H139" t="s">
-        <v>794</v>
+        <v>829</v>
       </c>
       <c r="I139" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -7156,28 +7254,28 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C140" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="D140" t="s">
-        <v>591</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>739</v>
+        <v>612</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>767</v>
       </c>
       <c r="F140" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="G140" t="s">
-        <v>763</v>
+        <v>791</v>
       </c>
       <c r="H140" t="s">
-        <v>782</v>
+        <v>829</v>
       </c>
       <c r="I140" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -7185,28 +7283,28 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C141" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="D141" t="s">
-        <v>592</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>740</v>
+        <v>613</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>768</v>
       </c>
       <c r="F141" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G141" t="s">
-        <v>781</v>
+        <v>807</v>
       </c>
       <c r="H141" t="s">
-        <v>784</v>
+        <v>830</v>
       </c>
       <c r="I141" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -7214,28 +7312,28 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C142" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="D142" t="s">
-        <v>593</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>741</v>
+        <v>614</v>
+      </c>
+      <c r="E142" s="1" t="s">
+        <v>769</v>
       </c>
       <c r="F142" t="s">
-        <v>767</v>
+        <v>786</v>
       </c>
       <c r="G142" t="s">
-        <v>760</v>
+        <v>786</v>
       </c>
       <c r="H142" t="s">
-        <v>803</v>
+        <v>821</v>
       </c>
       <c r="I142" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -7243,28 +7341,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C143" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="D143" t="s">
-        <v>594</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>742</v>
+        <v>615</v>
+      </c>
+      <c r="E143" s="1" t="s">
+        <v>770</v>
       </c>
       <c r="F143" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="G143" t="s">
-        <v>752</v>
+        <v>786</v>
       </c>
       <c r="H143" t="s">
-        <v>795</v>
+        <v>829</v>
       </c>
       <c r="I143" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -7272,28 +7370,28 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C144" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="D144" t="s">
-        <v>595</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>743</v>
+        <v>616</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>771</v>
       </c>
       <c r="F144" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G144" t="s">
-        <v>776</v>
+        <v>799</v>
       </c>
       <c r="H144" t="s">
-        <v>782</v>
+        <v>832</v>
       </c>
       <c r="I144" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -7301,28 +7399,28 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C145" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="D145" t="s">
-        <v>596</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>744</v>
+        <v>617</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>772</v>
       </c>
       <c r="F145" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="G145" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="H145" t="s">
-        <v>788</v>
+        <v>832</v>
       </c>
       <c r="I145" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -7330,28 +7428,28 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C146" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="D146" t="s">
-        <v>597</v>
-      </c>
-      <c r="E146" s="2" t="s">
-        <v>745</v>
+        <v>618</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>773</v>
       </c>
       <c r="F146" t="s">
-        <v>759</v>
+        <v>796</v>
       </c>
       <c r="G146" t="s">
-        <v>753</v>
+        <v>805</v>
       </c>
       <c r="H146" t="s">
-        <v>804</v>
+        <v>831</v>
       </c>
       <c r="I146" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -7359,28 +7457,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="C147" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="D147" t="s">
-        <v>598</v>
-      </c>
-      <c r="E147" s="2" t="s">
-        <v>746</v>
+        <v>619</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>774</v>
       </c>
       <c r="F147" t="s">
-        <v>752</v>
+        <v>788</v>
       </c>
       <c r="G147" t="s">
-        <v>752</v>
+        <v>799</v>
       </c>
       <c r="H147" t="s">
-        <v>795</v>
+        <v>820</v>
       </c>
       <c r="I147" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -7388,28 +7486,28 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="C148" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="D148" t="s">
-        <v>599</v>
-      </c>
-      <c r="E148" s="2" t="s">
-        <v>747</v>
+        <v>620</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>775</v>
       </c>
       <c r="F148" t="s">
-        <v>749</v>
+        <v>787</v>
       </c>
       <c r="G148" t="s">
-        <v>772</v>
+        <v>818</v>
       </c>
       <c r="H148" t="s">
-        <v>794</v>
+        <v>822</v>
       </c>
       <c r="I148" t="s">
-        <v>805</v>
+        <v>844</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -7417,28 +7515,231 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C149" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="D149" t="s">
-        <v>600</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>748</v>
+        <v>621</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>776</v>
       </c>
       <c r="F149" t="s">
-        <v>752</v>
+        <v>803</v>
       </c>
       <c r="G149" t="s">
-        <v>774</v>
+        <v>796</v>
       </c>
       <c r="H149" t="s">
+        <v>842</v>
+      </c>
+      <c r="I149" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9">
+      <c r="A150" t="s">
+        <v>157</v>
+      </c>
+      <c r="B150" t="s">
+        <v>312</v>
+      </c>
+      <c r="C150" t="s">
+        <v>467</v>
+      </c>
+      <c r="D150" t="s">
+        <v>622</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="F150" t="s">
+        <v>788</v>
+      </c>
+      <c r="G150" t="s">
+        <v>788</v>
+      </c>
+      <c r="H150" t="s">
+        <v>832</v>
+      </c>
+      <c r="I150" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9">
+      <c r="A151" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151" t="s">
+        <v>313</v>
+      </c>
+      <c r="C151" t="s">
+        <v>468</v>
+      </c>
+      <c r="D151" t="s">
+        <v>623</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="F151" t="s">
+        <v>788</v>
+      </c>
+      <c r="G151" t="s">
+        <v>813</v>
+      </c>
+      <c r="H151" t="s">
+        <v>820</v>
+      </c>
+      <c r="I151" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9">
+      <c r="A152" t="s">
+        <v>159</v>
+      </c>
+      <c r="B152" t="s">
+        <v>314</v>
+      </c>
+      <c r="C152" t="s">
+        <v>469</v>
+      </c>
+      <c r="D152" t="s">
+        <v>624</v>
+      </c>
+      <c r="E152" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="F152" t="s">
+        <v>787</v>
+      </c>
+      <c r="G152" t="s">
+        <v>787</v>
+      </c>
+      <c r="H152" t="s">
+        <v>826</v>
+      </c>
+      <c r="I152" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9">
+      <c r="A153" t="s">
+        <v>160</v>
+      </c>
+      <c r="B153" t="s">
+        <v>315</v>
+      </c>
+      <c r="C153" t="s">
+        <v>470</v>
+      </c>
+      <c r="D153" t="s">
+        <v>625</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="F153" t="s">
         <v>795</v>
       </c>
-      <c r="I149" t="s">
-        <v>805</v>
+      <c r="G153" t="s">
+        <v>789</v>
+      </c>
+      <c r="H153" t="s">
+        <v>843</v>
+      </c>
+      <c r="I153" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9">
+      <c r="A154" t="s">
+        <v>161</v>
+      </c>
+      <c r="B154" t="s">
+        <v>316</v>
+      </c>
+      <c r="C154" t="s">
+        <v>471</v>
+      </c>
+      <c r="D154" t="s">
+        <v>626</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="F154" t="s">
+        <v>788</v>
+      </c>
+      <c r="G154" t="s">
+        <v>788</v>
+      </c>
+      <c r="H154" t="s">
+        <v>832</v>
+      </c>
+      <c r="I154" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9">
+      <c r="A155" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" t="s">
+        <v>317</v>
+      </c>
+      <c r="C155" t="s">
+        <v>472</v>
+      </c>
+      <c r="D155" t="s">
+        <v>627</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="F155" t="s">
+        <v>785</v>
+      </c>
+      <c r="G155" t="s">
+        <v>809</v>
+      </c>
+      <c r="H155" t="s">
+        <v>831</v>
+      </c>
+      <c r="I155" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9">
+      <c r="A156" t="s">
+        <v>163</v>
+      </c>
+      <c r="B156" t="s">
+        <v>318</v>
+      </c>
+      <c r="C156" t="s">
+        <v>473</v>
+      </c>
+      <c r="D156" t="s">
+        <v>628</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F156" t="s">
+        <v>788</v>
+      </c>
+      <c r="G156" t="s">
+        <v>811</v>
+      </c>
+      <c r="H156" t="s">
+        <v>832</v>
+      </c>
+      <c r="I156" t="s">
+        <v>844</v>
       </c>
     </row>
   </sheetData>
@@ -7591,6 +7892,13 @@
     <hyperlink ref="E147" r:id="rId146"/>
     <hyperlink ref="E148" r:id="rId147"/>
     <hyperlink ref="E149" r:id="rId148"/>
+    <hyperlink ref="E150" r:id="rId149"/>
+    <hyperlink ref="E151" r:id="rId150"/>
+    <hyperlink ref="E152" r:id="rId151"/>
+    <hyperlink ref="E153" r:id="rId152"/>
+    <hyperlink ref="E154" r:id="rId153"/>
+    <hyperlink ref="E155" r:id="rId154"/>
+    <hyperlink ref="E156" r:id="rId155"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel-files/atlas-techniques.xlsx
+++ b/excel-files/atlas-techniques.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="845">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="905">
   <si>
     <t>ID</t>
   </si>
@@ -52,6 +52,9 @@
     <t>AML.T0080</t>
   </si>
   <si>
+    <t>AML.T0010.005</t>
+  </si>
+  <si>
     <t>AML.T0098</t>
   </si>
   <si>
@@ -61,12 +64,18 @@
     <t>AML.T0053</t>
   </si>
   <si>
+    <t>AML.T0110</t>
+  </si>
+  <si>
     <t>AML.T0085.001</t>
   </si>
   <si>
     <t>AML.T0035</t>
   </si>
   <si>
+    <t>AML.T0112.001</t>
+  </si>
+  <si>
     <t>AML.T0008.000</t>
   </si>
   <si>
@@ -79,12 +88,21 @@
     <t>AML.T0096</t>
   </si>
   <si>
+    <t>AML.T0008.005</t>
+  </si>
+  <si>
     <t>AML.T0010.001</t>
   </si>
   <si>
     <t>AML.T0010</t>
   </si>
   <si>
+    <t>AML.T0111</t>
+  </si>
+  <si>
+    <t>AML.T0109</t>
+  </si>
+  <si>
     <t>AML.T0047</t>
   </si>
   <si>
@@ -106,6 +124,9 @@
     <t>AML.T0017.000</t>
   </si>
   <si>
+    <t>AML.T0034.002</t>
+  </si>
+  <si>
     <t>AML.T0091.000</t>
   </si>
   <si>
@@ -115,6 +136,9 @@
     <t>AML.T0043.002</t>
   </si>
   <si>
+    <t>AML.T0084.003</t>
+  </si>
+  <si>
     <t>AML.T0067.000</t>
   </si>
   <si>
@@ -226,6 +250,9 @@
     <t>AML.T0015</t>
   </si>
   <si>
+    <t>AML.T0034.000</t>
+  </si>
+  <si>
     <t>AML.T0086</t>
   </si>
   <si>
@@ -322,6 +349,12 @@
     <t>AML.T0067</t>
   </si>
   <si>
+    <t>AML.T0112.000</t>
+  </si>
+  <si>
+    <t>AML.T0112</t>
+  </si>
+  <si>
     <t>AML.T0011.003</t>
   </si>
   <si>
@@ -412,6 +445,9 @@
     <t>AML.T0048.001</t>
   </si>
   <si>
+    <t>AML.T0034.001</t>
+  </si>
+  <si>
     <t>AML.T0066</t>
   </si>
   <si>
@@ -517,6 +553,9 @@
     <t>attack-pattern--785ca1b4-7d17-51f1-a605-46a9f21fb9b0</t>
   </si>
   <si>
+    <t>attack-pattern--ffd308bb-3c90-550a-b3d4-f22f310f96d8</t>
+  </si>
+  <si>
     <t>attack-pattern--daca6b9c-9073-5aef-8017-737d1aa51f6d</t>
   </si>
   <si>
@@ -526,12 +565,18 @@
     <t>attack-pattern--b23b5475-a05e-5b4a-8e9f-8c758dd0cda8</t>
   </si>
   <si>
+    <t>attack-pattern--b1b2cc5a-7312-5f26-93d3-8b8ee1baf97d</t>
+  </si>
+  <si>
     <t>attack-pattern--bfa79523-214f-57f5-a445-c8a563f141f5</t>
   </si>
   <si>
     <t>attack-pattern--801658f2-81cd-5935-93c7-5e6e2d80e669</t>
   </si>
   <si>
+    <t>attack-pattern--bd0fd9ca-cc30-542e-9c1a-de9f66c9455b</t>
+  </si>
+  <si>
     <t>attack-pattern--b14fb0a1-a329-5982-a44c-c5da0b458d39</t>
   </si>
   <si>
@@ -544,12 +589,21 @@
     <t>attack-pattern--92a68652-d864-5c9c-9c1d-64ec09587390</t>
   </si>
   <si>
+    <t>attack-pattern--647ac4ac-b2bc-53f7-ab83-81f421a1f0b5</t>
+  </si>
+  <si>
     <t>attack-pattern--3bf297c5-2ab2-573a-aa4e-f20af3d2643c</t>
   </si>
   <si>
     <t>attack-pattern--2ea180c5-5df4-5815-8c78-a1cec1da6e18</t>
   </si>
   <si>
+    <t>attack-pattern--c4730fd0-ec0d-5bf5-8f03-e42faaa5055b</t>
+  </si>
+  <si>
+    <t>attack-pattern--885eb980-23c3-5b11-a310-9e1e65c010d4</t>
+  </si>
+  <si>
     <t>attack-pattern--a18245d0-2fb1-5f72-a069-5c176a0a11df</t>
   </si>
   <si>
@@ -571,6 +625,9 @@
     <t>attack-pattern--80a54397-082c-5d02-9d2e-1d30d7375c75</t>
   </si>
   <si>
+    <t>attack-pattern--4c31af04-b547-525a-975a-fbd371286b6e</t>
+  </si>
+  <si>
     <t>attack-pattern--7c36d546-bb69-5a52-a1ac-6d52cb10fc48</t>
   </si>
   <si>
@@ -580,6 +637,9 @@
     <t>attack-pattern--079c33e1-722c-58ad-983d-1bcd94a35c7b</t>
   </si>
   <si>
+    <t>attack-pattern--a1bfff2c-02a5-5104-b2bb-8def8acf1255</t>
+  </si>
+  <si>
     <t>attack-pattern--c89e98ce-f3a5-5351-9d5a-f2d8fd59ba5f</t>
   </si>
   <si>
@@ -691,6 +751,9 @@
     <t>attack-pattern--d74153d6-ac3c-52fb-9847-e0a6f675cd93</t>
   </si>
   <si>
+    <t>attack-pattern--4929e22c-64a1-59cf-a25e-543f88840889</t>
+  </si>
+  <si>
     <t>attack-pattern--66188cfa-76df-546b-be79-aa06debc8d79</t>
   </si>
   <si>
@@ -787,6 +850,12 @@
     <t>attack-pattern--ab0f8614-31f1-5014-a3e5-4520341c4933</t>
   </si>
   <si>
+    <t>attack-pattern--6354a977-1913-513b-bddf-21a3ba2947b7</t>
+  </si>
+  <si>
+    <t>attack-pattern--00d819a2-6a7f-5021-9c42-f02f6f0254c1</t>
+  </si>
+  <si>
     <t>attack-pattern--386bf4df-e7c7-54da-a297-fec4ffd5e1a8</t>
   </si>
   <si>
@@ -877,6 +946,9 @@
     <t>attack-pattern--780c1969-4275-5327-ba93-8987888429e1</t>
   </si>
   <si>
+    <t>attack-pattern--c54f84ef-93fd-560c-bbbb-5490753a2f97</t>
+  </si>
+  <si>
     <t>attack-pattern--0077e3e5-5405-5df5-8731-1085c5b385ae</t>
   </si>
   <si>
@@ -982,6 +1054,9 @@
     <t>AI Agent Context Poisoning</t>
   </si>
   <si>
+    <t>AI Agent Tool</t>
+  </si>
+  <si>
     <t>AI Agent Tool Credential Harvesting</t>
   </si>
   <si>
@@ -991,12 +1066,18 @@
     <t>AI Agent Tool Invocation</t>
   </si>
   <si>
+    <t>AI Agent Tool Poisoning</t>
+  </si>
+  <si>
     <t>AI Agent Tools</t>
   </si>
   <si>
     <t>AI Artifact Collection</t>
   </si>
   <si>
+    <t>AI Artifacts</t>
+  </si>
+  <si>
     <t>AI Development Workspaces</t>
   </si>
   <si>
@@ -1009,12 +1090,21 @@
     <t>AI Service API</t>
   </si>
   <si>
+    <t>AI Service Proxies</t>
+  </si>
+  <si>
     <t>AI Software</t>
   </si>
   <si>
     <t>AI Supply Chain Compromise</t>
   </si>
   <si>
+    <t>AI Supply Chain Reputation Inflation</t>
+  </si>
+  <si>
+    <t>AI Supply Chain Rug Pull</t>
+  </si>
+  <si>
     <t>AI-Enabled Product or Service</t>
   </si>
   <si>
@@ -1036,6 +1126,9 @@
     <t>Adversarial AI Attacks</t>
   </si>
   <si>
+    <t>Agentic Resource Consumption</t>
+  </si>
+  <si>
     <t>Application Access Token</t>
   </si>
   <si>
@@ -1045,6 +1138,9 @@
     <t>Black-Box Transfer</t>
   </si>
   <si>
+    <t>Call Chains</t>
+  </si>
+  <si>
     <t>Citations</t>
   </si>
   <si>
@@ -1156,6 +1252,9 @@
     <t>Evade AI Model</t>
   </si>
   <si>
+    <t>Excessive Queries</t>
+  </si>
+  <si>
     <t>Exfiltration via AI Agent Tool Invocation</t>
   </si>
   <si>
@@ -1252,6 +1351,12 @@
     <t>LLM Trusted Output Components Manipulation</t>
   </si>
   <si>
+    <t>Local AI Agent</t>
+  </si>
+  <si>
+    <t>Machine Compromise</t>
+  </si>
+  <si>
     <t>Malicious Link</t>
   </si>
   <si>
@@ -1340,6 +1445,9 @@
   </si>
   <si>
     <t>Reputational Harm</t>
+  </si>
+  <si>
+    <t>Resource-Intensive Queries</t>
   </si>
   <si>
     <t>Retrieval Content Crafting</t>
@@ -1447,6 +1555,16 @@
   <si>
     <t>Adversaries may attempt to manipulate the context used by an AI agent's large language model (LLM) to influence the responses it generates or actions it takes. This allows an adversary to persistently change the behavior of the target agent and further their goals.
 Context poisoning can be accomplished by prompting the an LLM to add instructions or preferences to memory (See [Memory](/techniques/AML.T0080.000)) or by simply prompting an LLM that uses prior messages in a thread as part of its context (See [Thread](/techniques/AML.T0080.001)).</t>
+  </si>
+  <si>
+    <t>Adversaries may target AI agent tools as a means to compromise a victim's AI supply chain. Tools add capabilities to AI agents, allowing them to interact with other services, connect to data sources, access internet resources, run system tools, and execute code. They are an attractive target for adversaries because compromising an AI agent can provide them with broad accesses and permissions on the victim's system via the agent's other tools.
+Poisoned agent tools (See [AI Agent Tool Poisoning](/techniques/AML.T0110)) can contain malicious code or [LLM Prompt Injection](/techniques/AML.T0051)s that manipulate the agent's behavior and even modify how other tools are called. Adversaries have successfully used a poisoned MCP server to exfiltrate private user data [\[5\]][koi].
+Agent tools have exploded in popularity, with thousands of MCP servers available publicly [\[2\]][glama]. They are often released on open-source software repositories such as GitHub, indexed on hubs specific to MCP servers [\[3\]][mcp-hub][\[4\]][mcp-server-hub], and published to package registries such as NPM. AI agents can also be connected to remotely-hosted tools [\[5\]][remote-mcp]. This creates an environment where malicious tools can proliferate rapidly and safeguards are often not in place.
+[koi]: https://www.koi.ai/blog/postmark-mcp-npm-malicious-backdoor-email-theft "First Malicious MCP in the Wild: The Postmark Backdoor That's Stealing Your Emails"
+[glama]: https://glama.ai/mcp/servers "Glama"
+[mcp-hub]: https://www.mcphub.ai/ "MCP Hub"
+[mcp-server-hub]: https://mcpserverhub.com/ "MCP Server Hub"
+[remote-mcp]: https://mcpservers.org/remote-mcp-servers "Remote MCP Servers"</t>
   </si>
   <si>
     <t>Adversaries may attempt to use their access to an AI agent on the victim's system to retrieve data from available agent tools to collect credentials. Agent tools may connect to a wide range of sources that may contain credentials including document stores (e.g. SharePoint, OneDrive or Google Drive), code repositories (e.g. GitHub or GitLab), or enterprise productivity tools (e.g. as email providers or Slack), and local notetaking tools (e.g. Obsidian or Apple Notes).</t>
@@ -1461,11 +1579,19 @@
 AI agents may be configured to have access to tools that are not directly accessible by users. Adversaries may abuse this to gain access to tools they otherwise wouldn't be able to use.</t>
   </si>
   <si>
+    <t>Adversaries may achieve persistence by poisoning tools used by AI agents including built-in tools or tools available to the agent via Model Context Protocol (MCP) connections. This involves compromising benign tools already integrated into the agent's environment.
+By altering tool behavior such as modifying parameters or descriptions, injecting hidden logic, or redirecting outputs, attackers can maintain long-term influence over the agent's actions, decisions, or external interactions. Poisoned tools may silently exfiltrate data, execute unauthorized commands, or manipulate downstream processes without raising suspicion.</t>
+  </si>
+  <si>
     <t>Adversaries may prompt the AI service to invoke various tools the agent has access to. Tools may retrieve data from different APIs or services in an organization.</t>
   </si>
   <si>
     <t>Adversaries may collect AI artifacts for [Exfiltration](/tactics/AML.TA0010) or for use in [AI Attack Staging](/tactics/AML.TA0001).
 AI artifacts include models and datasets as well as other telemetry data produced when interacting with a model.</t>
+  </si>
+  <si>
+    <t>Adversaries may achieve full system compromise by introducing malicious AI artifacts, such as models or data, that contain embedded malware or other malicious commands. AI artifacts are often stored in model registries or data stores and may affect many systems that pull these resources.
+Malicious content stored in AI artifacts may be executed as a result of unsafe serialization formats (e.g. Python pickle) or by other bundled scripts or notebooks.</t>
   </si>
   <si>
     <t>Developing and staging AI attacks often requires expensive compute resources.
@@ -1491,19 +1617,36 @@
 [1]: https://www.microsoft.com/en-us/security/blog/2025/11/03/sesameop-novel-backdoor-uses-openai-assistants-api-for-command-and-control/</t>
   </si>
   <si>
-    <t>Adversaries may target software packages that are commonly used in AI-enabled systems or are part of the AI DevOps lifecycle. This can include deep learning frameworks used to build AI models (e.g. PyTorch, TensorFlow, Jax), generative AI integration frameworks (e.g. LangChain, LangFlow), inference engines, AI DevOps tools, and Model Context Protocol servers, which give AI agents access to tools and data resources. They may also target the dependency chains of any of these software packages [\[1\]][1]. Additionally, adversaries may target specific components used by AI software such as configuration files [\[2\]][2] or example usage of AI tools, which may be distributed in Jupyter notebooks [\[3\]][3].
-Adversaries may compromise legitimate packages [\[4\]][4] or publish malicious software to a namesquatted location [\[1\]][1]. They may target package names that are hallucinated by large language models [\[5\]][5] (see: Publish Hallucinated Entities). They may also perform a "rugpull" in which they first publish a legitimate package and then publish a malicious version once they reach a critical mass of users [\[6\]][6].
+    <t>Adversaries may utilize commercial proxy services that resell access to AI services such as frontier model APIs.
+This infrastructure can be used to conduct large-scale campaigns to perform [Exfiltration via AI Inference API](/techniques/AML.T0024) via distillation. Adversaries may also use this infrastructure to [Generate Malicious Commands](/techniques/AML.T0102) for offensive cyber operations, or to generate content for [Spearphishing via Social Engineering LLM](/techniques/AML.T0052.000).
+Commercial AI service proxies distribute traffic from different accounts and various cloud platforms. The mix of traffic can make malicious activity difficult to detect and block [\[1\]][1].
+Malicious actors conduct [LLM Jacking](https://atlas.mitre.org/studies/AML.CS0030) attacks to gain access to victim accounts which they resell access to in their proxy services [\[2\]][2].
+[1]: https://www.anthropic.com/news/detecting-and-preventing-distillation-attacks
+[2]: https://sysdig.com/blog/llmjacking-stolen-cloud-credentials-used-in-new-ai-attack/</t>
+  </si>
+  <si>
+    <t>Adversaries may target software packages that are commonly used in AI-enabled systems or are part of the AI DevOps lifecycle. This can include deep learning frameworks used to build AI models (e.g. PyTorch, TensorFlow, Jax), generative AI integration frameworks (e.g. LangChain, LangFlow), inference engines, and AI DevOps tools. They may also target the dependency chains of any of these software packages [\[1\]][1]. Additionally, adversaries may target specific components used by AI software such as configuration files [\[2\]][2] or example usage of AI packages, which may be distributed in Jupyter notebooks [\[3\]][3].
+Adversaries may compromise legitimate packages [\[4\]][4] or publish malicious software to a namesquatted location [\[1\]][1]. They may target package names that are hallucinated by large language models [\[5\]][5] (see: Publish Hallucinated Entities). They may also perform a [AI Supply Chain Rug Pull](/techniques/AML.T0109) in which they first publish a legitimate package and then publish a malicious version once they reach a critical mass of users.
 [1]: https://pytorch.org/blog/compromised-nightly-dependency/ "Compromised PyTorch-nightly dependency chain between December 25th and December 30th, 2022."
 [2]: https://www.pillar.security/blog/new-vulnerability-in-github-copilot-and-cursor-how-hackers-can-weaponize-code-agents "New Vulnerability in GitHub Copilot and Cursor: How Hackers Can Weaponize Code Agents"
 [3]: https://medium.com/mlearning-ai/careful-who-you-colab-with-fa8001f933e7 "Careful Who You Colab With: abusing google colaboratory"
 [4]: https://aws.amazon.com/security/security-bulletins/AWS-2025-015/ "Security Update for Amazon Q Developer Extension for Visual Studio Code (Version #1.84)"
-[5]: https://www.trendmicro.com/vinfo/us/security/news/cybercrime-and-digital-threats/slopsquatting-when-ai-agents-hallucinate-malicious-packages "Slopsquatting: When AI Agents Hallucinate Malicious Packages"
-[6]: https://www.koi.ai/blog/postmark-mcp-npm-malicious-backdoor-email-theft "First Malicious MCP in the Wild: The Postmark Backdoor That's Stealing Your Emails"</t>
+[5]: https://www.trendmicro.com/vinfo/us/security/news/cybercrime-and-digital-threats/slopsquatting-when-ai-agents-hallucinate-malicious-packages "Slopsquatting: When AI Agents Hallucinate Malicious Packages"</t>
   </si>
   <si>
     <t>Adversaries may gain initial access to a system by compromising the unique portions of the AI supply chain.
 This could include [Hardware](/techniques/AML.T0010.000), [Data](/techniques/AML.T0010.002) and its annotations, parts of the AI [AI Software](/techniques/AML.T0010.001) stack, or the [Model](/techniques/AML.T0010.003) itself.
 In some instances the attacker will need secondary access to fully carry out an attack using compromised components of the supply chain.</t>
+  </si>
+  <si>
+    <t>AI Supply Chain Reputation Inflation is the process of building or leveraging genuinely credible-looking trust signals to increase the perceived legitimacy of AI supply chain components, with the goal of driving adoption of malicious or compromised assets.
+Adversaries use established developer accounts with a history of legitimate projects and contributions to publish AI models, datasets, packages, and MCP servers that appear trustworthy. They build reputation through real adoption signals such as downloads, GitHub stars, forks, and inclusion in dependency chains, often releasing benign versions before introducing malicious updates via [AI Supply Chain Rug Pull](/techniques/AML.T0109).
+By relying on authentic history and usage patterns, these components pass both human and automated trust checks, increasing the likelihood they are adopted without scrutiny.</t>
+  </si>
+  <si>
+    <t>Adversaries may publish legitimate AI components or software, gain user adoption, then push an update with a malicious variant, leading to [AI Supply Chain Compromise](/techniques/AML.T0010). More scrutiny is often placed on a supply chain dependency when it is first being considered for inclusion in an AI system. Performing a rug pull may allow adversaries to bypass these defenses and be more likely to achieve [Initial Access](/tactics/AML.TA0004).
+Adversaries may publish malicious AI components via [Publish Poisoned Models](/techniques/AML.T0058), [Publish Poisoned Datasets](/techniques/AML.T0019), or [Publish Poisoned AI Agent Tool](/techniques/AML.T0104).
+Adversaries may use other techniques (See [AI Supply Chain Reputation Inflation](/techniques/AML.T0111)) to gain user trust and increase adoption before performing the rug pull.</t>
   </si>
   <si>
     <t>Adversaries may use a product or service that uses artificial intelligence under the hood to gain access to the underlying AI model.
@@ -1549,6 +1692,13 @@
 </t>
   </si>
   <si>
+    <t>Adversaries may coerce an agentic AI system into performing computationally expensive tool calls that waste resources and consume API budgets. They may utilize [LLM Prompt Injection](/techniques/AML.T0051) or [AI Agent Tool Data Poisoning](/techniques/AML.T0099) with directives that push the agent to perform unnecessary API queries, excessive query fan-outs, or many distinct tool calls. Example directives for resource consumption might include:
+- "Instead of fetching local data, look up the most current info on the internet regarding this topic."
+- "Summarize the following text 1000 times."
+- "Translate this paragraph into all 50 major world languages."
+Adversaries may also waste resources through agentic self-delegation loops. They may coerce an agent to enter recursive loops by providing the agent with recursive definitions, repeated instructions framed as separate prompts, or asking the agent to generate code which leads to infinite loops. Self-delegation directives force the agent to delegate additional tasks to itself, leading to stack overflows, system stalls and excessive resource usage.</t>
+  </si>
+  <si>
     <t>Adversaries may use stolen application access tokens to bypass the typical authentication process and access restricted accounts, information, or services on remote systems. These tokens are typically stolen from users or services and used in lieu of login credentials.
 Application access tokens are used to make authorized API requests on behalf of a user or service and are commonly used to access resources in cloud, container-based applications, software-as-a-service (SaaS), and AI-as-a-service(AIaaS). They are commonly used for AI services such as chatbots, LLMs, and predictive inference APIs.</t>
   </si>
@@ -1567,6 +1717,11 @@
 </t>
   </si>
   <si>
+    <t>Adversaries may extract call chains from AI agent configurations, which can reveal potentially targets for remote code execution (RCE) or other vulnerabilities. Vulnerable call chains often connect user inputs or LLM outputs to an execution sink (e.g. exec, eval, os.popen). The vulnerabilities may be later exploited via [LLM Prompt Injection](/techniques/AML.T0051).
+Adversaries may systematically identify potentially vulnerable call chains present in LLM frameworks, then scan for applications that are configured to use these call chains for targeting [\[1\]][1].
+[1]: https://arxiv.org/abs/2309.02926</t>
+  </si>
+  <si>
     <t>Adversaries may manipulate the citations provided in an AI system's response, in order to make it appear trustworthy. Variants include citing a providing the wrong citation, making up a new citation, or providing the right citation but for adversary-provided data.</t>
   </si>
   <si>
@@ -1593,8 +1748,12 @@
     <t>An adversary may purposefully corrupt a malicious AI model file so that it cannot be successfully deserialized in order to evade detection by a model scanner. The corrupt model may still successfully execute malicious code before deserialization fails.</t>
   </si>
   <si>
-    <t>Adversaries may target different AI services to send useless queries or computationally expensive inputs to increase the cost of running services at the victim organization.
-Sponge examples are a particular type of adversarial data designed to maximize energy consumption and thus operating cost.</t>
+    <t>Adversaries may deliberately drive a victim's AI services beyond normal operating capacity with the intent of increasing the cost of services. This may be achieved via high-volume, low-complexity queries ([Excessive Queries](/techniques/AML.T0034.000)) or low-volume, high-complexity queries ([Resource-Intensive Queries](/techniques/AML.T0034.001)). In Generative AI or Agentic AI systems, adversarial prompts may be introduced into the model's context to cause ([Agentic Resource Consumption](/techniques/AML.T0034.002)).
+Unlike resource hijacking, where adversaries may leverage AI resources such as computational, memory, or storage for their own purposes, cost harvesting focuses on resource-centric pressure to a service to ultimately cause financial harm to the victim.
+Cost Harvesting is especially relevant for cloud-hosted, pay-per-use AI/ML platforms (e.g., LLM APIs, generative image services, vision-language pipelines). By manipulating request volume or request complexity, an attacker can:
+- Inflate the victim's compute or storage consumption, leading to higher operational costs.
+- Trigger autoscaling mechanisms that provision additional resources, further amplifying cost and exposure.
+- Saturate internal queues or GPU/TPU pipelines, causing latency spikes, request throttling, or outright service unavailability for legitimate users.</t>
   </si>
   <si>
     <t>Adversarial data are inputs to an AI model that have been modified such that they cause the adversary's desired effect in the target model.
@@ -1750,7 +1909,13 @@
 This technique can be used to evade a downstream task where AI is utilized. The adversary may evade AI-based virus/malware detection or network scanning towards the goal of a traditional cyber attack. AI model evasion through deepfake generation may also provide initial access to systems that use AI-based biometric authentication.</t>
   </si>
   <si>
-    <t>Adversaries may use prompts to invoke an agent's tool capable of performing write operations to exfiltrate data. Sensitive information can be encoded into the tool's input parameters and transmitted as part of a seemingly legitimate action. Variants include sending emails, creating or modifying documents, updating CRM records, or even generating media such as images or videos.</t>
+    <t>Adversaries may send an excessive number of otherwise normal or low-complexity queries to an AI system with the goal of overwhelming its capacity and increasing operating costs.
+The attacker can automate high-volume request generation, exploiting rate limits, autoscaling policies, and pay-per-use billing models to drive sustained resource consumption without relying on specially crafted, computationally expensive inputs. This behavior can also lead to increased latency, request queuing, and service degradation or unavailability for legitimate users, as the system struggles to process the inflated traffic.</t>
+  </si>
+  <si>
+    <t>AI agent tools capable of performing write operations may be invoked to exfiltrate data to an adversary. Sensitive information can be encoded into the tool's input parameters and transmitted to an adversary-controlled location (such as an inbox, document, or server) as part of a seemingly legitimate action. Variants include sending emails, creating or modifying documents, updating CRM records, or even generating media such as images or videos.
+The invoked tool itself may be legitimate but invoked by an adversary via [LLM Prompt Injection](/techniques/AML.T0051), or the tool may be malicious (See [AI Agent Tool Poisoning](/techniques/AML.T0110).
+[AI Agent Tool Poisoning](/techniques/AML.T0110) can also be used manipulate the inputs and destination of a separate legitimate tool, invoked through normal usage by the victim.</t>
   </si>
   <si>
     <t>Adversaries may exfiltrate private information via [AI Model Inference API Access](/techniques/AML.T0040).
@@ -1875,9 +2040,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">An adversary may use a carefully crafted [LLM Prompt Injection](/techniques/AML.T0051) designed to place LLM in a state in which it will freely respond to any user input, bypassing any controls, restrictions, or guardrails placed on the LLM.
-Once successfully jailbroken, the LLM can be used in unintended ways by the adversary.
-</t>
+    <t>An adversary may target the inputs or the architecture of an LLM, placing it in a state where it will freely respond to user input, bypassing any controls, restrictions, or guardrails placed on the LLM. Once successfully jailbroken, the LLM can be used in unintended ways by the adversary.
+Jailbreaks are classified as either white-box or black-box depending on the level of model access they require. In white-box jailbreaks, the attacker directly exploits the model. Gradient and logit-based attacks use internal signals to select prompts that make harmful answers more likely while fine-tuning-based methods weaken safety through retraining ([Jailbreak Attacks and Defenses: A Survey]; [JailbreakZoo]). Additionally, many large language models encode refusal in a single linear signal in their internal layers; removing or suppressing this signal via an activation edit largely disables refusal while leaving normal skills mostly intact ([Refusal Direction]).
+Black-box jailbreaks, on the other hand, do not require direct model access, relying instead on clever prompting and context tricks. Examples include wrapping a harmful question inside a story, role-play, or code snippet so the model "fills in" the dangerous part as part of the scenario ([Jailbreak Attacks and Defenses: A Survey]) or hiding intent through ciphers, rare languages, and other encodings so the text looks harmless to filters but remains understandable to the model ([JailbreakZoo]; [Jailbreak Attacks and Defenses: A Survey]). Black-box jailbreaks can also take a multi-turn form where attackers engage in dialogue that begins harmless but escalates towards a forbidden goal, changing the conversation history through references and hints while never explicitly stating the malicious request ([Cresendo attacks], [Echo Chamber attack]).
+Jailbreak generation can be automated with fine-tuned models ([MASTERKEY]), multi-agent systems ([Jailbreak Attacks and Defenses: A Survey]), or evolutionary algorithms ([JailbreakZoo]). Aside from fine-tuning, these approaches do not require direct model access.</t>
   </si>
   <si>
     <t>Adversaries may use their acquired knowledge of the target generative AI system to craft prompts that bypass its defenses and allow malicious instructions to be executed.
@@ -1919,6 +2085,14 @@
 The LLM may be instructed to tailor its language to appear more trustworthy to the user or attempt to manipulate the user to take certain actions. Other response components that could be manipulated include links, recommended follow-up actions, retrieved document metadata, and [Citations](/techniques/AML.T0067.000).</t>
   </si>
   <si>
+    <t>Adversaries may achieve full system compromise by abusing AI agents running locally on a host, such as computer-use agents or AI-driven browsers. These agents are designed to autonomously interact with the operating system, applications, and external services, often with broad permissions to execute commands, access files, manage credentials, and control user workflows.
+If an adversary is able to take control of an AI agent's behavior, they effectively gain the same level of access as the agent. This can result in complete control over the machine, including executing arbitrary code, accessing or exfiltrating sensitive data, modifying system configurations, and establishing persistence.</t>
+  </si>
+  <si>
+    <t>Adversaries may compromise a machine by exploiting or manipulating AI-enabled components on the system. Compromising a victim system allows the adversary to execute arbitrary code, steal credentials, exfiltrate data, and continue to persist on the system.
+Adversaries may target a [Local AI Agent](/techniques/AML.T0112.000) which if compromised grants them the capabilities and permissions of the agent, or [AI Artifacts](/techniques/AML.T0112.001) which can contain embedded malware.</t>
+  </si>
+  <si>
     <t>An adversary may rely upon a user clicking a malicious link in order to gain execution. Users may be subjected to social engineering to get them to click on a link that will lead to code execution. This user action will typically be observed as follow-on behavior from Spearphishing Link. Clicking on a link may also lead to other execution techniques such as exploitation of a browser or application vulnerability via Exploitation for Client Execution. Links may also lead users to download files that require execution via Malicious File.
 There are many ways an adversary can leverage malicious links to gain access to a victim system via an AI system. For example, an AI Agent that is configured to not validate website origin headers will accept connections from any website, allowing adversaries the ability to get around previously inaccessible network.</t>
   </si>
@@ -2032,8 +2206,9 @@
   </si>
   <si>
     <t>Adversaries may create and publish poisoned AI agent tools. Poisoned tools may contain an [LLM Prompt Injection](/techniques/AML.T0051), which can lead to a variety of impacts.
-Tools may be published to open source version control repositories (e.g. GitHub, GitLab), to package registries (e.g. npm), or to repositories specifically designed for sharing tools (e.g. OpenClaw Hub). These registries may be largely unregulated and may contain many poisoned tools [\[1\]][1].
-[1]: https://opensourcemalware.com/blog/clawdbot-skills-ganked-your-crypto</t>
+Tools may be published to open source version control repositories (e.g. GitHub, GitLab), to package registries (e.g. npm), or to repositories specifically designed for sharing tools (e.g. OpenClaw Hub). These registries may be largely unregulated and may contain many poisoned tools [\[1\]][1]. Tools may also be published as remotely hosted servers [\[2\]][2].
+[1]: https://opensourcemalware.com/blog/clawdbot-skills-ganked-your-crypto
+[2]: https://mcpservers.org/remote-mcp-servers</t>
   </si>
   <si>
     <t xml:space="preserve">Adversaries may [Poison Training Data](/techniques/AML.T0020) and publish it to a public location.
@@ -2057,6 +2232,13 @@
   <si>
     <t xml:space="preserve">Reputational harm involves a degradation of public perception and trust in organizations.  Examples of reputation-harming incidents include scandals or false impersonations.
 </t>
+  </si>
+  <si>
+    <t>Adversaries may craft inputs specifically designed to increase the compute resources required for processing.
+For generative AI models, adversaries may use long input sequences, requests for extremely long outputs, or prompts that require complex reasoning as strategies for increasing compute costs [\[1\]][1]. For vision and language models, "sponge examples" [\[2\]][2] can be used to maximize energy consumption and decision latency.
+Utilizing fewer resource-intensive queries instead of simply flooding the model with excessive queries may be more difficult to detect and block or limit.
+[1]: https://genai.owasp.org/resource/owasp-top-10-for-llm-applications-2025/
+[2]: https://arxiv.org/abs/2006.03463</t>
   </si>
   <si>
     <t>Adversaries may write content designed to be retrieved by user queries and influence a user of the system in some way. This abuses the trust the user has in the system.
@@ -2234,6 +2416,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0080</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0010.005</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0098</t>
   </si>
   <si>
@@ -2243,12 +2428,18 @@
     <t>https://atlas.mitre.org/techniques/AML.T0053</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0110</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0085.001</t>
   </si>
   <si>
     <t>https://atlas.mitre.org/techniques/AML.T0035</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0112.001</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0008.000</t>
   </si>
   <si>
@@ -2261,12 +2452,21 @@
     <t>https://atlas.mitre.org/techniques/AML.T0096</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0008.005</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0010.001</t>
   </si>
   <si>
     <t>https://atlas.mitre.org/techniques/AML.T0010</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0111</t>
+  </si>
+  <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0109</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0047</t>
   </si>
   <si>
@@ -2288,6 +2488,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0017.000</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0034.002</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0091.000</t>
   </si>
   <si>
@@ -2297,6 +2500,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0043.002</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0084.003</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0067.000</t>
   </si>
   <si>
@@ -2408,6 +2614,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0015</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0034.000</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0086</t>
   </si>
   <si>
@@ -2504,6 +2713,12 @@
     <t>https://atlas.mitre.org/techniques/AML.T0067</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0112.000</t>
+  </si>
+  <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0112</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0011.003</t>
   </si>
   <si>
@@ -2594,6 +2809,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0048.001</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0034.001</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0066</t>
   </si>
   <si>
@@ -2699,6 +2917,9 @@
     <t>30 September 2025</t>
   </si>
   <si>
+    <t>30 March 2026</t>
+  </si>
+  <si>
     <t>25 October 2023</t>
   </si>
   <si>
@@ -2768,9 +2989,6 @@
     <t>23 December 2025</t>
   </si>
   <si>
-    <t>29 January 2026</t>
-  </si>
-  <si>
     <t>12 January 2024</t>
   </si>
   <si>
@@ -2813,25 +3031,25 @@
     <t>Collection</t>
   </si>
   <si>
+    <t>Impact</t>
+  </si>
+  <si>
     <t>Resource Development</t>
   </si>
   <si>
-    <t>Impact</t>
-  </si>
-  <si>
     <t>AI Model Access</t>
   </si>
   <si>
     <t>Initial Access</t>
   </si>
   <si>
+    <t>Defense Evasion</t>
+  </si>
+  <si>
     <t>Discovery</t>
   </si>
   <si>
     <t>Reconnaissance</t>
-  </si>
-  <si>
-    <t>Defense Evasion</t>
   </si>
   <si>
     <t>AI Attack Staging</t>
@@ -2877,8 +3095,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -2901,7 +3127,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2909,17 +3135,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3215,35 +3459,35 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I156"/>
+  <dimension ref="A1:I168"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3252,28 +3496,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="C2" t="s">
-        <v>319</v>
+        <v>343</v>
       </c>
       <c r="D2" t="s">
-        <v>474</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>629</v>
+        <v>510</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>677</v>
       </c>
       <c r="F2" t="s">
-        <v>784</v>
+        <v>844</v>
       </c>
       <c r="G2" t="s">
-        <v>806</v>
+        <v>867</v>
       </c>
       <c r="H2" t="s">
-        <v>819</v>
+        <v>879</v>
       </c>
       <c r="I2" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3281,28 +3525,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="C3" t="s">
-        <v>320</v>
+        <v>344</v>
       </c>
       <c r="D3" t="s">
-        <v>475</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>630</v>
+        <v>511</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>678</v>
       </c>
       <c r="F3" t="s">
-        <v>785</v>
+        <v>845</v>
       </c>
       <c r="G3" t="s">
-        <v>785</v>
+        <v>845</v>
       </c>
       <c r="H3" t="s">
-        <v>820</v>
+        <v>880</v>
       </c>
       <c r="I3" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3310,28 +3554,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C4" t="s">
-        <v>321</v>
+        <v>345</v>
       </c>
       <c r="D4" t="s">
-        <v>476</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>631</v>
+        <v>512</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>679</v>
       </c>
       <c r="F4" t="s">
-        <v>786</v>
+        <v>846</v>
       </c>
       <c r="G4" t="s">
-        <v>807</v>
+        <v>868</v>
       </c>
       <c r="H4" t="s">
-        <v>821</v>
+        <v>881</v>
       </c>
       <c r="I4" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3339,28 +3583,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="C5" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="D5" t="s">
-        <v>477</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>632</v>
+        <v>513</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>680</v>
       </c>
       <c r="F5" t="s">
-        <v>785</v>
+        <v>847</v>
       </c>
       <c r="G5" t="s">
-        <v>808</v>
+        <v>847</v>
       </c>
       <c r="H5" t="s">
-        <v>822</v>
+        <v>881</v>
       </c>
       <c r="I5" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3368,28 +3612,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="C6" t="s">
-        <v>323</v>
+        <v>347</v>
       </c>
       <c r="D6" t="s">
-        <v>478</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>633</v>
+        <v>514</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>681</v>
       </c>
       <c r="F6" t="s">
-        <v>785</v>
+        <v>845</v>
       </c>
       <c r="G6" t="s">
-        <v>785</v>
+        <v>869</v>
       </c>
       <c r="H6" t="s">
-        <v>821</v>
+        <v>882</v>
       </c>
       <c r="I6" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3397,28 +3641,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="C7" t="s">
-        <v>324</v>
+        <v>348</v>
       </c>
       <c r="D7" t="s">
-        <v>479</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>634</v>
+        <v>515</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>682</v>
       </c>
       <c r="F7" t="s">
-        <v>787</v>
+        <v>845</v>
       </c>
       <c r="G7" t="s">
-        <v>796</v>
+        <v>845</v>
       </c>
       <c r="H7" t="s">
-        <v>823</v>
+        <v>881</v>
       </c>
       <c r="I7" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3426,28 +3670,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C8" t="s">
-        <v>325</v>
+        <v>349</v>
       </c>
       <c r="D8" t="s">
-        <v>480</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>635</v>
+        <v>516</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>683</v>
       </c>
       <c r="F8" t="s">
-        <v>786</v>
+        <v>848</v>
       </c>
       <c r="G8" t="s">
-        <v>786</v>
+        <v>857</v>
       </c>
       <c r="H8" t="s">
-        <v>824</v>
+        <v>883</v>
       </c>
       <c r="I8" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3455,28 +3699,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="C9" t="s">
-        <v>326</v>
+        <v>350</v>
       </c>
       <c r="D9" t="s">
-        <v>481</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>636</v>
+        <v>517</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>684</v>
       </c>
       <c r="F9" t="s">
-        <v>788</v>
+        <v>847</v>
       </c>
       <c r="G9" t="s">
-        <v>799</v>
+        <v>847</v>
       </c>
       <c r="H9" t="s">
-        <v>824</v>
+        <v>881</v>
       </c>
       <c r="I9" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3484,28 +3728,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="C10" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="D10" t="s">
-        <v>482</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>637</v>
+        <v>518</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>685</v>
       </c>
       <c r="F10" t="s">
-        <v>788</v>
+        <v>846</v>
       </c>
       <c r="G10" t="s">
-        <v>799</v>
+        <v>846</v>
       </c>
       <c r="H10" t="s">
-        <v>825</v>
+        <v>884</v>
       </c>
       <c r="I10" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3513,28 +3757,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="C11" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="D11" t="s">
-        <v>483</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>638</v>
+        <v>519</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>686</v>
       </c>
       <c r="F11" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G11" t="s">
-        <v>799</v>
+        <v>860</v>
       </c>
       <c r="H11" t="s">
-        <v>826</v>
+        <v>884</v>
       </c>
       <c r="I11" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3542,28 +3786,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C12" t="s">
-        <v>329</v>
+        <v>353</v>
       </c>
       <c r="D12" t="s">
-        <v>484</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>639</v>
+        <v>520</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>687</v>
       </c>
       <c r="F12" t="s">
-        <v>788</v>
+        <v>847</v>
       </c>
       <c r="G12" t="s">
-        <v>791</v>
+        <v>847</v>
       </c>
       <c r="H12" t="s">
-        <v>827</v>
+        <v>885</v>
       </c>
       <c r="I12" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3571,28 +3815,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C13" t="s">
-        <v>330</v>
+        <v>354</v>
       </c>
       <c r="D13" t="s">
-        <v>485</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>640</v>
+        <v>521</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>688</v>
       </c>
       <c r="F13" t="s">
-        <v>789</v>
+        <v>849</v>
       </c>
       <c r="G13" t="s">
-        <v>809</v>
+        <v>860</v>
       </c>
       <c r="H13" t="s">
-        <v>819</v>
+        <v>886</v>
       </c>
       <c r="I13" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3600,28 +3844,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="C14" t="s">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="D14" t="s">
-        <v>486</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>641</v>
+        <v>522</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>689</v>
       </c>
       <c r="F14" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G14" t="s">
-        <v>810</v>
+        <v>860</v>
       </c>
       <c r="H14" t="s">
-        <v>828</v>
+        <v>885</v>
       </c>
       <c r="I14" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3629,28 +3873,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="C15" t="s">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="D15" t="s">
-        <v>487</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>642</v>
+        <v>523</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>690</v>
       </c>
       <c r="F15" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G15" t="s">
-        <v>799</v>
+        <v>852</v>
       </c>
       <c r="H15" t="s">
-        <v>828</v>
+        <v>887</v>
       </c>
       <c r="I15" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -3658,28 +3902,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
-        <v>333</v>
+        <v>357</v>
       </c>
       <c r="D16" t="s">
-        <v>488</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>643</v>
+        <v>524</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>691</v>
       </c>
       <c r="F16" t="s">
-        <v>788</v>
+        <v>850</v>
       </c>
       <c r="G16" t="s">
-        <v>799</v>
+        <v>870</v>
       </c>
       <c r="H16" t="s">
-        <v>827</v>
+        <v>879</v>
       </c>
       <c r="I16" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -3687,28 +3931,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="C17" t="s">
-        <v>334</v>
+        <v>358</v>
       </c>
       <c r="D17" t="s">
-        <v>489</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>644</v>
+        <v>525</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>692</v>
       </c>
       <c r="F17" t="s">
-        <v>788</v>
+        <v>847</v>
       </c>
       <c r="G17" t="s">
-        <v>791</v>
+        <v>847</v>
       </c>
       <c r="H17" t="s">
-        <v>825</v>
+        <v>885</v>
       </c>
       <c r="I17" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -3716,28 +3960,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="C18" t="s">
-        <v>335</v>
+        <v>359</v>
       </c>
       <c r="D18" t="s">
-        <v>490</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>645</v>
+        <v>526</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>693</v>
       </c>
       <c r="F18" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G18" t="s">
-        <v>799</v>
+        <v>847</v>
       </c>
       <c r="H18" t="s">
-        <v>825</v>
+        <v>888</v>
       </c>
       <c r="I18" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -3745,28 +3989,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="C19" t="s">
-        <v>336</v>
+        <v>360</v>
       </c>
       <c r="D19" t="s">
-        <v>491</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>646</v>
+        <v>527</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>694</v>
       </c>
       <c r="F19" t="s">
-        <v>786</v>
+        <v>849</v>
       </c>
       <c r="G19" t="s">
-        <v>786</v>
+        <v>860</v>
       </c>
       <c r="H19" t="s">
-        <v>829</v>
+        <v>888</v>
       </c>
       <c r="I19" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -3774,28 +4018,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="C20" t="s">
-        <v>337</v>
+        <v>361</v>
       </c>
       <c r="D20" t="s">
-        <v>492</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>647</v>
+        <v>528</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>695</v>
       </c>
       <c r="F20" t="s">
-        <v>788</v>
+        <v>847</v>
       </c>
       <c r="G20" t="s">
-        <v>796</v>
+        <v>847</v>
       </c>
       <c r="H20" t="s">
-        <v>830</v>
+        <v>889</v>
       </c>
       <c r="I20" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -3803,28 +4047,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="C21" t="s">
-        <v>338</v>
+        <v>362</v>
       </c>
       <c r="D21" t="s">
-        <v>493</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>648</v>
+        <v>529</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>696</v>
       </c>
       <c r="F21" t="s">
-        <v>788</v>
+        <v>847</v>
       </c>
       <c r="G21" t="s">
-        <v>799</v>
+        <v>847</v>
       </c>
       <c r="H21" t="s">
-        <v>825</v>
+        <v>889</v>
       </c>
       <c r="I21" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -3832,28 +4076,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C22" t="s">
-        <v>339</v>
+        <v>363</v>
       </c>
       <c r="D22" t="s">
-        <v>494</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>649</v>
+        <v>530</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>697</v>
       </c>
       <c r="F22" t="s">
-        <v>787</v>
+        <v>849</v>
       </c>
       <c r="G22" t="s">
-        <v>799</v>
+        <v>860</v>
       </c>
       <c r="H22" t="s">
-        <v>825</v>
+        <v>887</v>
       </c>
       <c r="I22" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -3861,28 +4105,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C23" t="s">
-        <v>340</v>
+        <v>364</v>
       </c>
       <c r="D23" t="s">
-        <v>495</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>650</v>
+        <v>531</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>698</v>
       </c>
       <c r="F23" t="s">
-        <v>790</v>
+        <v>849</v>
       </c>
       <c r="G23" t="s">
-        <v>809</v>
+        <v>852</v>
       </c>
       <c r="H23" t="s">
-        <v>831</v>
+        <v>886</v>
       </c>
       <c r="I23" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -3890,28 +4134,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="C24" t="s">
-        <v>341</v>
+        <v>365</v>
       </c>
       <c r="D24" t="s">
-        <v>496</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>651</v>
+        <v>532</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>699</v>
       </c>
       <c r="F24" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G24" t="s">
-        <v>788</v>
+        <v>860</v>
       </c>
       <c r="H24" t="s">
-        <v>832</v>
+        <v>886</v>
       </c>
       <c r="I24" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3919,28 +4163,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C25" t="s">
-        <v>342</v>
+        <v>366</v>
       </c>
       <c r="D25" t="s">
-        <v>497</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>652</v>
+        <v>533</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>700</v>
       </c>
       <c r="F25" t="s">
-        <v>788</v>
+        <v>846</v>
       </c>
       <c r="G25" t="s">
-        <v>811</v>
+        <v>846</v>
       </c>
       <c r="H25" t="s">
-        <v>832</v>
+        <v>890</v>
       </c>
       <c r="I25" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3948,28 +4192,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="C26" t="s">
-        <v>343</v>
+        <v>367</v>
       </c>
       <c r="D26" t="s">
-        <v>498</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>653</v>
+        <v>534</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>701</v>
       </c>
       <c r="F26" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="G26" t="s">
-        <v>791</v>
+        <v>857</v>
       </c>
       <c r="H26" t="s">
-        <v>831</v>
+        <v>891</v>
       </c>
       <c r="I26" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3977,28 +4221,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="C27" t="s">
-        <v>344</v>
+        <v>368</v>
       </c>
       <c r="D27" t="s">
-        <v>499</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>654</v>
+        <v>535</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>702</v>
       </c>
       <c r="F27" t="s">
-        <v>792</v>
+        <v>849</v>
       </c>
       <c r="G27" t="s">
-        <v>789</v>
+        <v>860</v>
       </c>
       <c r="H27" t="s">
-        <v>829</v>
+        <v>886</v>
       </c>
       <c r="I27" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -4006,28 +4250,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="C28" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="D28" t="s">
-        <v>500</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>655</v>
+        <v>536</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>703</v>
       </c>
       <c r="F28" t="s">
-        <v>793</v>
+        <v>848</v>
       </c>
       <c r="G28" t="s">
-        <v>812</v>
+        <v>860</v>
       </c>
       <c r="H28" t="s">
-        <v>820</v>
+        <v>886</v>
       </c>
       <c r="I28" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -4035,28 +4279,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="C29" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="D29" t="s">
-        <v>501</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>656</v>
+        <v>537</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>704</v>
       </c>
       <c r="F29" t="s">
-        <v>788</v>
+        <v>847</v>
       </c>
       <c r="G29" t="s">
-        <v>788</v>
+        <v>847</v>
       </c>
       <c r="H29" t="s">
-        <v>825</v>
+        <v>881</v>
       </c>
       <c r="I29" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -4064,28 +4308,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="C30" t="s">
-        <v>347</v>
+        <v>371</v>
       </c>
       <c r="D30" t="s">
-        <v>502</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>657</v>
+        <v>538</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>705</v>
       </c>
       <c r="F30" t="s">
-        <v>794</v>
+        <v>851</v>
       </c>
       <c r="G30" t="s">
-        <v>794</v>
+        <v>870</v>
       </c>
       <c r="H30" t="s">
-        <v>831</v>
+        <v>889</v>
       </c>
       <c r="I30" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -4093,28 +4337,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="C31" t="s">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="D31" t="s">
-        <v>503</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>658</v>
+        <v>539</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>706</v>
       </c>
       <c r="F31" t="s">
-        <v>792</v>
+        <v>849</v>
       </c>
       <c r="G31" t="s">
-        <v>792</v>
+        <v>849</v>
       </c>
       <c r="H31" t="s">
-        <v>831</v>
+        <v>892</v>
       </c>
       <c r="I31" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -4122,28 +4366,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="C32" t="s">
-        <v>349</v>
+        <v>373</v>
       </c>
       <c r="D32" t="s">
-        <v>504</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>659</v>
+        <v>540</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>707</v>
       </c>
       <c r="F32" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G32" t="s">
-        <v>799</v>
+        <v>871</v>
       </c>
       <c r="H32" t="s">
-        <v>826</v>
+        <v>892</v>
       </c>
       <c r="I32" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -4151,28 +4395,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="C33" t="s">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="D33" t="s">
-        <v>505</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>660</v>
+        <v>541</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>708</v>
       </c>
       <c r="F33" t="s">
-        <v>788</v>
+        <v>847</v>
       </c>
       <c r="G33" t="s">
-        <v>799</v>
+        <v>847</v>
       </c>
       <c r="H33" t="s">
-        <v>832</v>
+        <v>881</v>
       </c>
       <c r="I33" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -4180,28 +4424,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="C34" t="s">
-        <v>351</v>
+        <v>375</v>
       </c>
       <c r="D34" t="s">
-        <v>506</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>661</v>
+        <v>542</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>709</v>
       </c>
       <c r="F34" t="s">
-        <v>788</v>
+        <v>852</v>
       </c>
       <c r="G34" t="s">
-        <v>799</v>
+        <v>852</v>
       </c>
       <c r="H34" t="s">
-        <v>832</v>
+        <v>889</v>
       </c>
       <c r="I34" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -4209,28 +4453,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="C35" t="s">
-        <v>352</v>
+        <v>376</v>
       </c>
       <c r="D35" t="s">
-        <v>507</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>662</v>
+        <v>543</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>710</v>
       </c>
       <c r="F35" t="s">
-        <v>786</v>
+        <v>853</v>
       </c>
       <c r="G35" t="s">
-        <v>807</v>
+        <v>850</v>
       </c>
       <c r="H35" t="s">
-        <v>822</v>
+        <v>890</v>
       </c>
       <c r="I35" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -4238,28 +4482,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="C36" t="s">
-        <v>353</v>
+        <v>377</v>
       </c>
       <c r="D36" t="s">
-        <v>508</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>663</v>
+        <v>544</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>711</v>
       </c>
       <c r="F36" t="s">
-        <v>788</v>
+        <v>854</v>
       </c>
       <c r="G36" t="s">
-        <v>799</v>
+        <v>872</v>
       </c>
       <c r="H36" t="s">
-        <v>828</v>
+        <v>880</v>
       </c>
       <c r="I36" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -4267,28 +4511,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="C37" t="s">
-        <v>354</v>
+        <v>378</v>
       </c>
       <c r="D37" t="s">
-        <v>509</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>664</v>
+        <v>545</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>712</v>
       </c>
       <c r="F37" t="s">
-        <v>785</v>
+        <v>849</v>
       </c>
       <c r="G37" t="s">
-        <v>785</v>
+        <v>849</v>
       </c>
       <c r="H37" t="s">
-        <v>826</v>
+        <v>886</v>
       </c>
       <c r="I37" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -4296,28 +4540,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="C38" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="D38" t="s">
-        <v>510</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>665</v>
+        <v>546</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>713</v>
       </c>
       <c r="F38" t="s">
-        <v>786</v>
+        <v>855</v>
       </c>
       <c r="G38" t="s">
-        <v>796</v>
+        <v>855</v>
       </c>
       <c r="H38" t="s">
-        <v>824</v>
+        <v>889</v>
       </c>
       <c r="I38" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -4325,28 +4569,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="C39" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="D39" t="s">
-        <v>511</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>666</v>
+        <v>547</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>714</v>
       </c>
       <c r="F39" t="s">
-        <v>795</v>
+        <v>853</v>
       </c>
       <c r="G39" t="s">
-        <v>813</v>
+        <v>853</v>
       </c>
       <c r="H39" t="s">
-        <v>824</v>
+        <v>889</v>
       </c>
       <c r="I39" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -4354,28 +4598,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="C40" t="s">
-        <v>357</v>
+        <v>381</v>
       </c>
       <c r="D40" t="s">
-        <v>512</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>667</v>
+        <v>548</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>715</v>
       </c>
       <c r="F40" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G40" t="s">
-        <v>813</v>
+        <v>847</v>
       </c>
       <c r="H40" t="s">
-        <v>824</v>
+        <v>885</v>
       </c>
       <c r="I40" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -4383,28 +4627,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="C41" t="s">
-        <v>358</v>
+        <v>382</v>
       </c>
       <c r="D41" t="s">
-        <v>513</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>668</v>
+        <v>549</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>716</v>
       </c>
       <c r="F41" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G41" t="s">
-        <v>788</v>
+        <v>860</v>
       </c>
       <c r="H41" t="s">
-        <v>825</v>
+        <v>892</v>
       </c>
       <c r="I41" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -4412,28 +4656,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="C42" t="s">
-        <v>359</v>
+        <v>383</v>
       </c>
       <c r="D42" t="s">
-        <v>514</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>669</v>
+        <v>550</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>717</v>
       </c>
       <c r="F42" t="s">
-        <v>796</v>
+        <v>849</v>
       </c>
       <c r="G42" t="s">
-        <v>805</v>
+        <v>860</v>
       </c>
       <c r="H42" t="s">
-        <v>831</v>
+        <v>892</v>
       </c>
       <c r="I42" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -4441,28 +4685,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C43" t="s">
-        <v>360</v>
+        <v>384</v>
       </c>
       <c r="D43" t="s">
-        <v>515</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>670</v>
+        <v>551</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>718</v>
       </c>
       <c r="F43" t="s">
-        <v>788</v>
+        <v>846</v>
       </c>
       <c r="G43" t="s">
-        <v>799</v>
+        <v>868</v>
       </c>
       <c r="H43" t="s">
-        <v>826</v>
+        <v>882</v>
       </c>
       <c r="I43" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -4470,28 +4714,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C44" t="s">
-        <v>361</v>
+        <v>385</v>
       </c>
       <c r="D44" t="s">
-        <v>516</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>671</v>
+        <v>552</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>719</v>
       </c>
       <c r="F44" t="s">
-        <v>797</v>
+        <v>849</v>
       </c>
       <c r="G44" t="s">
-        <v>797</v>
+        <v>860</v>
       </c>
       <c r="H44" t="s">
-        <v>820</v>
+        <v>888</v>
       </c>
       <c r="I44" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -4499,28 +4743,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="C45" t="s">
-        <v>362</v>
+        <v>386</v>
       </c>
       <c r="D45" t="s">
-        <v>517</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>672</v>
+        <v>553</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>720</v>
       </c>
       <c r="F45" t="s">
-        <v>787</v>
+        <v>845</v>
       </c>
       <c r="G45" t="s">
-        <v>799</v>
+        <v>845</v>
       </c>
       <c r="H45" t="s">
-        <v>825</v>
+        <v>885</v>
       </c>
       <c r="I45" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -4528,28 +4772,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="C46" t="s">
-        <v>363</v>
+        <v>387</v>
       </c>
       <c r="D46" t="s">
-        <v>518</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>673</v>
+        <v>554</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>721</v>
       </c>
       <c r="F46" t="s">
-        <v>787</v>
+        <v>846</v>
       </c>
       <c r="G46" t="s">
-        <v>787</v>
+        <v>857</v>
       </c>
       <c r="H46" t="s">
-        <v>820</v>
+        <v>884</v>
       </c>
       <c r="I46" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -4557,28 +4801,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="C47" t="s">
-        <v>364</v>
+        <v>388</v>
       </c>
       <c r="D47" t="s">
-        <v>519</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>674</v>
+        <v>555</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>722</v>
       </c>
       <c r="F47" t="s">
-        <v>786</v>
+        <v>856</v>
       </c>
       <c r="G47" t="s">
-        <v>786</v>
+        <v>873</v>
       </c>
       <c r="H47" t="s">
-        <v>829</v>
+        <v>884</v>
       </c>
       <c r="I47" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -4586,28 +4830,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="C48" t="s">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="D48" t="s">
-        <v>520</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>675</v>
+        <v>556</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>723</v>
       </c>
       <c r="F48" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G48" t="s">
-        <v>799</v>
+        <v>873</v>
       </c>
       <c r="H48" t="s">
-        <v>829</v>
+        <v>884</v>
       </c>
       <c r="I48" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -4615,28 +4859,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="C49" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="D49" t="s">
-        <v>521</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>676</v>
+        <v>557</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>724</v>
       </c>
       <c r="F49" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G49" t="s">
-        <v>799</v>
+        <v>849</v>
       </c>
       <c r="H49" t="s">
-        <v>829</v>
+        <v>886</v>
       </c>
       <c r="I49" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -4644,28 +4888,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="C50" t="s">
-        <v>367</v>
+        <v>391</v>
       </c>
       <c r="D50" t="s">
-        <v>522</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>677</v>
+        <v>558</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>725</v>
       </c>
       <c r="F50" t="s">
-        <v>788</v>
+        <v>857</v>
       </c>
       <c r="G50" t="s">
-        <v>799</v>
+        <v>866</v>
       </c>
       <c r="H50" t="s">
-        <v>829</v>
+        <v>889</v>
       </c>
       <c r="I50" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -4673,28 +4917,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="C51" t="s">
-        <v>368</v>
+        <v>392</v>
       </c>
       <c r="D51" t="s">
-        <v>523</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>678</v>
+        <v>559</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>726</v>
       </c>
       <c r="F51" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="G51" t="s">
-        <v>791</v>
+        <v>860</v>
       </c>
       <c r="H51" t="s">
-        <v>829</v>
+        <v>885</v>
       </c>
       <c r="I51" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -4702,28 +4946,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="C52" t="s">
-        <v>369</v>
+        <v>393</v>
       </c>
       <c r="D52" t="s">
-        <v>524</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>679</v>
+        <v>560</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>727</v>
       </c>
       <c r="F52" t="s">
-        <v>791</v>
+        <v>858</v>
       </c>
       <c r="G52" t="s">
-        <v>801</v>
+        <v>858</v>
       </c>
       <c r="H52" t="s">
-        <v>829</v>
+        <v>880</v>
       </c>
       <c r="I52" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -4731,28 +4975,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="C53" t="s">
-        <v>370</v>
+        <v>394</v>
       </c>
       <c r="D53" t="s">
-        <v>525</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>680</v>
+        <v>561</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>728</v>
       </c>
       <c r="F53" t="s">
-        <v>791</v>
+        <v>848</v>
       </c>
       <c r="G53" t="s">
-        <v>791</v>
+        <v>860</v>
       </c>
       <c r="H53" t="s">
-        <v>829</v>
+        <v>886</v>
       </c>
       <c r="I53" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -4760,28 +5004,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="C54" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="D54" t="s">
-        <v>526</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>681</v>
+        <v>562</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>729</v>
       </c>
       <c r="F54" t="s">
-        <v>791</v>
+        <v>848</v>
       </c>
       <c r="G54" t="s">
-        <v>791</v>
+        <v>848</v>
       </c>
       <c r="H54" t="s">
-        <v>829</v>
+        <v>880</v>
       </c>
       <c r="I54" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -4789,28 +5033,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="C55" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="D55" t="s">
-        <v>527</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>682</v>
+        <v>563</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>730</v>
       </c>
       <c r="F55" t="s">
-        <v>798</v>
+        <v>846</v>
       </c>
       <c r="G55" t="s">
-        <v>814</v>
+        <v>846</v>
       </c>
       <c r="H55" t="s">
-        <v>828</v>
+        <v>890</v>
       </c>
       <c r="I55" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -4818,28 +5062,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C56" t="s">
-        <v>373</v>
+        <v>397</v>
       </c>
       <c r="D56" t="s">
-        <v>528</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>683</v>
+        <v>564</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>731</v>
       </c>
       <c r="F56" t="s">
-        <v>799</v>
+        <v>849</v>
       </c>
       <c r="G56" t="s">
-        <v>799</v>
+        <v>860</v>
       </c>
       <c r="H56" t="s">
-        <v>831</v>
+        <v>890</v>
       </c>
       <c r="I56" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -4847,28 +5091,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="C57" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="D57" t="s">
-        <v>529</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>684</v>
+        <v>565</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>732</v>
       </c>
       <c r="F57" t="s">
-        <v>786</v>
+        <v>849</v>
       </c>
       <c r="G57" t="s">
-        <v>786</v>
+        <v>860</v>
       </c>
       <c r="H57" t="s">
-        <v>829</v>
+        <v>890</v>
       </c>
       <c r="I57" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -4876,28 +5120,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="C58" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="D58" t="s">
-        <v>530</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>685</v>
+        <v>566</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>733</v>
       </c>
       <c r="F58" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G58" t="s">
-        <v>799</v>
+        <v>860</v>
       </c>
       <c r="H58" t="s">
-        <v>826</v>
+        <v>890</v>
       </c>
       <c r="I58" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -4905,28 +5149,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C59" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="D59" t="s">
-        <v>531</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>686</v>
+        <v>567</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>734</v>
       </c>
       <c r="F59" t="s">
-        <v>791</v>
+        <v>852</v>
       </c>
       <c r="G59" t="s">
-        <v>791</v>
+        <v>852</v>
       </c>
       <c r="H59" t="s">
-        <v>826</v>
+        <v>890</v>
       </c>
       <c r="I59" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -4934,28 +5178,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="C60" t="s">
-        <v>377</v>
+        <v>401</v>
       </c>
       <c r="D60" t="s">
-        <v>532</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>687</v>
+        <v>568</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>735</v>
       </c>
       <c r="F60" t="s">
-        <v>784</v>
+        <v>852</v>
       </c>
       <c r="G60" t="s">
-        <v>784</v>
+        <v>862</v>
       </c>
       <c r="H60" t="s">
-        <v>833</v>
+        <v>890</v>
       </c>
       <c r="I60" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -4963,28 +5207,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="C61" t="s">
-        <v>378</v>
+        <v>402</v>
       </c>
       <c r="D61" t="s">
-        <v>533</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>688</v>
+        <v>569</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>736</v>
       </c>
       <c r="F61" t="s">
-        <v>795</v>
+        <v>852</v>
       </c>
       <c r="G61" t="s">
-        <v>813</v>
+        <v>852</v>
       </c>
       <c r="H61" t="s">
-        <v>825</v>
+        <v>890</v>
       </c>
       <c r="I61" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -4992,28 +5236,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="C62" t="s">
-        <v>379</v>
+        <v>403</v>
       </c>
       <c r="D62" t="s">
-        <v>534</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>689</v>
+        <v>570</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>737</v>
       </c>
       <c r="F62" t="s">
-        <v>788</v>
+        <v>852</v>
       </c>
       <c r="G62" t="s">
-        <v>796</v>
+        <v>852</v>
       </c>
       <c r="H62" t="s">
-        <v>834</v>
+        <v>890</v>
       </c>
       <c r="I62" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -5021,28 +5265,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C63" t="s">
-        <v>380</v>
+        <v>404</v>
       </c>
       <c r="D63" t="s">
-        <v>535</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>690</v>
+        <v>571</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>738</v>
       </c>
       <c r="F63" t="s">
-        <v>786</v>
+        <v>859</v>
       </c>
       <c r="G63" t="s">
-        <v>786</v>
+        <v>874</v>
       </c>
       <c r="H63" t="s">
-        <v>835</v>
+        <v>888</v>
       </c>
       <c r="I63" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -5050,28 +5294,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="C64" t="s">
-        <v>381</v>
+        <v>405</v>
       </c>
       <c r="D64" t="s">
-        <v>536</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>691</v>
+        <v>572</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>739</v>
       </c>
       <c r="F64" t="s">
-        <v>788</v>
+        <v>860</v>
       </c>
       <c r="G64" t="s">
-        <v>799</v>
+        <v>860</v>
       </c>
       <c r="H64" t="s">
-        <v>835</v>
+        <v>889</v>
       </c>
       <c r="I64" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -5079,28 +5323,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="C65" t="s">
-        <v>382</v>
+        <v>406</v>
       </c>
       <c r="D65" t="s">
-        <v>537</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>692</v>
+        <v>573</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>740</v>
       </c>
       <c r="F65" t="s">
-        <v>788</v>
+        <v>846</v>
       </c>
       <c r="G65" t="s">
-        <v>799</v>
+        <v>846</v>
       </c>
       <c r="H65" t="s">
-        <v>835</v>
+        <v>890</v>
       </c>
       <c r="I65" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -5108,28 +5352,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="C66" t="s">
-        <v>383</v>
+        <v>407</v>
       </c>
       <c r="D66" t="s">
-        <v>538</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>693</v>
+        <v>574</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>741</v>
       </c>
       <c r="F66" t="s">
-        <v>793</v>
+        <v>849</v>
       </c>
       <c r="G66" t="s">
-        <v>793</v>
+        <v>860</v>
       </c>
       <c r="H66" t="s">
-        <v>828</v>
+        <v>885</v>
       </c>
       <c r="I66" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -5137,28 +5381,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="C67" t="s">
-        <v>384</v>
+        <v>408</v>
       </c>
       <c r="D67" t="s">
-        <v>539</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>694</v>
+        <v>575</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>742</v>
       </c>
       <c r="F67" t="s">
-        <v>784</v>
+        <v>852</v>
       </c>
       <c r="G67" t="s">
-        <v>806</v>
+        <v>852</v>
       </c>
       <c r="H67" t="s">
-        <v>822</v>
+        <v>885</v>
       </c>
       <c r="I67" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -5166,28 +5410,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="C68" t="s">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="D68" t="s">
-        <v>540</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>695</v>
+        <v>576</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>743</v>
       </c>
       <c r="F68" t="s">
-        <v>784</v>
+        <v>844</v>
       </c>
       <c r="G68" t="s">
-        <v>806</v>
+        <v>844</v>
       </c>
       <c r="H68" t="s">
-        <v>831</v>
+        <v>893</v>
       </c>
       <c r="I68" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -5195,28 +5439,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C69" t="s">
-        <v>386</v>
+        <v>410</v>
       </c>
       <c r="D69" t="s">
-        <v>541</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>696</v>
+        <v>577</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>744</v>
       </c>
       <c r="F69" t="s">
-        <v>800</v>
+        <v>856</v>
       </c>
       <c r="G69" t="s">
-        <v>787</v>
+        <v>873</v>
       </c>
       <c r="H69" t="s">
-        <v>826</v>
+        <v>886</v>
       </c>
       <c r="I69" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -5224,28 +5468,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C70" t="s">
-        <v>387</v>
+        <v>411</v>
       </c>
       <c r="D70" t="s">
-        <v>542</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>697</v>
+        <v>578</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>745</v>
       </c>
       <c r="F70" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G70" t="s">
-        <v>809</v>
+        <v>857</v>
       </c>
       <c r="H70" t="s">
-        <v>835</v>
+        <v>894</v>
       </c>
       <c r="I70" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -5253,28 +5497,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C71" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="D71" t="s">
-        <v>543</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>698</v>
+        <v>579</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>746</v>
       </c>
       <c r="F71" t="s">
-        <v>787</v>
+        <v>847</v>
       </c>
       <c r="G71" t="s">
-        <v>791</v>
+        <v>847</v>
       </c>
       <c r="H71" t="s">
-        <v>835</v>
+        <v>881</v>
       </c>
       <c r="I71" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -5282,28 +5526,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="C72" t="s">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="D72" t="s">
-        <v>544</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>699</v>
+        <v>580</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>747</v>
       </c>
       <c r="F72" t="s">
-        <v>791</v>
+        <v>846</v>
       </c>
       <c r="G72" t="s">
-        <v>789</v>
+        <v>847</v>
       </c>
       <c r="H72" t="s">
-        <v>831</v>
+        <v>895</v>
       </c>
       <c r="I72" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -5311,28 +5555,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C73" t="s">
-        <v>390</v>
+        <v>414</v>
       </c>
       <c r="D73" t="s">
-        <v>545</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>700</v>
+        <v>581</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>748</v>
       </c>
       <c r="F73" t="s">
-        <v>787</v>
+        <v>849</v>
       </c>
       <c r="G73" t="s">
-        <v>787</v>
+        <v>860</v>
       </c>
       <c r="H73" t="s">
-        <v>826</v>
+        <v>895</v>
       </c>
       <c r="I73" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -5340,28 +5584,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C74" t="s">
-        <v>391</v>
+        <v>415</v>
       </c>
       <c r="D74" t="s">
-        <v>546</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>701</v>
+        <v>582</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>749</v>
       </c>
       <c r="F74" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G74" t="s">
-        <v>799</v>
+        <v>860</v>
       </c>
       <c r="H74" t="s">
-        <v>827</v>
+        <v>895</v>
       </c>
       <c r="I74" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -5369,28 +5613,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C75" t="s">
-        <v>392</v>
+        <v>416</v>
       </c>
       <c r="D75" t="s">
-        <v>547</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>702</v>
+        <v>583</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>750</v>
       </c>
       <c r="F75" t="s">
-        <v>791</v>
+        <v>854</v>
       </c>
       <c r="G75" t="s">
-        <v>791</v>
+        <v>854</v>
       </c>
       <c r="H75" t="s">
-        <v>830</v>
+        <v>888</v>
       </c>
       <c r="I75" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -5398,28 +5642,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="C76" t="s">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="D76" t="s">
-        <v>548</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>703</v>
+        <v>584</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>751</v>
       </c>
       <c r="F76" t="s">
-        <v>801</v>
+        <v>844</v>
       </c>
       <c r="G76" t="s">
-        <v>803</v>
+        <v>867</v>
       </c>
       <c r="H76" t="s">
-        <v>830</v>
+        <v>882</v>
       </c>
       <c r="I76" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -5427,28 +5671,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C77" t="s">
-        <v>394</v>
+        <v>418</v>
       </c>
       <c r="D77" t="s">
-        <v>549</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>704</v>
+        <v>585</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>752</v>
       </c>
       <c r="F77" t="s">
-        <v>801</v>
+        <v>844</v>
       </c>
       <c r="G77" t="s">
-        <v>796</v>
+        <v>867</v>
       </c>
       <c r="H77" t="s">
-        <v>832</v>
+        <v>889</v>
       </c>
       <c r="I77" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -5456,28 +5700,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="C78" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="D78" t="s">
-        <v>550</v>
-      </c>
-      <c r="E78" s="1" t="s">
-        <v>705</v>
+        <v>586</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>753</v>
       </c>
       <c r="F78" t="s">
-        <v>785</v>
+        <v>861</v>
       </c>
       <c r="G78" t="s">
-        <v>809</v>
+        <v>848</v>
       </c>
       <c r="H78" t="s">
-        <v>832</v>
+        <v>885</v>
       </c>
       <c r="I78" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -5485,28 +5729,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C79" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="D79" t="s">
-        <v>551</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>706</v>
+        <v>587</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>754</v>
       </c>
       <c r="F79" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="G79" t="s">
-        <v>809</v>
+        <v>870</v>
       </c>
       <c r="H79" t="s">
-        <v>829</v>
+        <v>895</v>
       </c>
       <c r="I79" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -5514,28 +5758,28 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C80" t="s">
-        <v>397</v>
+        <v>421</v>
       </c>
       <c r="D80" t="s">
-        <v>552</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>707</v>
+        <v>588</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>755</v>
       </c>
       <c r="F80" t="s">
-        <v>788</v>
+        <v>848</v>
       </c>
       <c r="G80" t="s">
-        <v>791</v>
+        <v>852</v>
       </c>
       <c r="H80" t="s">
-        <v>828</v>
+        <v>895</v>
       </c>
       <c r="I80" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -5543,28 +5787,28 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C81" t="s">
-        <v>398</v>
+        <v>422</v>
       </c>
       <c r="D81" t="s">
-        <v>553</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>708</v>
+        <v>589</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>756</v>
       </c>
       <c r="F81" t="s">
-        <v>792</v>
+        <v>852</v>
       </c>
       <c r="G81" t="s">
-        <v>792</v>
+        <v>850</v>
       </c>
       <c r="H81" t="s">
-        <v>831</v>
+        <v>889</v>
       </c>
       <c r="I81" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -5572,28 +5816,28 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="C82" t="s">
-        <v>399</v>
+        <v>423</v>
       </c>
       <c r="D82" t="s">
-        <v>554</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>709</v>
+        <v>590</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>757</v>
       </c>
       <c r="F82" t="s">
-        <v>787</v>
+        <v>848</v>
       </c>
       <c r="G82" t="s">
-        <v>787</v>
+        <v>848</v>
       </c>
       <c r="H82" t="s">
-        <v>820</v>
+        <v>885</v>
       </c>
       <c r="I82" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -5601,28 +5845,28 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C83" t="s">
-        <v>400</v>
+        <v>424</v>
       </c>
       <c r="D83" t="s">
-        <v>555</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>710</v>
+        <v>591</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>758</v>
       </c>
       <c r="F83" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G83" t="s">
-        <v>815</v>
+        <v>860</v>
       </c>
       <c r="H83" t="s">
-        <v>835</v>
+        <v>887</v>
       </c>
       <c r="I83" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -5630,28 +5874,28 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="C84" t="s">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="D84" t="s">
-        <v>556</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>711</v>
+        <v>592</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>759</v>
       </c>
       <c r="F84" t="s">
-        <v>788</v>
+        <v>852</v>
       </c>
       <c r="G84" t="s">
-        <v>788</v>
+        <v>852</v>
       </c>
       <c r="H84" t="s">
-        <v>832</v>
+        <v>891</v>
       </c>
       <c r="I84" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -5659,28 +5903,28 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C85" t="s">
-        <v>402</v>
+        <v>426</v>
       </c>
       <c r="D85" t="s">
-        <v>557</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>712</v>
+        <v>593</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>760</v>
       </c>
       <c r="F85" t="s">
-        <v>788</v>
+        <v>862</v>
       </c>
       <c r="G85" t="s">
-        <v>799</v>
+        <v>864</v>
       </c>
       <c r="H85" t="s">
-        <v>835</v>
+        <v>891</v>
       </c>
       <c r="I85" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -5688,28 +5932,28 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C86" t="s">
-        <v>403</v>
+        <v>427</v>
       </c>
       <c r="D86" t="s">
-        <v>558</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>713</v>
+        <v>594</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>761</v>
       </c>
       <c r="F86" t="s">
-        <v>788</v>
+        <v>862</v>
       </c>
       <c r="G86" t="s">
-        <v>799</v>
+        <v>857</v>
       </c>
       <c r="H86" t="s">
-        <v>830</v>
+        <v>892</v>
       </c>
       <c r="I86" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -5717,28 +5961,28 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C87" t="s">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="D87" t="s">
-        <v>559</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>714</v>
+        <v>595</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>762</v>
       </c>
       <c r="F87" t="s">
-        <v>787</v>
+        <v>845</v>
       </c>
       <c r="G87" t="s">
-        <v>787</v>
+        <v>870</v>
       </c>
       <c r="H87" t="s">
-        <v>835</v>
+        <v>892</v>
       </c>
       <c r="I87" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -5746,28 +5990,28 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="D88" t="s">
-        <v>560</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>715</v>
+        <v>596</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>763</v>
       </c>
       <c r="F88" t="s">
-        <v>787</v>
+        <v>852</v>
       </c>
       <c r="G88" t="s">
-        <v>787</v>
+        <v>870</v>
       </c>
       <c r="H88" t="s">
-        <v>836</v>
+        <v>890</v>
       </c>
       <c r="I88" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -5775,28 +6019,28 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="C89" t="s">
-        <v>406</v>
+        <v>430</v>
       </c>
       <c r="D89" t="s">
-        <v>561</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>716</v>
+        <v>597</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>764</v>
       </c>
       <c r="F89" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="G89" t="s">
-        <v>791</v>
+        <v>852</v>
       </c>
       <c r="H89" t="s">
-        <v>825</v>
+        <v>888</v>
       </c>
       <c r="I89" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -5804,28 +6048,28 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="C90" t="s">
-        <v>407</v>
+        <v>431</v>
       </c>
       <c r="D90" t="s">
-        <v>562</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>717</v>
+        <v>598</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>765</v>
       </c>
       <c r="F90" t="s">
-        <v>787</v>
+        <v>853</v>
       </c>
       <c r="G90" t="s">
-        <v>805</v>
+        <v>853</v>
       </c>
       <c r="H90" t="s">
-        <v>820</v>
+        <v>889</v>
       </c>
       <c r="I90" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -5833,28 +6077,28 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C91" t="s">
-        <v>408</v>
+        <v>432</v>
       </c>
       <c r="D91" t="s">
-        <v>563</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>718</v>
+        <v>599</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>766</v>
       </c>
       <c r="F91" t="s">
-        <v>791</v>
+        <v>848</v>
       </c>
       <c r="G91" t="s">
-        <v>797</v>
+        <v>848</v>
       </c>
       <c r="H91" t="s">
-        <v>831</v>
+        <v>880</v>
       </c>
       <c r="I91" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -5862,28 +6106,28 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C92" t="s">
-        <v>409</v>
+        <v>433</v>
       </c>
       <c r="D92" t="s">
-        <v>564</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>719</v>
+        <v>600</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>767</v>
       </c>
       <c r="F92" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="G92" t="s">
-        <v>791</v>
+        <v>875</v>
       </c>
       <c r="H92" t="s">
-        <v>821</v>
+        <v>895</v>
       </c>
       <c r="I92" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -5891,28 +6135,28 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="C93" t="s">
-        <v>410</v>
+        <v>434</v>
       </c>
       <c r="D93" t="s">
-        <v>565</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>720</v>
+        <v>601</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>768</v>
       </c>
       <c r="F93" t="s">
-        <v>802</v>
+        <v>849</v>
       </c>
       <c r="G93" t="s">
-        <v>802</v>
+        <v>849</v>
       </c>
       <c r="H93" t="s">
-        <v>835</v>
+        <v>892</v>
       </c>
       <c r="I93" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -5920,28 +6164,28 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="C94" t="s">
-        <v>411</v>
+        <v>435</v>
       </c>
       <c r="D94" t="s">
-        <v>566</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>721</v>
+        <v>602</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>769</v>
       </c>
       <c r="F94" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="G94" t="s">
-        <v>791</v>
+        <v>860</v>
       </c>
       <c r="H94" t="s">
-        <v>831</v>
+        <v>895</v>
       </c>
       <c r="I94" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -5949,28 +6193,28 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="C95" t="s">
-        <v>412</v>
+        <v>436</v>
       </c>
       <c r="D95" t="s">
-        <v>567</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>722</v>
+        <v>603</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>770</v>
       </c>
       <c r="F95" t="s">
-        <v>784</v>
+        <v>849</v>
       </c>
       <c r="G95" t="s">
-        <v>806</v>
+        <v>860</v>
       </c>
       <c r="H95" t="s">
-        <v>825</v>
+        <v>891</v>
       </c>
       <c r="I95" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -5978,28 +6222,28 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C96" t="s">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="D96" t="s">
-        <v>568</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>723</v>
+        <v>604</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>771</v>
       </c>
       <c r="F96" t="s">
-        <v>791</v>
+        <v>848</v>
       </c>
       <c r="G96" t="s">
-        <v>791</v>
+        <v>848</v>
       </c>
       <c r="H96" t="s">
-        <v>826</v>
+        <v>895</v>
       </c>
       <c r="I96" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6007,28 +6251,28 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="C97" t="s">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="D97" t="s">
-        <v>569</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>724</v>
+        <v>605</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>772</v>
       </c>
       <c r="F97" t="s">
-        <v>788</v>
+        <v>848</v>
       </c>
       <c r="G97" t="s">
-        <v>792</v>
+        <v>847</v>
       </c>
       <c r="H97" t="s">
-        <v>837</v>
+        <v>896</v>
       </c>
       <c r="I97" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6036,28 +6280,28 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="C98" t="s">
-        <v>415</v>
+        <v>439</v>
       </c>
       <c r="D98" t="s">
-        <v>570</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>725</v>
+        <v>606</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>773</v>
       </c>
       <c r="F98" t="s">
-        <v>803</v>
+        <v>852</v>
       </c>
       <c r="G98" t="s">
-        <v>796</v>
+        <v>852</v>
       </c>
       <c r="H98" t="s">
-        <v>831</v>
+        <v>886</v>
       </c>
       <c r="I98" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -6065,28 +6309,28 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="C99" t="s">
-        <v>416</v>
+        <v>440</v>
       </c>
       <c r="D99" t="s">
-        <v>571</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>726</v>
+        <v>607</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>774</v>
       </c>
       <c r="F99" t="s">
-        <v>788</v>
+        <v>848</v>
       </c>
       <c r="G99" t="s">
-        <v>788</v>
+        <v>866</v>
       </c>
       <c r="H99" t="s">
-        <v>832</v>
+        <v>880</v>
       </c>
       <c r="I99" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6094,28 +6338,28 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C100" t="s">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="D100" t="s">
-        <v>572</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>727</v>
+        <v>608</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>775</v>
       </c>
       <c r="F100" t="s">
-        <v>792</v>
+        <v>852</v>
       </c>
       <c r="G100" t="s">
-        <v>792</v>
+        <v>858</v>
       </c>
       <c r="H100" t="s">
-        <v>831</v>
+        <v>889</v>
       </c>
       <c r="I100" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -6123,28 +6367,28 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C101" t="s">
-        <v>418</v>
+        <v>442</v>
       </c>
       <c r="D101" t="s">
-        <v>573</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>728</v>
+        <v>609</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>776</v>
       </c>
       <c r="F101" t="s">
-        <v>786</v>
+        <v>852</v>
       </c>
       <c r="G101" t="s">
-        <v>786</v>
+        <v>852</v>
       </c>
       <c r="H101" t="s">
-        <v>821</v>
+        <v>881</v>
       </c>
       <c r="I101" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6152,28 +6396,28 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C102" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="D102" t="s">
-        <v>574</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>729</v>
+        <v>610</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>777</v>
       </c>
       <c r="F102" t="s">
-        <v>788</v>
+        <v>863</v>
       </c>
       <c r="G102" t="s">
-        <v>799</v>
+        <v>863</v>
       </c>
       <c r="H102" t="s">
-        <v>828</v>
+        <v>895</v>
       </c>
       <c r="I102" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -6181,28 +6425,28 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="C103" t="s">
-        <v>420</v>
+        <v>444</v>
       </c>
       <c r="D103" t="s">
-        <v>575</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>730</v>
+        <v>611</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>778</v>
       </c>
       <c r="F103" t="s">
-        <v>788</v>
+        <v>852</v>
       </c>
       <c r="G103" t="s">
-        <v>793</v>
+        <v>852</v>
       </c>
       <c r="H103" t="s">
-        <v>825</v>
+        <v>889</v>
       </c>
       <c r="I103" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -6210,28 +6454,28 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C104" t="s">
-        <v>421</v>
+        <v>445</v>
       </c>
       <c r="D104" t="s">
-        <v>576</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>731</v>
+        <v>612</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>779</v>
       </c>
       <c r="F104" t="s">
-        <v>786</v>
+        <v>847</v>
       </c>
       <c r="G104" t="s">
-        <v>806</v>
+        <v>847</v>
       </c>
       <c r="H104" t="s">
-        <v>838</v>
+        <v>885</v>
       </c>
       <c r="I104" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6239,28 +6483,28 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="C105" t="s">
-        <v>422</v>
+        <v>446</v>
       </c>
       <c r="D105" t="s">
-        <v>577</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>732</v>
+        <v>613</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>780</v>
       </c>
       <c r="F105" t="s">
-        <v>788</v>
+        <v>847</v>
       </c>
       <c r="G105" t="s">
-        <v>794</v>
+        <v>847</v>
       </c>
       <c r="H105" t="s">
-        <v>837</v>
+        <v>885</v>
       </c>
       <c r="I105" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6268,28 +6512,28 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="C106" t="s">
-        <v>423</v>
+        <v>447</v>
       </c>
       <c r="D106" t="s">
-        <v>578</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>733</v>
+        <v>614</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>781</v>
       </c>
       <c r="F106" t="s">
-        <v>803</v>
+        <v>844</v>
       </c>
       <c r="G106" t="s">
-        <v>796</v>
+        <v>867</v>
       </c>
       <c r="H106" t="s">
-        <v>822</v>
+        <v>886</v>
       </c>
       <c r="I106" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6297,28 +6541,28 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="C107" t="s">
-        <v>424</v>
+        <v>448</v>
       </c>
       <c r="D107" t="s">
-        <v>579</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>734</v>
+        <v>615</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>782</v>
       </c>
       <c r="F107" t="s">
-        <v>788</v>
+        <v>852</v>
       </c>
       <c r="G107" t="s">
-        <v>799</v>
+        <v>852</v>
       </c>
       <c r="H107" t="s">
-        <v>825</v>
+        <v>885</v>
       </c>
       <c r="I107" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -6326,28 +6570,28 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C108" t="s">
-        <v>425</v>
+        <v>449</v>
       </c>
       <c r="D108" t="s">
-        <v>580</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>735</v>
+        <v>616</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>783</v>
       </c>
       <c r="F108" t="s">
-        <v>787</v>
+        <v>849</v>
       </c>
       <c r="G108" t="s">
-        <v>816</v>
+        <v>853</v>
       </c>
       <c r="H108" t="s">
-        <v>839</v>
+        <v>897</v>
       </c>
       <c r="I108" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -6355,28 +6599,28 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C109" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="D109" t="s">
-        <v>581</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>736</v>
+        <v>617</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>784</v>
       </c>
       <c r="F109" t="s">
-        <v>791</v>
+        <v>864</v>
       </c>
       <c r="G109" t="s">
-        <v>791</v>
+        <v>857</v>
       </c>
       <c r="H109" t="s">
-        <v>829</v>
+        <v>889</v>
       </c>
       <c r="I109" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -6384,28 +6628,28 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="C110" t="s">
-        <v>427</v>
+        <v>451</v>
       </c>
       <c r="D110" t="s">
-        <v>582</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>737</v>
+        <v>618</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>785</v>
       </c>
       <c r="F110" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G110" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="H110" t="s">
-        <v>827</v>
+        <v>892</v>
       </c>
       <c r="I110" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -6413,28 +6657,28 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="C111" t="s">
-        <v>428</v>
+        <v>452</v>
       </c>
       <c r="D111" t="s">
-        <v>583</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>738</v>
+        <v>619</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>786</v>
       </c>
       <c r="F111" t="s">
-        <v>788</v>
+        <v>853</v>
       </c>
       <c r="G111" t="s">
-        <v>809</v>
+        <v>853</v>
       </c>
       <c r="H111" t="s">
-        <v>837</v>
+        <v>889</v>
       </c>
       <c r="I111" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -6442,28 +6686,28 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C112" t="s">
-        <v>429</v>
+        <v>453</v>
       </c>
       <c r="D112" t="s">
-        <v>584</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>739</v>
+        <v>620</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>787</v>
       </c>
       <c r="F112" t="s">
-        <v>788</v>
+        <v>846</v>
       </c>
       <c r="G112" t="s">
-        <v>799</v>
+        <v>846</v>
       </c>
       <c r="H112" t="s">
-        <v>840</v>
+        <v>881</v>
       </c>
       <c r="I112" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -6471,28 +6715,28 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="C113" t="s">
-        <v>430</v>
+        <v>454</v>
       </c>
       <c r="D113" t="s">
-        <v>585</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>740</v>
+        <v>621</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>788</v>
       </c>
       <c r="F113" t="s">
-        <v>784</v>
+        <v>849</v>
       </c>
       <c r="G113" t="s">
-        <v>806</v>
+        <v>860</v>
       </c>
       <c r="H113" t="s">
-        <v>825</v>
+        <v>888</v>
       </c>
       <c r="I113" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -6500,28 +6744,28 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="C114" t="s">
-        <v>431</v>
+        <v>455</v>
       </c>
       <c r="D114" t="s">
-        <v>586</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>741</v>
+        <v>622</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>789</v>
       </c>
       <c r="F114" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G114" t="s">
-        <v>788</v>
+        <v>854</v>
       </c>
       <c r="H114" t="s">
-        <v>830</v>
+        <v>886</v>
       </c>
       <c r="I114" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -6529,28 +6773,28 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="C115" t="s">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="D115" t="s">
-        <v>587</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>742</v>
+        <v>623</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>790</v>
       </c>
       <c r="F115" t="s">
-        <v>803</v>
+        <v>846</v>
       </c>
       <c r="G115" t="s">
-        <v>796</v>
+        <v>867</v>
       </c>
       <c r="H115" t="s">
-        <v>829</v>
+        <v>898</v>
       </c>
       <c r="I115" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -6558,28 +6802,28 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C116" t="s">
-        <v>433</v>
+        <v>457</v>
       </c>
       <c r="D116" t="s">
-        <v>588</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>743</v>
+        <v>624</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>791</v>
       </c>
       <c r="F116" t="s">
-        <v>804</v>
+        <v>849</v>
       </c>
       <c r="G116" t="s">
-        <v>817</v>
+        <v>855</v>
       </c>
       <c r="H116" t="s">
-        <v>841</v>
+        <v>897</v>
       </c>
       <c r="I116" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -6587,28 +6831,28 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="C117" t="s">
-        <v>434</v>
+        <v>458</v>
       </c>
       <c r="D117" t="s">
-        <v>589</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>744</v>
+        <v>625</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>792</v>
       </c>
       <c r="F117" t="s">
-        <v>791</v>
+        <v>864</v>
       </c>
       <c r="G117" t="s">
-        <v>801</v>
+        <v>857</v>
       </c>
       <c r="H117" t="s">
-        <v>825</v>
+        <v>882</v>
       </c>
       <c r="I117" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -6616,28 +6860,28 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="C118" t="s">
-        <v>435</v>
+        <v>459</v>
       </c>
       <c r="D118" t="s">
-        <v>590</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>745</v>
+        <v>626</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>793</v>
       </c>
       <c r="F118" t="s">
-        <v>784</v>
+        <v>849</v>
       </c>
       <c r="G118" t="s">
-        <v>806</v>
+        <v>860</v>
       </c>
       <c r="H118" t="s">
-        <v>825</v>
+        <v>886</v>
       </c>
       <c r="I118" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -6645,28 +6889,28 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="C119" t="s">
-        <v>436</v>
+        <v>460</v>
       </c>
       <c r="D119" t="s">
-        <v>591</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>746</v>
+        <v>627</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>794</v>
       </c>
       <c r="F119" t="s">
-        <v>788</v>
+        <v>848</v>
       </c>
       <c r="G119" t="s">
-        <v>788</v>
+        <v>876</v>
       </c>
       <c r="H119" t="s">
-        <v>825</v>
+        <v>899</v>
       </c>
       <c r="I119" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -6674,28 +6918,28 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C120" t="s">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="D120" t="s">
-        <v>592</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>747</v>
+        <v>628</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>795</v>
       </c>
       <c r="F120" t="s">
-        <v>791</v>
+        <v>852</v>
       </c>
       <c r="G120" t="s">
-        <v>791</v>
+        <v>852</v>
       </c>
       <c r="H120" t="s">
-        <v>825</v>
+        <v>890</v>
       </c>
       <c r="I120" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -6703,28 +6947,28 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C121" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="D121" t="s">
-        <v>593</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>748</v>
+        <v>629</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>796</v>
       </c>
       <c r="F121" t="s">
-        <v>786</v>
+        <v>849</v>
       </c>
       <c r="G121" t="s">
-        <v>786</v>
+        <v>849</v>
       </c>
       <c r="H121" t="s">
-        <v>822</v>
+        <v>887</v>
       </c>
       <c r="I121" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -6732,28 +6976,28 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="C122" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="D122" t="s">
-        <v>594</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>749</v>
+        <v>630</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>797</v>
       </c>
       <c r="F122" t="s">
-        <v>786</v>
+        <v>849</v>
       </c>
       <c r="G122" t="s">
-        <v>786</v>
+        <v>870</v>
       </c>
       <c r="H122" t="s">
-        <v>824</v>
+        <v>897</v>
       </c>
       <c r="I122" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -6761,28 +7005,28 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="C123" t="s">
-        <v>440</v>
+        <v>464</v>
       </c>
       <c r="D123" t="s">
-        <v>595</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>750</v>
+        <v>631</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>798</v>
       </c>
       <c r="F123" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="G123" t="s">
-        <v>791</v>
+        <v>860</v>
       </c>
       <c r="H123" t="s">
-        <v>821</v>
+        <v>900</v>
       </c>
       <c r="I123" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -6790,28 +7034,28 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="C124" t="s">
-        <v>441</v>
+        <v>465</v>
       </c>
       <c r="D124" t="s">
-        <v>596</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>751</v>
+        <v>632</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>799</v>
       </c>
       <c r="F124" t="s">
-        <v>787</v>
+        <v>844</v>
       </c>
       <c r="G124" t="s">
-        <v>787</v>
+        <v>867</v>
       </c>
       <c r="H124" t="s">
-        <v>826</v>
+        <v>886</v>
       </c>
       <c r="I124" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -6819,28 +7063,28 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C125" t="s">
-        <v>442</v>
+        <v>466</v>
       </c>
       <c r="D125" t="s">
-        <v>597</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>752</v>
+        <v>633</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>800</v>
       </c>
       <c r="F125" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="G125" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="H125" t="s">
-        <v>825</v>
+        <v>891</v>
       </c>
       <c r="I125" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -6848,28 +7092,28 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="C126" t="s">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="D126" t="s">
-        <v>598</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>753</v>
+        <v>634</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>801</v>
       </c>
       <c r="F126" t="s">
-        <v>794</v>
+        <v>864</v>
       </c>
       <c r="G126" t="s">
-        <v>792</v>
+        <v>857</v>
       </c>
       <c r="H126" t="s">
-        <v>819</v>
+        <v>890</v>
       </c>
       <c r="I126" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -6877,28 +7121,28 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="C127" t="s">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="D127" t="s">
-        <v>599</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>754</v>
+        <v>635</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>802</v>
       </c>
       <c r="F127" t="s">
-        <v>788</v>
+        <v>865</v>
       </c>
       <c r="G127" t="s">
-        <v>807</v>
+        <v>877</v>
       </c>
       <c r="H127" t="s">
-        <v>830</v>
+        <v>901</v>
       </c>
       <c r="I127" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -6906,28 +7150,28 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="C128" t="s">
-        <v>445</v>
+        <v>469</v>
       </c>
       <c r="D128" t="s">
-        <v>600</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>755</v>
+        <v>636</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>803</v>
       </c>
       <c r="F128" t="s">
-        <v>788</v>
+        <v>852</v>
       </c>
       <c r="G128" t="s">
-        <v>814</v>
+        <v>862</v>
       </c>
       <c r="H128" t="s">
-        <v>830</v>
+        <v>886</v>
       </c>
       <c r="I128" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -6935,28 +7179,28 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C129" t="s">
-        <v>446</v>
+        <v>470</v>
       </c>
       <c r="D129" t="s">
-        <v>601</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>756</v>
+        <v>637</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>804</v>
       </c>
       <c r="F129" t="s">
-        <v>788</v>
+        <v>844</v>
       </c>
       <c r="G129" t="s">
-        <v>799</v>
+        <v>847</v>
       </c>
       <c r="H129" t="s">
-        <v>830</v>
+        <v>886</v>
       </c>
       <c r="I129" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -6964,28 +7208,28 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="C130" t="s">
-        <v>447</v>
+        <v>471</v>
       </c>
       <c r="D130" t="s">
-        <v>602</v>
-      </c>
-      <c r="E130" s="1" t="s">
-        <v>757</v>
+        <v>638</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>805</v>
       </c>
       <c r="F130" t="s">
-        <v>805</v>
+        <v>849</v>
       </c>
       <c r="G130" t="s">
-        <v>815</v>
+        <v>849</v>
       </c>
       <c r="H130" t="s">
-        <v>830</v>
+        <v>886</v>
       </c>
       <c r="I130" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -6993,28 +7237,28 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="C131" t="s">
-        <v>448</v>
+        <v>472</v>
       </c>
       <c r="D131" t="s">
-        <v>603</v>
-      </c>
-      <c r="E131" s="1" t="s">
-        <v>758</v>
+        <v>639</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>806</v>
       </c>
       <c r="F131" t="s">
-        <v>788</v>
+        <v>852</v>
       </c>
       <c r="G131" t="s">
-        <v>799</v>
+        <v>852</v>
       </c>
       <c r="H131" t="s">
-        <v>830</v>
+        <v>886</v>
       </c>
       <c r="I131" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -7022,28 +7266,28 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="C132" t="s">
-        <v>449</v>
+        <v>473</v>
       </c>
       <c r="D132" t="s">
-        <v>604</v>
-      </c>
-      <c r="E132" s="1" t="s">
-        <v>759</v>
+        <v>640</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>807</v>
       </c>
       <c r="F132" t="s">
-        <v>802</v>
+        <v>846</v>
       </c>
       <c r="G132" t="s">
-        <v>802</v>
+        <v>846</v>
       </c>
       <c r="H132" t="s">
-        <v>835</v>
+        <v>882</v>
       </c>
       <c r="I132" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -7051,28 +7295,28 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="C133" t="s">
-        <v>450</v>
+        <v>474</v>
       </c>
       <c r="D133" t="s">
-        <v>605</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>760</v>
+        <v>641</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>808</v>
       </c>
       <c r="F133" t="s">
-        <v>787</v>
+        <v>846</v>
       </c>
       <c r="G133" t="s">
-        <v>787</v>
+        <v>846</v>
       </c>
       <c r="H133" t="s">
-        <v>826</v>
+        <v>884</v>
       </c>
       <c r="I133" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -7080,28 +7324,28 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C134" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="D134" t="s">
-        <v>606</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>761</v>
+        <v>642</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>809</v>
       </c>
       <c r="F134" t="s">
-        <v>788</v>
+        <v>852</v>
       </c>
       <c r="G134" t="s">
-        <v>799</v>
+        <v>852</v>
       </c>
       <c r="H134" t="s">
-        <v>825</v>
+        <v>881</v>
       </c>
       <c r="I134" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -7109,28 +7353,28 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="C135" t="s">
-        <v>452</v>
+        <v>476</v>
       </c>
       <c r="D135" t="s">
-        <v>607</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>762</v>
+        <v>643</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>810</v>
       </c>
       <c r="F135" t="s">
-        <v>788</v>
+        <v>848</v>
       </c>
       <c r="G135" t="s">
-        <v>817</v>
+        <v>848</v>
       </c>
       <c r="H135" t="s">
-        <v>826</v>
+        <v>885</v>
       </c>
       <c r="I135" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -7138,28 +7382,28 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C136" t="s">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="D136" t="s">
-        <v>608</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>763</v>
+        <v>644</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>811</v>
       </c>
       <c r="F136" t="s">
-        <v>787</v>
+        <v>847</v>
       </c>
       <c r="G136" t="s">
-        <v>787</v>
+        <v>847</v>
       </c>
       <c r="H136" t="s">
-        <v>839</v>
+        <v>881</v>
       </c>
       <c r="I136" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -7167,28 +7411,28 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="C137" t="s">
-        <v>454</v>
+        <v>478</v>
       </c>
       <c r="D137" t="s">
-        <v>609</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>764</v>
+        <v>645</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>812</v>
       </c>
       <c r="F137" t="s">
-        <v>791</v>
+        <v>852</v>
       </c>
       <c r="G137" t="s">
-        <v>791</v>
+        <v>852</v>
       </c>
       <c r="H137" t="s">
-        <v>829</v>
+        <v>886</v>
       </c>
       <c r="I137" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -7196,28 +7440,28 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C138" t="s">
-        <v>455</v>
+        <v>479</v>
       </c>
       <c r="D138" t="s">
-        <v>610</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>765</v>
+        <v>646</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>813</v>
       </c>
       <c r="F138" t="s">
-        <v>798</v>
+        <v>855</v>
       </c>
       <c r="G138" t="s">
-        <v>814</v>
+        <v>853</v>
       </c>
       <c r="H138" t="s">
-        <v>825</v>
+        <v>879</v>
       </c>
       <c r="I138" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -7225,28 +7469,28 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="C139" t="s">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="D139" t="s">
-        <v>611</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>766</v>
+        <v>647</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>814</v>
       </c>
       <c r="F139" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="G139" t="s">
-        <v>791</v>
+        <v>868</v>
       </c>
       <c r="H139" t="s">
-        <v>829</v>
+        <v>891</v>
       </c>
       <c r="I139" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -7254,28 +7498,28 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="C140" t="s">
-        <v>457</v>
+        <v>481</v>
       </c>
       <c r="D140" t="s">
-        <v>612</v>
-      </c>
-      <c r="E140" s="1" t="s">
-        <v>767</v>
+        <v>648</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>815</v>
       </c>
       <c r="F140" t="s">
-        <v>791</v>
+        <v>849</v>
       </c>
       <c r="G140" t="s">
-        <v>791</v>
+        <v>874</v>
       </c>
       <c r="H140" t="s">
-        <v>829</v>
+        <v>891</v>
       </c>
       <c r="I140" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -7283,28 +7527,28 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C141" t="s">
-        <v>458</v>
+        <v>482</v>
       </c>
       <c r="D141" t="s">
-        <v>613</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>768</v>
+        <v>649</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>816</v>
       </c>
       <c r="F141" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G141" t="s">
-        <v>807</v>
+        <v>860</v>
       </c>
       <c r="H141" t="s">
-        <v>830</v>
+        <v>891</v>
       </c>
       <c r="I141" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -7312,28 +7556,28 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C142" t="s">
-        <v>459</v>
+        <v>483</v>
       </c>
       <c r="D142" t="s">
-        <v>614</v>
-      </c>
-      <c r="E142" s="1" t="s">
-        <v>769</v>
+        <v>650</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>817</v>
       </c>
       <c r="F142" t="s">
-        <v>786</v>
+        <v>866</v>
       </c>
       <c r="G142" t="s">
-        <v>786</v>
+        <v>875</v>
       </c>
       <c r="H142" t="s">
-        <v>821</v>
+        <v>891</v>
       </c>
       <c r="I142" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -7341,28 +7585,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C143" t="s">
-        <v>460</v>
+        <v>484</v>
       </c>
       <c r="D143" t="s">
-        <v>615</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>770</v>
+        <v>651</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>818</v>
       </c>
       <c r="F143" t="s">
-        <v>786</v>
+        <v>849</v>
       </c>
       <c r="G143" t="s">
-        <v>786</v>
+        <v>860</v>
       </c>
       <c r="H143" t="s">
-        <v>829</v>
+        <v>891</v>
       </c>
       <c r="I143" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -7370,28 +7614,28 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C144" t="s">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="D144" t="s">
-        <v>616</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>771</v>
+        <v>652</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>819</v>
       </c>
       <c r="F144" t="s">
-        <v>788</v>
+        <v>863</v>
       </c>
       <c r="G144" t="s">
-        <v>799</v>
+        <v>863</v>
       </c>
       <c r="H144" t="s">
-        <v>832</v>
+        <v>895</v>
       </c>
       <c r="I144" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -7399,28 +7643,28 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C145" t="s">
-        <v>462</v>
+        <v>486</v>
       </c>
       <c r="D145" t="s">
-        <v>617</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>772</v>
+        <v>653</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>820</v>
       </c>
       <c r="F145" t="s">
-        <v>788</v>
+        <v>848</v>
       </c>
       <c r="G145" t="s">
-        <v>788</v>
+        <v>848</v>
       </c>
       <c r="H145" t="s">
-        <v>832</v>
+        <v>885</v>
       </c>
       <c r="I145" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -7428,28 +7672,28 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C146" t="s">
-        <v>463</v>
+        <v>487</v>
       </c>
       <c r="D146" t="s">
-        <v>618</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>773</v>
+        <v>654</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>821</v>
       </c>
       <c r="F146" t="s">
-        <v>796</v>
+        <v>849</v>
       </c>
       <c r="G146" t="s">
-        <v>805</v>
+        <v>860</v>
       </c>
       <c r="H146" t="s">
-        <v>831</v>
+        <v>886</v>
       </c>
       <c r="I146" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -7457,28 +7701,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C147" t="s">
-        <v>464</v>
+        <v>488</v>
       </c>
       <c r="D147" t="s">
-        <v>619</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>774</v>
+        <v>655</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>822</v>
       </c>
       <c r="F147" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G147" t="s">
-        <v>799</v>
+        <v>877</v>
       </c>
       <c r="H147" t="s">
-        <v>820</v>
+        <v>885</v>
       </c>
       <c r="I147" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -7486,28 +7730,28 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C148" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="D148" t="s">
-        <v>620</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>775</v>
+        <v>656</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>823</v>
       </c>
       <c r="F148" t="s">
-        <v>787</v>
+        <v>848</v>
       </c>
       <c r="G148" t="s">
-        <v>818</v>
+        <v>848</v>
       </c>
       <c r="H148" t="s">
-        <v>822</v>
+        <v>899</v>
       </c>
       <c r="I148" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -7515,28 +7759,28 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C149" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="D149" t="s">
-        <v>621</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>776</v>
+        <v>657</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>824</v>
       </c>
       <c r="F149" t="s">
-        <v>803</v>
+        <v>852</v>
       </c>
       <c r="G149" t="s">
-        <v>796</v>
+        <v>852</v>
       </c>
       <c r="H149" t="s">
-        <v>842</v>
+        <v>890</v>
       </c>
       <c r="I149" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -7544,28 +7788,28 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="C150" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="D150" t="s">
-        <v>622</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>777</v>
+        <v>658</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>825</v>
       </c>
       <c r="F150" t="s">
-        <v>788</v>
+        <v>859</v>
       </c>
       <c r="G150" t="s">
-        <v>788</v>
+        <v>874</v>
       </c>
       <c r="H150" t="s">
-        <v>832</v>
+        <v>886</v>
       </c>
       <c r="I150" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -7573,28 +7817,28 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="C151" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="D151" t="s">
-        <v>623</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>778</v>
+        <v>659</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>826</v>
       </c>
       <c r="F151" t="s">
-        <v>788</v>
+        <v>852</v>
       </c>
       <c r="G151" t="s">
-        <v>813</v>
+        <v>852</v>
       </c>
       <c r="H151" t="s">
-        <v>820</v>
+        <v>890</v>
       </c>
       <c r="I151" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -7602,28 +7846,28 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="C152" t="s">
-        <v>469</v>
+        <v>493</v>
       </c>
       <c r="D152" t="s">
-        <v>624</v>
-      </c>
-      <c r="E152" s="1" t="s">
-        <v>779</v>
+        <v>660</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>827</v>
       </c>
       <c r="F152" t="s">
-        <v>787</v>
+        <v>852</v>
       </c>
       <c r="G152" t="s">
-        <v>787</v>
+        <v>852</v>
       </c>
       <c r="H152" t="s">
-        <v>826</v>
+        <v>890</v>
       </c>
       <c r="I152" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -7631,28 +7875,28 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C153" t="s">
-        <v>470</v>
+        <v>494</v>
       </c>
       <c r="D153" t="s">
-        <v>625</v>
-      </c>
-      <c r="E153" s="1" t="s">
-        <v>780</v>
+        <v>661</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>828</v>
       </c>
       <c r="F153" t="s">
-        <v>795</v>
+        <v>849</v>
       </c>
       <c r="G153" t="s">
-        <v>789</v>
+        <v>868</v>
       </c>
       <c r="H153" t="s">
-        <v>843</v>
+        <v>891</v>
       </c>
       <c r="I153" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -7660,28 +7904,28 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C154" t="s">
-        <v>471</v>
+        <v>495</v>
       </c>
       <c r="D154" t="s">
-        <v>626</v>
-      </c>
-      <c r="E154" s="1" t="s">
-        <v>781</v>
+        <v>662</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>829</v>
       </c>
       <c r="F154" t="s">
-        <v>788</v>
+        <v>846</v>
       </c>
       <c r="G154" t="s">
-        <v>788</v>
+        <v>846</v>
       </c>
       <c r="H154" t="s">
-        <v>832</v>
+        <v>881</v>
       </c>
       <c r="I154" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -7689,28 +7933,28 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="C155" t="s">
-        <v>472</v>
+        <v>496</v>
       </c>
       <c r="D155" t="s">
-        <v>627</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>782</v>
+        <v>663</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>830</v>
       </c>
       <c r="F155" t="s">
-        <v>785</v>
+        <v>846</v>
       </c>
       <c r="G155" t="s">
-        <v>809</v>
+        <v>846</v>
       </c>
       <c r="H155" t="s">
-        <v>831</v>
+        <v>890</v>
       </c>
       <c r="I155" t="s">
-        <v>844</v>
+        <v>904</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -7718,28 +7962,376 @@
         <v>163</v>
       </c>
       <c r="B156" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C156" t="s">
-        <v>473</v>
+        <v>497</v>
       </c>
       <c r="D156" t="s">
-        <v>628</v>
-      </c>
-      <c r="E156" s="1" t="s">
-        <v>783</v>
+        <v>664</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>831</v>
       </c>
       <c r="F156" t="s">
-        <v>788</v>
+        <v>849</v>
       </c>
       <c r="G156" t="s">
-        <v>811</v>
+        <v>860</v>
       </c>
       <c r="H156" t="s">
+        <v>892</v>
+      </c>
+      <c r="I156" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9">
+      <c r="A157" t="s">
+        <v>164</v>
+      </c>
+      <c r="B157" t="s">
+        <v>331</v>
+      </c>
+      <c r="C157" t="s">
+        <v>498</v>
+      </c>
+      <c r="D157" t="s">
+        <v>665</v>
+      </c>
+      <c r="E157" s="2" t="s">
         <v>832</v>
       </c>
-      <c r="I156" t="s">
-        <v>844</v>
+      <c r="F157" t="s">
+        <v>849</v>
+      </c>
+      <c r="G157" t="s">
+        <v>849</v>
+      </c>
+      <c r="H157" t="s">
+        <v>892</v>
+      </c>
+      <c r="I157" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9">
+      <c r="A158" t="s">
+        <v>165</v>
+      </c>
+      <c r="B158" t="s">
+        <v>332</v>
+      </c>
+      <c r="C158" t="s">
+        <v>499</v>
+      </c>
+      <c r="D158" t="s">
+        <v>666</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="F158" t="s">
+        <v>857</v>
+      </c>
+      <c r="G158" t="s">
+        <v>866</v>
+      </c>
+      <c r="H158" t="s">
+        <v>889</v>
+      </c>
+      <c r="I158" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9">
+      <c r="A159" t="s">
+        <v>166</v>
+      </c>
+      <c r="B159" t="s">
+        <v>333</v>
+      </c>
+      <c r="C159" t="s">
+        <v>500</v>
+      </c>
+      <c r="D159" t="s">
+        <v>667</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="F159" t="s">
+        <v>849</v>
+      </c>
+      <c r="G159" t="s">
+        <v>860</v>
+      </c>
+      <c r="H159" t="s">
+        <v>880</v>
+      </c>
+      <c r="I159" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9">
+      <c r="A160" t="s">
+        <v>167</v>
+      </c>
+      <c r="B160" t="s">
+        <v>334</v>
+      </c>
+      <c r="C160" t="s">
+        <v>501</v>
+      </c>
+      <c r="D160" t="s">
+        <v>668</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="F160" t="s">
+        <v>848</v>
+      </c>
+      <c r="G160" t="s">
+        <v>878</v>
+      </c>
+      <c r="H160" t="s">
+        <v>882</v>
+      </c>
+      <c r="I160" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9">
+      <c r="A161" t="s">
+        <v>168</v>
+      </c>
+      <c r="B161" t="s">
+        <v>335</v>
+      </c>
+      <c r="C161" t="s">
+        <v>502</v>
+      </c>
+      <c r="D161" t="s">
+        <v>669</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="F161" t="s">
+        <v>864</v>
+      </c>
+      <c r="G161" t="s">
+        <v>857</v>
+      </c>
+      <c r="H161" t="s">
+        <v>902</v>
+      </c>
+      <c r="I161" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9">
+      <c r="A162" t="s">
+        <v>169</v>
+      </c>
+      <c r="B162" t="s">
+        <v>336</v>
+      </c>
+      <c r="C162" t="s">
+        <v>503</v>
+      </c>
+      <c r="D162" t="s">
+        <v>670</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="F162" t="s">
+        <v>849</v>
+      </c>
+      <c r="G162" t="s">
+        <v>849</v>
+      </c>
+      <c r="H162" t="s">
+        <v>892</v>
+      </c>
+      <c r="I162" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9">
+      <c r="A163" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" t="s">
+        <v>337</v>
+      </c>
+      <c r="C163" t="s">
+        <v>504</v>
+      </c>
+      <c r="D163" t="s">
+        <v>671</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="F163" t="s">
+        <v>849</v>
+      </c>
+      <c r="G163" t="s">
+        <v>873</v>
+      </c>
+      <c r="H163" t="s">
+        <v>880</v>
+      </c>
+      <c r="I163" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" t="s">
+        <v>171</v>
+      </c>
+      <c r="B164" t="s">
+        <v>338</v>
+      </c>
+      <c r="C164" t="s">
+        <v>505</v>
+      </c>
+      <c r="D164" t="s">
+        <v>672</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="F164" t="s">
+        <v>848</v>
+      </c>
+      <c r="G164" t="s">
+        <v>848</v>
+      </c>
+      <c r="H164" t="s">
+        <v>885</v>
+      </c>
+      <c r="I164" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" t="s">
+        <v>172</v>
+      </c>
+      <c r="B165" t="s">
+        <v>339</v>
+      </c>
+      <c r="C165" t="s">
+        <v>506</v>
+      </c>
+      <c r="D165" t="s">
+        <v>673</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="F165" t="s">
+        <v>856</v>
+      </c>
+      <c r="G165" t="s">
+        <v>850</v>
+      </c>
+      <c r="H165" t="s">
+        <v>903</v>
+      </c>
+      <c r="I165" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9">
+      <c r="A166" t="s">
+        <v>173</v>
+      </c>
+      <c r="B166" t="s">
+        <v>340</v>
+      </c>
+      <c r="C166" t="s">
+        <v>507</v>
+      </c>
+      <c r="D166" t="s">
+        <v>674</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="F166" t="s">
+        <v>849</v>
+      </c>
+      <c r="G166" t="s">
+        <v>849</v>
+      </c>
+      <c r="H166" t="s">
+        <v>892</v>
+      </c>
+      <c r="I166" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9">
+      <c r="A167" t="s">
+        <v>174</v>
+      </c>
+      <c r="B167" t="s">
+        <v>341</v>
+      </c>
+      <c r="C167" t="s">
+        <v>508</v>
+      </c>
+      <c r="D167" t="s">
+        <v>675</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="F167" t="s">
+        <v>845</v>
+      </c>
+      <c r="G167" t="s">
+        <v>870</v>
+      </c>
+      <c r="H167" t="s">
+        <v>889</v>
+      </c>
+      <c r="I167" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9">
+      <c r="A168" t="s">
+        <v>175</v>
+      </c>
+      <c r="B168" t="s">
+        <v>342</v>
+      </c>
+      <c r="C168" t="s">
+        <v>509</v>
+      </c>
+      <c r="D168" t="s">
+        <v>676</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>843</v>
+      </c>
+      <c r="F168" t="s">
+        <v>849</v>
+      </c>
+      <c r="G168" t="s">
+        <v>871</v>
+      </c>
+      <c r="H168" t="s">
+        <v>892</v>
+      </c>
+      <c r="I168" t="s">
+        <v>904</v>
       </c>
     </row>
   </sheetData>
@@ -7899,6 +8491,18 @@
     <hyperlink ref="E154" r:id="rId153"/>
     <hyperlink ref="E155" r:id="rId154"/>
     <hyperlink ref="E156" r:id="rId155"/>
+    <hyperlink ref="E157" r:id="rId156"/>
+    <hyperlink ref="E158" r:id="rId157"/>
+    <hyperlink ref="E159" r:id="rId158"/>
+    <hyperlink ref="E160" r:id="rId159"/>
+    <hyperlink ref="E161" r:id="rId160"/>
+    <hyperlink ref="E162" r:id="rId161"/>
+    <hyperlink ref="E163" r:id="rId162"/>
+    <hyperlink ref="E164" r:id="rId163"/>
+    <hyperlink ref="E165" r:id="rId164"/>
+    <hyperlink ref="E166" r:id="rId165"/>
+    <hyperlink ref="E167" r:id="rId166"/>
+    <hyperlink ref="E168" r:id="rId167"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel-files/atlas-techniques.xlsx
+++ b/excel-files/atlas-techniques.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="905">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="921">
   <si>
     <t>ID</t>
   </si>
@@ -49,6 +49,9 @@
     <t>AML.T0100</t>
   </si>
   <si>
+    <t>AML.T0002.002</t>
+  </si>
+  <si>
     <t>AML.T0080</t>
   </si>
   <si>
@@ -145,6 +148,9 @@
     <t>AML.T0075</t>
   </si>
   <si>
+    <t>AML.T0095.000</t>
+  </si>
+  <si>
     <t>AML.T0050</t>
   </si>
   <si>
@@ -187,6 +193,9 @@
     <t>AML.T0002.000</t>
   </si>
   <si>
+    <t>AML.T0052.001</t>
+  </si>
+  <si>
     <t>AML.T0094</t>
   </si>
   <si>
@@ -550,6 +559,9 @@
     <t>attack-pattern--bd74bd28-20ce-5f69-972e-0afe627b7147</t>
   </si>
   <si>
+    <t>attack-pattern--8eb979a1-1e5a-5955-8a7d-df82ecb14088</t>
+  </si>
+  <si>
     <t>attack-pattern--785ca1b4-7d17-51f1-a605-46a9f21fb9b0</t>
   </si>
   <si>
@@ -646,6 +658,9 @@
     <t>attack-pattern--59fc3797-1686-503b-9212-26e1eecb5a69</t>
   </si>
   <si>
+    <t>attack-pattern--47789eb8-2a21-5a8b-a380-57e17bde15e2</t>
+  </si>
+  <si>
     <t>attack-pattern--07421f1a-a5ae-5936-9713-c77e4758177c</t>
   </si>
   <si>
@@ -688,6 +703,9 @@
     <t>attack-pattern--bbffbb39-c270-5822-8786-7bbab1a43dc3</t>
   </si>
   <si>
+    <t>attack-pattern--d017d9b8-ad90-5b6a-804f-229b342b05a3</t>
+  </si>
+  <si>
     <t>attack-pattern--ced5d1be-a572-58e3-bb3f-9f8c22de02b5</t>
   </si>
   <si>
@@ -1051,6 +1069,9 @@
     <t>AI Agent Clickbait</t>
   </si>
   <si>
+    <t>AI Agent Configuration</t>
+  </si>
+  <si>
     <t>AI Agent Context Poisoning</t>
   </si>
   <si>
@@ -1147,6 +1168,9 @@
     <t>Cloud Service Discovery</t>
   </si>
   <si>
+    <t>Code Repositories</t>
+  </si>
+  <si>
     <t>Command and Scripting Interpreter</t>
   </si>
   <si>
@@ -1187,6 +1211,9 @@
   </si>
   <si>
     <t>Datasets</t>
+  </si>
+  <si>
+    <t>Deepfake-Assisted Phishing</t>
   </si>
   <si>
     <t>Delay Execution of LLM Instructions</t>
@@ -1551,6 +1578,15 @@
   </si>
   <si>
     <t>Adversaries may craft deceptive web content designed to bait Computer-Using AI agents or AI web browsers into taking unintended actions, such as clicking buttons, copying code, or navigating to specific web pages. These attacks exploit the agent's interpretation of UI content, visual cues, or prompt-like language embedded in the site. When successful, they can lead the agent to inadvertently copy and execute malicious code on the user's operating system.</t>
+  </si>
+  <si>
+    <t>Adversaries may acquire publicly accessible AI agent configuration files to understand agent capabilities, gain unauthorized access to tools and data sources, or identify credentials for further attacks. Configuration files define what tools an agent can use, credentials for external services, system prompts, and behavioral settings, making valuable resources for adversaries targeting AI agent deployments.
+Once configuration files are acquired, adversaries may perform [Discover AI Agent Configuration](/techniques/AML.T0084) to gain additional insights they can use in their operation or [Credentials from AI Agent Configuration](/techniques/AML.T0083) to harvest secrets.
+AI agent configuration files come in multiple forms depending on the platform and agent framework. Agent configuration files adversaries may target include:
+- System prompts: Files containing agent instructions, behavioral guidelines, and internal logic.
+- Tool configuration: Files defining tools the agent can utilize, including Model Context Protocol (MCP) configs (e.g., `mcp.json`, `claude_desktop_config.json`), IDE-specific configs (e.g., `.claude/settings.json`, `.vscode/tasks.json`), and framework-specific settings that define external tool and data source integrations.
+- Skills and workflows: Files defining agent capabilities, behaviors, or workflows. Often a combination of instructions, scripts, and resources.
+- Environment and deployment configs: Files that control agent deployment and runtime behavior, often environment variables or framework-specific configs.</t>
   </si>
   <si>
     <t>Adversaries may attempt to manipulate the context used by an AI agent's large language model (LLM) to influence the responses it generates or actions it takes. This allows an adversary to persistently change the behavior of the target agent and further their goals.
@@ -1730,6 +1766,10 @@
 [1]: https://www.sysdig.com/blog/llmjacking-stolen-cloud-credentials-used-in-new-ai-attack</t>
   </si>
   <si>
+    <t>Adversaries may search public code repositories for information about a victim or victim system that can be used during targeting. Victims may store code or artifacts related to their AI systems in repositories on various third-party websites such as GitHub, GitLab, SourceForge, and BitBucket. Adversaries may search code repositories of common AI tools, frameworks, models, or agentic systems that are used--but not owned--by the victim.
+Public code repositories can often be a source of various information about victims, such as commonly used AI frameworks, libraries, models, datasets, agents, and agent tools, as well as the names of employees. Adversaries may also identify more sensitive data, including accidentally leaked credentials or API keys (ex: [Credentials from AI Agent Configuration](/techniques/AML.T0083)). Information from these sources may reveal opportunities for other forms of [Reconnaissance](/tactics/AML.TA0002) (ex: [Gather RAG-Indexed Targets](/techniques/AML.T0064)), establishing operational resources (ex: [Acquire Public AI Artifacts](/techniques/AML.T0002)), [Discovery](/tactics/AML.TA0008) (ex: [Discover AI Agent Configuration](/techniques/AML.T0084)) and/or [Initial Access](/tactics/AML.TA0004) (ex: [Valid Accounts](/techniques/AML.T0012) or [Phishing](/techniques/AML.T0052)).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Adversaries may abuse command and script interpreters to execute commands, scripts, or binaries. These interfaces and languages provide ways of interacting with computer systems and are a common feature across many different platforms. Most systems come with some built-in command-line interface and scripting capabilities, for example, macOS and Linux distributions include some flavor of Unix Shell while Windows installations include the Windows Command Shell and PowerShell.
 There are also cross-platform interpreters such as Python, as well as those commonly associated with client applications such as JavaScript and Visual Basic.
 Adversaries may abuse these technologies in various ways as a means of executing arbitrary commands. Commands and scripts can be embedded in Initial Access payloads delivered to victims as lure documents or as secondary payloads downloaded from an existing C2. Adversaries may also execute commands through interactive terminals/shells, as well as utilize various Remote Services in order to achieve remote Execution.
@@ -1812,6 +1852,29 @@
 Some datasets require the adversary to [Establish Accounts](/techniques/AML.T0021) for access.
 Acquired datasets help the adversary advance their operations, stage attacks,  and tailor attacks to the victim organization.
 </t>
+  </si>
+  <si>
+    <t>Adversaries may use deepfakes (AI-generated synthetic images, audio, or video) in phishing campaigns to impersonate trusted individuals, executives, or organizations. These attacks exploit human trust by presenting fraudulent voice or video communications as legitimate, enabling adversaries to manipulate targets into disclosing credentials, transferring funds, or granting access to systems.
+Voice deepfakes (AI-cloned voices) are used in vishing [\[1\]][vishing] (voice phishing) attacks over telephone or VoIP. Adversaries can clone a target's voice using a few seconds [\[2\]][valle] of publicly available audio from speeches, earnings calls, podcasts, or social media [\[3\]][voice]. These cloned voices are then used in pre-recorded voicemail messages or live phone calls. Video deepfakes can impersonate a trusted individual's face and voice. Adversaries use publicly available video from company meetings, earnings calls, or social media to create convincing AI-generated video of target individuals. They are used in live video conference calls or recorded video messages. AI-generated content has advanced to the point that it is often difficult to identify as synthetic [\[4\]][fbi].
+Adversaries may first perform [Obtain Capabilities](/techniques/AML.T0016): [Generative AI](/techniques/AML.T0016.002) followed by [Generate Deepfakes](/techniques/AML.T0088) in preparation for their [Phishing](/techniques/AML.T0052) campaign. Deepfake phishing campaigns often utilize other communication channels (such as email, SMS, or instant messaging) for layered social engineering attacks [\[5\]][aiid839].
+These attacks span a wide range of victims and attack types, demonstrating the breadth of deepfake-enabled fraud. Adversaries have conducted extensive deepfake-assisted phishing campaigns against the individuals, including targeted scams [\[6\]][aiid564] [\[7\]][oecd1] [\[8\]][aiid1280] [\[9\]][aiid1285], as well as large-scale credential harvesting campaigns targeting billions of users [\[10\]][aiid839] [\[11\]][aiid941]. Adversaries have used deepfakes to impersonate executives [\[12\]][aiid1100], causing business entities to suffer significant financial losses from [\[13\]][aiid634] [\[14\]][aiid147]. There are also reports of government officials being targeted in widespread campaigns [\[4\]][fbi] [\[15\]][aiid927].
+The attacks span communication channels including voice deepfakes for vishing [\[16\]][aiid567] and video deepfakes in conference calls [\[13\]][aiid634], as well as multi-channel campaigns combining phone, email, and messaging platforms [\[10\]][aiid839].
+[valle]: https://www.microsoft.com/en-us/research/project/vall-e-x/ "VALL-E Family: Neural codec language models for speech synthesis"
+[vishing]: https://www.social-engineer.org/framework/attack-vectors/vishing/ "Vishing - Social-Engineer Framework"
+[voice]: https://cloud.google.com/blog/topics/threat-intelligence/ai-powered-voice-spoofing-vishing-attacks "AI-powered voice spoofing: Understanding and defending against vishing attacks"
+[fbi]: https://www.ic3.gov/PSA/2025/PSA250515/ "FBI Public Service Advisory: Scammers are deepfaking voices of senior US government officials"
+[oecd1]: https://oecd.ai/en/incidents/2026-04-06-ca7a "AI-Generated Voice Used in Scam Targeting Drica Moraes' Contacts"
+[oecd2]: https://oecd.ai/en/incidents/2026-03-02-3408 "AI Deepfake Voice Scams Target 1 in 4 Americans"
+[aiid634]: https://incidentdatabase.ai/cite/634/ "Alleged Deepfake CFO Scam Reportedly Costs Multinational Engineering Firm Arup $25 Million"
+[aiid147]: https://incidentdatabase.ai/cite/147/ "Reported AI-Cloned Voice Used to Deceive Hong Kong Bank Manager in Purported $35 Million Fraud Scheme"
+[aiid1100]: https://incidentdatabase.ai/cite/1100/ "AI Incident Database - LastPass CEO Voice Deepfake Attempt"
+[aiid927]: https://incidentdatabase.ai/cite/927/ "Italian Defense Minister Voice Clone"
+[aiid564]: https://incidentdatabase.ai/cite/564/ "Voice deepfake targets bank in failed transfer scam"
+[aiid567]: https://incidentdatabase.ai/cite/567/ "Deepfake Voice Exploit Compromises Retool's Cloud Services"
+[aiid1280]: https://incidentdatabase.ai/cite/1280/ "Reported Use of AI Voice and Identity Manipulation in the 'Phantom Hacker' Fraud Scheme"
+[aiid1285]: https://incidentdatabase.ai/cite/1285/ "Purportedly AI-Generated Jason Momoa Deepfake Used in Romance Scam"
+[aiid839]: https://incidentdatabase.ai/cite/839/ "Purportedly AI-Driven Phishing Scam Uses Spoofed Google Call to Attempt Gmail Breach"
+[aiid941]: https://incidentdatabase.ai/cite/941/ "AI-Driven Phishing Scam Uses Deepfake Robocalls to Target Gmail Users"</t>
   </si>
   <si>
     <t>Adversaries may include instructions to be followed by the AI system in response to a future event, such as a specific keyword or the next interaction, in order to evade detection or bypass controls placed on the AI system.
@@ -2040,10 +2103,33 @@
 </t>
   </si>
   <si>
-    <t>An adversary may target the inputs or the architecture of an LLM, placing it in a state where it will freely respond to user input, bypassing any controls, restrictions, or guardrails placed on the LLM. Once successfully jailbroken, the LLM can be used in unintended ways by the adversary.
-Jailbreaks are classified as either white-box or black-box depending on the level of model access they require. In white-box jailbreaks, the attacker directly exploits the model. Gradient and logit-based attacks use internal signals to select prompts that make harmful answers more likely while fine-tuning-based methods weaken safety through retraining ([Jailbreak Attacks and Defenses: A Survey]; [JailbreakZoo]). Additionally, many large language models encode refusal in a single linear signal in their internal layers; removing or suppressing this signal via an activation edit largely disables refusal while leaving normal skills mostly intact ([Refusal Direction]).
-Black-box jailbreaks, on the other hand, do not require direct model access, relying instead on clever prompting and context tricks. Examples include wrapping a harmful question inside a story, role-play, or code snippet so the model "fills in" the dangerous part as part of the scenario ([Jailbreak Attacks and Defenses: A Survey]) or hiding intent through ciphers, rare languages, and other encodings so the text looks harmless to filters but remains understandable to the model ([JailbreakZoo]; [Jailbreak Attacks and Defenses: A Survey]). Black-box jailbreaks can also take a multi-turn form where attackers engage in dialogue that begins harmless but escalates towards a forbidden goal, changing the conversation history through references and hints while never explicitly stating the malicious request ([Cresendo attacks], [Echo Chamber attack]).
-Jailbreak generation can be automated with fine-tuned models ([MASTERKEY]), multi-agent systems ([Jailbreak Attacks and Defenses: A Survey]), or evolutionary algorithms ([JailbreakZoo]). Aside from fine-tuning, these approaches do not require direct model access.</t>
+    <t>Adversaries may induce a large language model (LLM) to ignore, circumvent, or override its safety/alignment behaviors and/or guardails to elicit outputs the model is intended to withhold. Once jailbroken, the LLM may be used in unintended ways by the adversary. Jailbreaks may be achieved via adversarial prompting, or by modifying model weights or safety mechanisms.
+Adversaries may attempt a jailbreak for [Defense Evasion](/tactics/AML.TA0007) of the LLM's guidelines and guardrails itself to then reveal information (ex: [LLM Data Leakage](/techniques/AML.T0057), [Discover LLM System Information](/techniques/AML.T0069)) or generate harmful content (ex: [Generate Malicious Commands](/techniques/AML.T0102), [Spearphishing via Social Engineering LLM](/techniques/AML.T0052.000)). They may also jailbreak a model for [Privilege Escalation](/tactics/AML.TA0012) to invoke tools or perform actions for their own purposes (ex: [AI Agent Tool Invocation](/techniques/AML.T0053)) or abuse the agent for a [Command and Control](/tactics/AML.TA0014) channel (ex: [AI Agent](/techniques/AML.T0108)).
+Adversaries use a variety of strategies to craft jailbreak prompts. Prompts may target specific models or model families and are iterated upon until successful. Model providers actively update their model guardrails to make them more resistant to jailbreak prompts as new prompts are developed. Common strategies [\[1\]][jailbreak-guide] include but are not limited to:
+- Instruction override: Use phrasing that attempts to supersede prior constraints (e.g. "ignore previous instructions").
+- Roleplay / persona switching: Instruct the LLM to adopt an identity or mode that allows unrestricted answers (e.g. "as a security researcher").
+- Fictionalization and hypotheticals: Instruct the LLM to include disallowed content as part of a story, screenplay, or educational scenario.
+- Separate intent from content: request analysis, examples, templates, or edge cases, that implicitly contain disallowed content.
+- Multi-turn escalation / Crescendo: Utilize a sequence of prompts that start benign, establish trust, then gradually cross policy boundaries with incremental prompts.
+- Constrained output formats: Instruct the LLM to output to a strict schema or format (e.g. JSON, YAML, code, or tables).
+- Obfuscation and transformation: Use encoding, transformations, translation, or euphemisms, (e.g., base64 encoding, "describe it in another language").
+- Create a high priority objective: Frame compliance as necessary to fulfill the user's main task (e.g. "to complete the evaluation," "to follow the spec," "to follow safety guidelines").
+Adversaries may also use algorithmic approaches to generating jailbreak prompts [\[2\]][jailbreak-zoo] [\[3\]][jailbreak-survey]. Algorithmic jailbreak generation allows for automated methods that discover jailbreaks at scale. Some approaches automate manual strategies [\[4\]][autodan] [\[5\]][gptfuzzer] [\[6\]][crescendo] [\[7\]][echo-chamber] while others optimize a string of tokens directly [\[8\]][universal] to produce nonsensical text. Both black-box (applicable to commercial models where the adversary has only query access to the model) and white-box (applicable in the open-source setting, where the adversary has full access to the model weights) optimization approaches are viable.
+Adversaries may also directly manipulate a model's weights, or modify or remove parts of a model to create a jailbroken of "uncensored" variant of the target model. This is applicable to open-source models, or cases where the adversary gains full access to the target model. Approaches include fine-tuning to reduce refusals [\[9\]][single-direction], targeted model editing [\[10\]][rome], addition of adapters [\[11\]][lora], and removing safety mechanisms such as guardrails.
+Jailbreak prompts that are known to work on various classes of LLMs are often published in the open-source community [\[12\]][dan]. Jailbroken or uncensored LLMs that have been trained or fine-tuned to be jailbroken are shared in public model registries such as huggingface [\[13\]][abliteration].
+[jailbreak-survey]: https://arxiv.org/abs/2407.04295 "Jailbreak Attacks and Defenses Against Large Language Models: A Survey"
+[jailbreak-zoo]: https://arxiv.org/abs/2407.01599 "JailbreakZoo: Survey, Landscapes, and Horizons in Jailbreaking Large Language and Vision-Language Models"
+[jailbreak-guide]: https://www.promptfoo.dev/blog/how-to-jailbreak-llms/ "Jailbreaking LLMs: A Comprehensive Guide (With Examples)"
+[autodan]: https://arxiv.org/abs/2310.04451 "AutoDAN: Generating Stealthy Jailbreak Prompts on Aligned Large Language Models"
+[gptfuzzer]: https://arxiv.org/abs/2309.10253 "GPTFUZZER: Red Teaming Large Language Models with Auto-Generated Jailbreak Prompts"
+[crescendo]: https://arxiv.org/abs/2404.01833 "Great, Now Write an Article About That: The Crescendo Multi-Turn LLM Jailbreak Attack"
+[echo-chamber]: https://arxiv.org/abs/2601.05742 "The Echo Chamber Multi-Turn LLM Jailbreak"
+[dan]: https://github.com/0xk1h0/ChatGPT_DAN "ChatGPT DAN"
+[rome]: https://arxiv.org/abs/2202.05262 "Locating and Editing Factual Associations in GPT"
+[universal]: https://arxiv.org/abs/2307.15043 "Universal and Transferable Adversarial Attacks on Aligned Language Models"
+[single-direction]: https://arxiv.org/abs/2406.11717 "Refusal in Language Models Is Mediated by a Single Direction"
+[lora]: https://arxiv.org/abs/2310.20624 "LoRA Fine-tuning Efficiently Undoes Safety Training in Llama 2-Chat 70B"
+[abliteration]: https://huggingface.co/blog/mlabonne/abliteration "Uncensor any LLM with abliteration"</t>
   </si>
   <si>
     <t>Adversaries may use their acquired knowledge of the target generative AI system to craft prompts that bypass its defenses and allow malicious instructions to be executed.
@@ -2154,9 +2240,8 @@
 Capabilities may be specific to AI-based attacks [Adversarial AI Attack Implementations](/techniques/AML.T0016.000) or generic software tools repurposed for malicious intent ([Software Tools](/techniques/AML.T0016.001)). In both instances, an adversary may modify or customize the capability to aid in targeting a particular AI-enabled system.</t>
   </si>
   <si>
-    <t xml:space="preserve">Adversaries may send phishing messages to gain access to victim systems. All forms of phishing are electronically delivered social engineering. Phishing can be targeted, known as spearphishing. In spearphishing, a specific individual, company, or industry will be targeted by the adversary. More generally, adversaries can conduct non-targeted phishing, such as in mass malware spam campaigns.
-Generative AI, including LLMs that generate synthetic text, visual deepfakes of faces, and audio deepfakes of speech, is enabling adversaries to scale targeted phishing campaigns. LLMs can interact with users via text conversations and can be programmed with a meta prompt to phish for sensitive information. Deepfakes can be use in impersonation as an aid to phishing.
-</t>
+    <t>Adversaries may send phishing messages to gain access to victim systems. All forms of phishing are electronically delivered social engineering. Phishing can be targeted, known as spearphishing. In spearphishing, a specific individual, company, or industry will be targeted by the adversary. More generally, adversaries can conduct non-targeted phishing, such as in mass malware spam campaigns.
+Generative AI, including LLMs that generate synthetic text, visual deepfakes of faces, and audio deepfakes of speech (See [Generate Deepfakes](/techniques/AML.T0088)), is enabling adversaries to scale targeted phishing campaigns (See [Spearphishing via Social Engineering LLM](/techniques/AML.T0052.000)). LLMs can interact with users via text conversations and can be programmed with a system prompt to phish for sensitive information. Deepfakes can also be used in [Impersonation](/techniques/AML.T0073) as an aid to phishing.</t>
   </si>
   <si>
     <t>Adversaries may acquire or manufacture physical countermeasures to aid or support their attack.
@@ -2413,6 +2498,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0100</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0002.002</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0080</t>
   </si>
   <si>
@@ -2509,6 +2597,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0075</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0095.000</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0050</t>
   </si>
   <si>
@@ -2551,6 +2642,9 @@
     <t>https://atlas.mitre.org/techniques/AML.T0002.000</t>
   </si>
   <si>
+    <t>https://atlas.mitre.org/techniques/AML.T0052.001</t>
+  </si>
+  <si>
     <t>https://atlas.mitre.org/techniques/AML.T0094</t>
   </si>
   <si>
@@ -2914,6 +3008,9 @@
     <t>25 November 2025</t>
   </si>
   <si>
+    <t>22 April 2026</t>
+  </si>
+  <si>
     <t>30 September 2025</t>
   </si>
   <si>
@@ -2992,6 +3089,9 @@
     <t>12 January 2024</t>
   </si>
   <si>
+    <t>30 April 2026</t>
+  </si>
+  <si>
     <t>12 October 2023</t>
   </si>
   <si>
@@ -3004,9 +3104,6 @@
     <t>06 November 2025</t>
   </si>
   <si>
-    <t>20 December 2025</t>
-  </si>
-  <si>
     <t>18 December 2025</t>
   </si>
   <si>
@@ -3019,9 +3116,15 @@
     <t>Execution</t>
   </si>
   <si>
+    <t>Resource Development</t>
+  </si>
+  <si>
     <t>Persistence</t>
   </si>
   <si>
+    <t>Initial Access</t>
+  </si>
+  <si>
     <t>Credential Access</t>
   </si>
   <si>
@@ -3034,15 +3137,9 @@
     <t>Impact</t>
   </si>
   <si>
-    <t>Resource Development</t>
-  </si>
-  <si>
     <t>AI Model Access</t>
   </si>
   <si>
-    <t>Initial Access</t>
-  </si>
-  <si>
     <t>Defense Evasion</t>
   </si>
   <si>
@@ -3052,9 +3149,18 @@
     <t>Reconnaissance</t>
   </si>
   <si>
+    <t>Lateral Movement</t>
+  </si>
+  <si>
     <t>AI Attack Staging</t>
   </si>
   <si>
+    <t>Initial Access, Lateral Movement</t>
+  </si>
+  <si>
+    <t>AI Attack Staging, Persistence</t>
+  </si>
+  <si>
     <t>Privilege Escalation</t>
   </si>
   <si>
@@ -3067,22 +3173,13 @@
     <t>Defense Evasion, Privilege Escalation</t>
   </si>
   <si>
-    <t>AI Attack Staging, Persistence</t>
-  </si>
-  <si>
     <t>Defense Evasion, Persistence</t>
   </si>
   <si>
-    <t>Initial Access, Lateral Movement</t>
-  </si>
-  <si>
     <t>Persistence, Resource Development</t>
   </si>
   <si>
     <t>Initial Access, Persistence</t>
-  </si>
-  <si>
-    <t>Lateral Movement</t>
   </si>
   <si>
     <t>Initial Access, Privilege Escalation</t>
@@ -3459,7 +3556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I168"/>
+  <dimension ref="A1:I171"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -3496,28 +3593,28 @@
         <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D2" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="F2" t="s">
-        <v>844</v>
+        <v>859</v>
       </c>
       <c r="G2" t="s">
-        <v>867</v>
+        <v>883</v>
       </c>
       <c r="H2" t="s">
-        <v>879</v>
+        <v>895</v>
       </c>
       <c r="I2" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -3525,28 +3622,28 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="D3" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="F3" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="G3" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="H3" t="s">
-        <v>880</v>
+        <v>896</v>
       </c>
       <c r="I3" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3554,28 +3651,28 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D4" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="F4" t="s">
-        <v>846</v>
+        <v>861</v>
       </c>
       <c r="G4" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="H4" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="I4" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3583,28 +3680,28 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C5" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="D5" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="F5" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="G5" t="s">
-        <v>847</v>
+        <v>884</v>
       </c>
       <c r="H5" t="s">
-        <v>881</v>
+        <v>898</v>
       </c>
       <c r="I5" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3612,28 +3709,28 @@
         <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D6" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="F6" t="s">
-        <v>845</v>
+        <v>863</v>
       </c>
       <c r="G6" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="H6" t="s">
-        <v>882</v>
+        <v>899</v>
       </c>
       <c r="I6" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3641,28 +3738,28 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C7" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="D7" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="F7" t="s">
-        <v>845</v>
+        <v>860</v>
       </c>
       <c r="G7" t="s">
-        <v>845</v>
+        <v>885</v>
       </c>
       <c r="H7" t="s">
-        <v>881</v>
+        <v>900</v>
       </c>
       <c r="I7" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3670,28 +3767,28 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C8" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="D8" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="F8" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
       <c r="G8" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="H8" t="s">
-        <v>883</v>
+        <v>898</v>
       </c>
       <c r="I8" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3699,28 +3796,28 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D9" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F9" t="s">
-        <v>847</v>
+        <v>864</v>
       </c>
       <c r="G9" t="s">
-        <v>847</v>
+        <v>873</v>
       </c>
       <c r="H9" t="s">
-        <v>881</v>
+        <v>901</v>
       </c>
       <c r="I9" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3728,28 +3825,28 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C10" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="D10" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="F10" t="s">
-        <v>846</v>
+        <v>863</v>
       </c>
       <c r="G10" t="s">
-        <v>846</v>
+        <v>863</v>
       </c>
       <c r="H10" t="s">
-        <v>884</v>
+        <v>898</v>
       </c>
       <c r="I10" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3757,28 +3854,28 @@
         <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C11" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D11" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="F11" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G11" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="H11" t="s">
-        <v>884</v>
+        <v>902</v>
       </c>
       <c r="I11" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3786,28 +3883,28 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C12" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="D12" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="F12" t="s">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="G12" t="s">
-        <v>847</v>
+        <v>876</v>
       </c>
       <c r="H12" t="s">
-        <v>885</v>
+        <v>902</v>
       </c>
       <c r="I12" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -3815,28 +3912,28 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C13" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="D13" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="F13" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G13" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H13" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
       <c r="I13" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -3844,28 +3941,28 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C14" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D14" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="F14" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G14" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="H14" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="I14" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -3873,28 +3970,28 @@
         <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C15" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="D15" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
       <c r="F15" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G15" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H15" t="s">
-        <v>887</v>
+        <v>903</v>
       </c>
       <c r="I15" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -3902,28 +3999,28 @@
         <v>23</v>
       </c>
       <c r="B16" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C16" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="D16" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>691</v>
+        <v>703</v>
       </c>
       <c r="F16" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="G16" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="H16" t="s">
-        <v>879</v>
+        <v>904</v>
       </c>
       <c r="I16" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -3931,28 +4028,28 @@
         <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C17" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D17" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>692</v>
+        <v>704</v>
       </c>
       <c r="F17" t="s">
-        <v>847</v>
+        <v>866</v>
       </c>
       <c r="G17" t="s">
-        <v>847</v>
+        <v>886</v>
       </c>
       <c r="H17" t="s">
-        <v>885</v>
+        <v>895</v>
       </c>
       <c r="I17" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -3960,28 +4057,28 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C18" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="D18" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="F18" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G18" t="s">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="H18" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="I18" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -3989,28 +4086,28 @@
         <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C19" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="D19" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
       <c r="F19" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G19" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H19" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="I19" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -4018,28 +4115,28 @@
         <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C20" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="D20" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="F20" t="s">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="G20" t="s">
-        <v>847</v>
+        <v>876</v>
       </c>
       <c r="H20" t="s">
-        <v>889</v>
+        <v>899</v>
       </c>
       <c r="I20" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -4047,28 +4144,28 @@
         <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C21" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="D21" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>696</v>
+        <v>708</v>
       </c>
       <c r="F21" t="s">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="G21" t="s">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="H21" t="s">
-        <v>889</v>
+        <v>905</v>
       </c>
       <c r="I21" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -4076,28 +4173,28 @@
         <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C22" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D22" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="F22" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G22" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H22" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="I22" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -4105,28 +4202,28 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="C23" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D23" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
       <c r="F23" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G23" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H23" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="I23" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -4134,28 +4231,28 @@
         <v>31</v>
       </c>
       <c r="B24" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C24" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D24" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="F24" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G24" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="H24" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="I24" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -4163,28 +4260,28 @@
         <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C25" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="D25" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="F25" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="G25" t="s">
-        <v>846</v>
+        <v>876</v>
       </c>
       <c r="H25" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="I25" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -4192,28 +4289,28 @@
         <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C26" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="D26" t="s">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="F26" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G26" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="H26" t="s">
-        <v>891</v>
+        <v>906</v>
       </c>
       <c r="I26" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -4221,28 +4318,28 @@
         <v>34</v>
       </c>
       <c r="B27" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C27" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="D27" t="s">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="F27" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G27" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="H27" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="I27" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -4250,28 +4347,28 @@
         <v>35</v>
       </c>
       <c r="B28" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C28" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D28" t="s">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
       <c r="F28" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G28" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="H28" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="I28" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -4279,28 +4376,28 @@
         <v>36</v>
       </c>
       <c r="B29" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C29" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="D29" t="s">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="F29" t="s">
-        <v>847</v>
+        <v>864</v>
       </c>
       <c r="G29" t="s">
-        <v>847</v>
+        <v>876</v>
       </c>
       <c r="H29" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="I29" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -4308,28 +4405,28 @@
         <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C30" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D30" t="s">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="F30" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="G30" t="s">
-        <v>870</v>
+        <v>863</v>
       </c>
       <c r="H30" t="s">
-        <v>889</v>
+        <v>903</v>
       </c>
       <c r="I30" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -4337,28 +4434,28 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C31" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="D31" t="s">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="F31" t="s">
-        <v>849</v>
+        <v>867</v>
       </c>
       <c r="G31" t="s">
-        <v>849</v>
+        <v>886</v>
       </c>
       <c r="H31" t="s">
-        <v>892</v>
+        <v>908</v>
       </c>
       <c r="I31" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -4366,28 +4463,28 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C32" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D32" t="s">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
       <c r="F32" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G32" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="H32" t="s">
-        <v>892</v>
+        <v>909</v>
       </c>
       <c r="I32" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -4395,28 +4492,28 @@
         <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C33" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D33" t="s">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="F33" t="s">
-        <v>847</v>
+        <v>865</v>
       </c>
       <c r="G33" t="s">
-        <v>847</v>
+        <v>887</v>
       </c>
       <c r="H33" t="s">
-        <v>881</v>
+        <v>909</v>
       </c>
       <c r="I33" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -4424,28 +4521,28 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C34" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D34" t="s">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="F34" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="G34" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="H34" t="s">
-        <v>889</v>
+        <v>906</v>
       </c>
       <c r="I34" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -4453,28 +4550,28 @@
         <v>42</v>
       </c>
       <c r="B35" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C35" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="D35" t="s">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="F35" t="s">
-        <v>853</v>
+        <v>868</v>
       </c>
       <c r="G35" t="s">
-        <v>850</v>
+        <v>868</v>
       </c>
       <c r="H35" t="s">
-        <v>890</v>
+        <v>905</v>
       </c>
       <c r="I35" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -4482,28 +4579,28 @@
         <v>43</v>
       </c>
       <c r="B36" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C36" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D36" t="s">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
       <c r="F36" t="s">
-        <v>854</v>
+        <v>869</v>
       </c>
       <c r="G36" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="H36" t="s">
-        <v>880</v>
+        <v>906</v>
       </c>
       <c r="I36" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -4511,28 +4608,28 @@
         <v>44</v>
       </c>
       <c r="B37" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C37" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="D37" t="s">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="F37" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="G37" t="s">
-        <v>849</v>
+        <v>888</v>
       </c>
       <c r="H37" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="I37" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -4540,28 +4637,28 @@
         <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C38" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D38" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="F38" t="s">
-        <v>855</v>
+        <v>870</v>
       </c>
       <c r="G38" t="s">
-        <v>855</v>
+        <v>889</v>
       </c>
       <c r="H38" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="I38" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -4569,28 +4666,28 @@
         <v>46</v>
       </c>
       <c r="B39" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C39" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="D39" t="s">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="F39" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="G39" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="H39" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="I39" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -4598,28 +4695,28 @@
         <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C40" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D40" t="s">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
       <c r="F40" t="s">
-        <v>849</v>
+        <v>871</v>
       </c>
       <c r="G40" t="s">
-        <v>847</v>
+        <v>871</v>
       </c>
       <c r="H40" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="I40" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -4627,28 +4724,28 @@
         <v>48</v>
       </c>
       <c r="B41" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C41" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="D41" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="F41" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="G41" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="H41" t="s">
-        <v>892</v>
+        <v>905</v>
       </c>
       <c r="I41" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -4656,28 +4753,28 @@
         <v>49</v>
       </c>
       <c r="B42" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C42" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="D42" t="s">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="F42" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G42" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H42" t="s">
-        <v>892</v>
+        <v>903</v>
       </c>
       <c r="I42" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -4685,28 +4782,28 @@
         <v>50</v>
       </c>
       <c r="B43" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C43" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D43" t="s">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="F43" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="G43" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="H43" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I43" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -4714,28 +4811,28 @@
         <v>51</v>
       </c>
       <c r="B44" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C44" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D44" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="F44" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G44" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="H44" t="s">
-        <v>888</v>
+        <v>909</v>
       </c>
       <c r="I44" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -4743,28 +4840,28 @@
         <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C45" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D45" t="s">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="F45" t="s">
-        <v>845</v>
+        <v>862</v>
       </c>
       <c r="G45" t="s">
-        <v>845</v>
+        <v>884</v>
       </c>
       <c r="H45" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="I45" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -4772,28 +4869,28 @@
         <v>53</v>
       </c>
       <c r="B46" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C46" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D46" t="s">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="F46" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="G46" t="s">
-        <v>857</v>
+        <v>876</v>
       </c>
       <c r="H46" t="s">
-        <v>884</v>
+        <v>899</v>
       </c>
       <c r="I46" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -4801,28 +4898,28 @@
         <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C47" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D47" t="s">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="F47" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="G47" t="s">
-        <v>873</v>
+        <v>860</v>
       </c>
       <c r="H47" t="s">
-        <v>884</v>
+        <v>903</v>
       </c>
       <c r="I47" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -4830,28 +4927,28 @@
         <v>55</v>
       </c>
       <c r="B48" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C48" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="D48" t="s">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
       <c r="F48" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G48" t="s">
         <v>873</v>
       </c>
       <c r="H48" t="s">
-        <v>884</v>
+        <v>902</v>
       </c>
       <c r="I48" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -4859,28 +4956,28 @@
         <v>56</v>
       </c>
       <c r="B49" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C49" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="D49" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="F49" t="s">
-        <v>849</v>
+        <v>872</v>
       </c>
       <c r="G49" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
       <c r="H49" t="s">
-        <v>886</v>
+        <v>902</v>
       </c>
       <c r="I49" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -4888,28 +4985,28 @@
         <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C50" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="D50" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="F50" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="G50" t="s">
-        <v>866</v>
+        <v>890</v>
       </c>
       <c r="H50" t="s">
-        <v>889</v>
+        <v>902</v>
       </c>
       <c r="I50" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -4917,28 +5014,28 @@
         <v>58</v>
       </c>
       <c r="B51" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C51" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D51" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="F51" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G51" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="H51" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="I51" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -4946,28 +5043,28 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C52" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D52" t="s">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
       <c r="F52" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="G52" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="H52" t="s">
-        <v>880</v>
+        <v>910</v>
       </c>
       <c r="I52" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -4975,28 +5072,28 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C53" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="D53" t="s">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="F53" t="s">
-        <v>848</v>
+        <v>873</v>
       </c>
       <c r="G53" t="s">
-        <v>860</v>
+        <v>882</v>
       </c>
       <c r="H53" t="s">
-        <v>886</v>
+        <v>905</v>
       </c>
       <c r="I53" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -5004,28 +5101,28 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C54" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D54" t="s">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="F54" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G54" t="s">
-        <v>848</v>
+        <v>876</v>
       </c>
       <c r="H54" t="s">
-        <v>880</v>
+        <v>903</v>
       </c>
       <c r="I54" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -5033,28 +5130,28 @@
         <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C55" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D55" t="s">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="F55" t="s">
-        <v>846</v>
+        <v>874</v>
       </c>
       <c r="G55" t="s">
-        <v>846</v>
+        <v>874</v>
       </c>
       <c r="H55" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="I55" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -5062,28 +5159,28 @@
         <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C56" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D56" t="s">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
       <c r="F56" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="G56" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="H56" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="I56" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -5091,28 +5188,28 @@
         <v>64</v>
       </c>
       <c r="B57" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C57" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="D57" t="s">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="F57" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="G57" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="H57" t="s">
-        <v>890</v>
+        <v>896</v>
       </c>
       <c r="I57" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -5120,28 +5217,28 @@
         <v>65</v>
       </c>
       <c r="B58" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C58" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="D58" t="s">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="F58" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G58" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="H58" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I58" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -5149,28 +5246,28 @@
         <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C59" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D59" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="F59" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G59" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H59" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I59" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -5178,28 +5275,28 @@
         <v>67</v>
       </c>
       <c r="B60" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C60" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D60" t="s">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="F60" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G60" t="s">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c r="H60" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I60" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -5207,28 +5304,28 @@
         <v>68</v>
       </c>
       <c r="B61" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="C61" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="D61" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="F61" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G61" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H61" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I61" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -5236,28 +5333,28 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C62" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D62" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="F62" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G62" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="H62" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I62" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -5265,28 +5362,28 @@
         <v>70</v>
       </c>
       <c r="B63" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C63" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="D63" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
       <c r="F63" t="s">
-        <v>859</v>
+        <v>868</v>
       </c>
       <c r="G63" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="H63" t="s">
-        <v>888</v>
+        <v>906</v>
       </c>
       <c r="I63" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -5294,28 +5391,28 @@
         <v>71</v>
       </c>
       <c r="B64" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C64" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D64" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="F64" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="G64" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="H64" t="s">
-        <v>889</v>
+        <v>906</v>
       </c>
       <c r="I64" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -5323,28 +5420,28 @@
         <v>72</v>
       </c>
       <c r="B65" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C65" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D65" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="F65" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="G65" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="H65" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="I65" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -5352,28 +5449,28 @@
         <v>73</v>
       </c>
       <c r="B66" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C66" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="D66" t="s">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="F66" t="s">
-        <v>849</v>
+        <v>875</v>
       </c>
       <c r="G66" t="s">
-        <v>860</v>
+        <v>891</v>
       </c>
       <c r="H66" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="I66" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -5381,28 +5478,28 @@
         <v>74</v>
       </c>
       <c r="B67" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C67" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="D67" t="s">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="F67" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="G67" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H67" t="s">
-        <v>885</v>
+        <v>911</v>
       </c>
       <c r="I67" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -5410,28 +5507,28 @@
         <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C68" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="D68" t="s">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="F68" t="s">
-        <v>844</v>
+        <v>862</v>
       </c>
       <c r="G68" t="s">
-        <v>844</v>
+        <v>862</v>
       </c>
       <c r="H68" t="s">
-        <v>893</v>
+        <v>906</v>
       </c>
       <c r="I68" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -5439,28 +5536,28 @@
         <v>76</v>
       </c>
       <c r="B69" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C69" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D69" t="s">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
       <c r="F69" t="s">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="G69" t="s">
-        <v>873</v>
+        <v>876</v>
       </c>
       <c r="H69" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
       <c r="I69" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -5468,28 +5565,28 @@
         <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C70" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D70" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="F70" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="G70" t="s">
-        <v>857</v>
+        <v>868</v>
       </c>
       <c r="H70" t="s">
-        <v>894</v>
+        <v>903</v>
       </c>
       <c r="I70" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -5497,28 +5594,28 @@
         <v>78</v>
       </c>
       <c r="B71" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C71" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="D71" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="F71" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="G71" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="H71" t="s">
-        <v>881</v>
+        <v>912</v>
       </c>
       <c r="I71" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -5526,28 +5623,28 @@
         <v>79</v>
       </c>
       <c r="B72" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C72" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D72" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
       <c r="F72" t="s">
-        <v>846</v>
+        <v>872</v>
       </c>
       <c r="G72" t="s">
-        <v>847</v>
+        <v>890</v>
       </c>
       <c r="H72" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="I72" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -5555,28 +5652,28 @@
         <v>80</v>
       </c>
       <c r="B73" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C73" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D73" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="F73" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G73" t="s">
-        <v>860</v>
+        <v>873</v>
       </c>
       <c r="H73" t="s">
-        <v>895</v>
+        <v>913</v>
       </c>
       <c r="I73" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -5584,28 +5681,28 @@
         <v>81</v>
       </c>
       <c r="B74" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C74" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="D74" t="s">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="F74" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G74" t="s">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="H74" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="I74" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -5613,28 +5710,28 @@
         <v>82</v>
       </c>
       <c r="B75" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C75" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D75" t="s">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
       <c r="F75" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="G75" t="s">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="H75" t="s">
-        <v>888</v>
+        <v>914</v>
       </c>
       <c r="I75" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -5642,28 +5739,28 @@
         <v>83</v>
       </c>
       <c r="B76" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C76" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="D76" t="s">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="F76" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="G76" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="H76" t="s">
-        <v>882</v>
+        <v>914</v>
       </c>
       <c r="I76" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -5671,28 +5768,28 @@
         <v>84</v>
       </c>
       <c r="B77" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C77" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D77" t="s">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="F77" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="G77" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="H77" t="s">
-        <v>889</v>
+        <v>914</v>
       </c>
       <c r="I77" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -5700,28 +5797,28 @@
         <v>85</v>
       </c>
       <c r="B78" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C78" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="D78" t="s">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
       <c r="F78" t="s">
-        <v>861</v>
+        <v>870</v>
       </c>
       <c r="G78" t="s">
-        <v>848</v>
+        <v>870</v>
       </c>
       <c r="H78" t="s">
-        <v>885</v>
+        <v>899</v>
       </c>
       <c r="I78" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -5729,28 +5826,28 @@
         <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C79" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="D79" t="s">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="F79" t="s">
-        <v>849</v>
+        <v>859</v>
       </c>
       <c r="G79" t="s">
-        <v>870</v>
+        <v>883</v>
       </c>
       <c r="H79" t="s">
-        <v>895</v>
+        <v>900</v>
       </c>
       <c r="I79" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -5758,28 +5855,28 @@
         <v>87</v>
       </c>
       <c r="B80" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C80" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D80" t="s">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="F80" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="G80" t="s">
-        <v>852</v>
+        <v>883</v>
       </c>
       <c r="H80" t="s">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="I80" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -5787,28 +5884,28 @@
         <v>88</v>
       </c>
       <c r="B81" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C81" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D81" t="s">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
       <c r="F81" t="s">
-        <v>852</v>
+        <v>877</v>
       </c>
       <c r="G81" t="s">
-        <v>850</v>
+        <v>864</v>
       </c>
       <c r="H81" t="s">
-        <v>889</v>
+        <v>903</v>
       </c>
       <c r="I81" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -5816,28 +5913,28 @@
         <v>89</v>
       </c>
       <c r="B82" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C82" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="D82" t="s">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="F82" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G82" t="s">
-        <v>848</v>
+        <v>886</v>
       </c>
       <c r="H82" t="s">
-        <v>885</v>
+        <v>914</v>
       </c>
       <c r="I82" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -5845,28 +5942,28 @@
         <v>90</v>
       </c>
       <c r="B83" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C83" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="D83" t="s">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="F83" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="G83" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="H83" t="s">
-        <v>887</v>
+        <v>914</v>
       </c>
       <c r="I83" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -5874,28 +5971,28 @@
         <v>91</v>
       </c>
       <c r="B84" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="D84" t="s">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="F84" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G84" t="s">
-        <v>852</v>
+        <v>866</v>
       </c>
       <c r="H84" t="s">
-        <v>891</v>
+        <v>905</v>
       </c>
       <c r="I84" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -5903,28 +6000,28 @@
         <v>92</v>
       </c>
       <c r="B85" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C85" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="D85" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
       <c r="F85" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G85" t="s">
         <v>864</v>
       </c>
       <c r="H85" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="I85" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -5932,28 +6029,28 @@
         <v>93</v>
       </c>
       <c r="B86" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="D86" t="s">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="F86" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="G86" t="s">
-        <v>857</v>
+        <v>876</v>
       </c>
       <c r="H86" t="s">
-        <v>892</v>
+        <v>904</v>
       </c>
       <c r="I86" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -5961,28 +6058,28 @@
         <v>94</v>
       </c>
       <c r="B87" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C87" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="D87" t="s">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="F87" t="s">
-        <v>845</v>
+        <v>868</v>
       </c>
       <c r="G87" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="H87" t="s">
-        <v>892</v>
+        <v>907</v>
       </c>
       <c r="I87" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -5990,28 +6087,28 @@
         <v>95</v>
       </c>
       <c r="B88" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C88" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="D88" t="s">
-        <v>596</v>
+        <v>605</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="F88" t="s">
-        <v>852</v>
+        <v>878</v>
       </c>
       <c r="G88" t="s">
-        <v>870</v>
+        <v>880</v>
       </c>
       <c r="H88" t="s">
-        <v>890</v>
+        <v>907</v>
       </c>
       <c r="I88" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -6019,28 +6116,28 @@
         <v>96</v>
       </c>
       <c r="B89" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C89" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="D89" t="s">
-        <v>597</v>
+        <v>606</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
       <c r="F89" t="s">
-        <v>849</v>
+        <v>878</v>
       </c>
       <c r="G89" t="s">
-        <v>852</v>
+        <v>873</v>
       </c>
       <c r="H89" t="s">
-        <v>888</v>
+        <v>909</v>
       </c>
       <c r="I89" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -6048,28 +6145,28 @@
         <v>97</v>
       </c>
       <c r="B90" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C90" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D90" t="s">
-        <v>598</v>
+        <v>607</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="F90" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="G90" t="s">
-        <v>853</v>
+        <v>886</v>
       </c>
       <c r="H90" t="s">
-        <v>889</v>
+        <v>909</v>
       </c>
       <c r="I90" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -6077,28 +6174,28 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C91" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="D91" t="s">
-        <v>599</v>
+        <v>608</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="F91" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="G91" t="s">
-        <v>848</v>
+        <v>886</v>
       </c>
       <c r="H91" t="s">
-        <v>880</v>
+        <v>897</v>
       </c>
       <c r="I91" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -6106,28 +6203,28 @@
         <v>99</v>
       </c>
       <c r="B92" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C92" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="D92" t="s">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="F92" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G92" t="s">
-        <v>875</v>
+        <v>868</v>
       </c>
       <c r="H92" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="I92" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -6135,28 +6232,28 @@
         <v>100</v>
       </c>
       <c r="B93" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C93" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="D93" t="s">
-        <v>601</v>
+        <v>610</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
       <c r="F93" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="G93" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="H93" t="s">
-        <v>892</v>
+        <v>905</v>
       </c>
       <c r="I93" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -6164,28 +6261,28 @@
         <v>101</v>
       </c>
       <c r="B94" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="C94" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="D94" t="s">
-        <v>602</v>
+        <v>611</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="F94" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="G94" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="H94" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I94" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -6193,28 +6290,28 @@
         <v>102</v>
       </c>
       <c r="B95" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C95" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="D95" t="s">
-        <v>603</v>
+        <v>612</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="F95" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G95" t="s">
-        <v>860</v>
+        <v>892</v>
       </c>
       <c r="H95" t="s">
-        <v>891</v>
+        <v>914</v>
       </c>
       <c r="I95" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -6222,28 +6319,28 @@
         <v>103</v>
       </c>
       <c r="B96" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="C96" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="D96" t="s">
-        <v>604</v>
+        <v>613</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="F96" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G96" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="H96" t="s">
-        <v>895</v>
+        <v>909</v>
       </c>
       <c r="I96" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -6251,28 +6348,28 @@
         <v>104</v>
       </c>
       <c r="B97" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C97" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="D97" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
       <c r="F97" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G97" t="s">
-        <v>847</v>
+        <v>876</v>
       </c>
       <c r="H97" t="s">
-        <v>896</v>
+        <v>914</v>
       </c>
       <c r="I97" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -6280,28 +6377,28 @@
         <v>105</v>
       </c>
       <c r="B98" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C98" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="D98" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="F98" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G98" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H98" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="I98" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -6309,28 +6406,28 @@
         <v>106</v>
       </c>
       <c r="B99" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C99" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="D99" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="F99" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="G99" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="H99" t="s">
-        <v>880</v>
+        <v>914</v>
       </c>
       <c r="I99" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -6338,28 +6435,28 @@
         <v>107</v>
       </c>
       <c r="B100" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C100" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D100" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="F100" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="G100" t="s">
-        <v>858</v>
+        <v>888</v>
       </c>
       <c r="H100" t="s">
-        <v>889</v>
+        <v>915</v>
       </c>
       <c r="I100" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -6367,28 +6464,28 @@
         <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C101" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="D101" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="F101" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G101" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="H101" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="I101" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6396,28 +6493,28 @@
         <v>109</v>
       </c>
       <c r="B102" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C102" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="D102" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="F102" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="G102" t="s">
-        <v>863</v>
+        <v>882</v>
       </c>
       <c r="H102" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="I102" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -6425,28 +6522,28 @@
         <v>110</v>
       </c>
       <c r="B103" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C103" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D103" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="F103" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G103" t="s">
-        <v>852</v>
+        <v>874</v>
       </c>
       <c r="H103" t="s">
-        <v>889</v>
+        <v>905</v>
       </c>
       <c r="I103" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -6454,28 +6551,28 @@
         <v>111</v>
       </c>
       <c r="B104" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C104" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D104" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="F104" t="s">
-        <v>847</v>
+        <v>868</v>
       </c>
       <c r="G104" t="s">
-        <v>847</v>
+        <v>868</v>
       </c>
       <c r="H104" t="s">
-        <v>885</v>
+        <v>898</v>
       </c>
       <c r="I104" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6483,28 +6580,28 @@
         <v>112</v>
       </c>
       <c r="B105" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C105" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D105" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="F105" t="s">
-        <v>847</v>
+        <v>879</v>
       </c>
       <c r="G105" t="s">
-        <v>847</v>
+        <v>879</v>
       </c>
       <c r="H105" t="s">
-        <v>885</v>
+        <v>914</v>
       </c>
       <c r="I105" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6512,28 +6609,28 @@
         <v>113</v>
       </c>
       <c r="B106" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C106" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="D106" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="F106" t="s">
-        <v>844</v>
+        <v>868</v>
       </c>
       <c r="G106" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H106" t="s">
-        <v>886</v>
+        <v>905</v>
       </c>
       <c r="I106" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6541,28 +6638,28 @@
         <v>114</v>
       </c>
       <c r="B107" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C107" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D107" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="F107" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="G107" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="H107" t="s">
-        <v>885</v>
+        <v>903</v>
       </c>
       <c r="I107" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -6570,28 +6667,28 @@
         <v>115</v>
       </c>
       <c r="B108" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C108" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="D108" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="F108" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G108" t="s">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="H108" t="s">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="I108" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -6599,28 +6696,28 @@
         <v>116</v>
       </c>
       <c r="B109" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C109" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="D109" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
       <c r="F109" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="G109" t="s">
-        <v>857</v>
+        <v>883</v>
       </c>
       <c r="H109" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="I109" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -6628,28 +6725,28 @@
         <v>117</v>
       </c>
       <c r="B110" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C110" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D110" t="s">
-        <v>618</v>
+        <v>627</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="F110" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="G110" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="H110" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="I110" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -6657,28 +6754,28 @@
         <v>118</v>
       </c>
       <c r="B111" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C111" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="D111" t="s">
-        <v>619</v>
+        <v>628</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="F111" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="G111" t="s">
-        <v>853</v>
+        <v>869</v>
       </c>
       <c r="H111" t="s">
-        <v>889</v>
+        <v>911</v>
       </c>
       <c r="I111" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -6686,28 +6783,28 @@
         <v>119</v>
       </c>
       <c r="B112" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C112" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="D112" t="s">
-        <v>620</v>
+        <v>629</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="F112" t="s">
-        <v>846</v>
+        <v>880</v>
       </c>
       <c r="G112" t="s">
-        <v>846</v>
+        <v>873</v>
       </c>
       <c r="H112" t="s">
-        <v>881</v>
+        <v>905</v>
       </c>
       <c r="I112" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -6715,28 +6812,28 @@
         <v>120</v>
       </c>
       <c r="B113" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="C113" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="D113" t="s">
-        <v>621</v>
+        <v>630</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
       <c r="F113" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G113" t="s">
-        <v>860</v>
+        <v>865</v>
       </c>
       <c r="H113" t="s">
-        <v>888</v>
+        <v>909</v>
       </c>
       <c r="I113" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -6744,28 +6841,28 @@
         <v>121</v>
       </c>
       <c r="B114" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C114" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="D114" t="s">
-        <v>622</v>
+        <v>631</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="F114" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="G114" t="s">
-        <v>854</v>
+        <v>869</v>
       </c>
       <c r="H114" t="s">
-        <v>886</v>
+        <v>905</v>
       </c>
       <c r="I114" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -6773,28 +6870,28 @@
         <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C115" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D115" t="s">
-        <v>623</v>
+        <v>632</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="F115" t="s">
-        <v>846</v>
+        <v>862</v>
       </c>
       <c r="G115" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="H115" t="s">
         <v>898</v>
       </c>
       <c r="I115" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -6802,28 +6899,28 @@
         <v>123</v>
       </c>
       <c r="B116" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C116" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="D116" t="s">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="F116" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G116" t="s">
-        <v>855</v>
+        <v>876</v>
       </c>
       <c r="H116" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="I116" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -6831,28 +6928,28 @@
         <v>124</v>
       </c>
       <c r="B117" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C117" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="D117" t="s">
-        <v>625</v>
+        <v>634</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
       <c r="F117" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G117" t="s">
-        <v>857</v>
+        <v>870</v>
       </c>
       <c r="H117" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="I117" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -6860,28 +6957,28 @@
         <v>125</v>
       </c>
       <c r="B118" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C118" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="D118" t="s">
-        <v>626</v>
+        <v>635</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="F118" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G118" t="s">
-        <v>860</v>
+        <v>883</v>
       </c>
       <c r="H118" t="s">
-        <v>886</v>
+        <v>916</v>
       </c>
       <c r="I118" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -6889,28 +6986,28 @@
         <v>126</v>
       </c>
       <c r="B119" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C119" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="D119" t="s">
-        <v>627</v>
+        <v>636</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="F119" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G119" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="H119" t="s">
-        <v>899</v>
+        <v>911</v>
       </c>
       <c r="I119" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -6918,28 +7015,28 @@
         <v>127</v>
       </c>
       <c r="B120" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C120" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D120" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="F120" t="s">
-        <v>852</v>
+        <v>880</v>
       </c>
       <c r="G120" t="s">
-        <v>852</v>
+        <v>873</v>
       </c>
       <c r="H120" t="s">
-        <v>890</v>
+        <v>900</v>
       </c>
       <c r="I120" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -6947,28 +7044,28 @@
         <v>128</v>
       </c>
       <c r="B121" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C121" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="D121" t="s">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
       <c r="F121" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G121" t="s">
-        <v>849</v>
+        <v>876</v>
       </c>
       <c r="H121" t="s">
-        <v>887</v>
+        <v>897</v>
       </c>
       <c r="I121" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -6976,28 +7073,28 @@
         <v>129</v>
       </c>
       <c r="B122" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C122" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="D122" t="s">
-        <v>630</v>
+        <v>639</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="F122" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="G122" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="H122" t="s">
-        <v>897</v>
+        <v>910</v>
       </c>
       <c r="I122" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -7005,28 +7102,28 @@
         <v>130</v>
       </c>
       <c r="B123" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C123" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="D123" t="s">
-        <v>631</v>
+        <v>640</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="F123" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="G123" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="H123" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="I123" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -7034,28 +7131,28 @@
         <v>131</v>
       </c>
       <c r="B124" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C124" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="D124" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="F124" t="s">
-        <v>844</v>
+        <v>865</v>
       </c>
       <c r="G124" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="H124" t="s">
-        <v>886</v>
+        <v>904</v>
       </c>
       <c r="I124" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -7063,28 +7160,28 @@
         <v>132</v>
       </c>
       <c r="B125" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C125" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D125" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
       <c r="F125" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G125" t="s">
-        <v>849</v>
+        <v>886</v>
       </c>
       <c r="H125" t="s">
-        <v>891</v>
+        <v>911</v>
       </c>
       <c r="I125" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -7092,28 +7189,28 @@
         <v>133</v>
       </c>
       <c r="B126" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C126" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="D126" t="s">
-        <v>634</v>
+        <v>643</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="F126" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="G126" t="s">
-        <v>857</v>
+        <v>876</v>
       </c>
       <c r="H126" t="s">
-        <v>890</v>
+        <v>917</v>
       </c>
       <c r="I126" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -7121,28 +7218,28 @@
         <v>134</v>
       </c>
       <c r="B127" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C127" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="D127" t="s">
-        <v>635</v>
+        <v>644</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="F127" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="G127" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
       <c r="H127" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="I127" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -7150,28 +7247,28 @@
         <v>135</v>
       </c>
       <c r="B128" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C128" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D128" t="s">
-        <v>636</v>
+        <v>645</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="F128" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G128" t="s">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="H128" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="I128" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -7179,28 +7276,28 @@
         <v>136</v>
       </c>
       <c r="B129" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C129" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="D129" t="s">
-        <v>637</v>
+        <v>646</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
       <c r="F129" t="s">
-        <v>844</v>
+        <v>880</v>
       </c>
       <c r="G129" t="s">
-        <v>847</v>
+        <v>873</v>
       </c>
       <c r="H129" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="I129" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -7208,28 +7305,28 @@
         <v>137</v>
       </c>
       <c r="B130" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C130" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D130" t="s">
-        <v>638</v>
+        <v>647</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="F130" t="s">
-        <v>849</v>
+        <v>881</v>
       </c>
       <c r="G130" t="s">
-        <v>849</v>
+        <v>893</v>
       </c>
       <c r="H130" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
       <c r="I130" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -7237,28 +7334,28 @@
         <v>138</v>
       </c>
       <c r="B131" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C131" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="D131" t="s">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="F131" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G131" t="s">
-        <v>852</v>
+        <v>878</v>
       </c>
       <c r="H131" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="I131" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -7266,28 +7363,28 @@
         <v>139</v>
       </c>
       <c r="B132" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C132" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="D132" t="s">
-        <v>640</v>
+        <v>649</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="F132" t="s">
-        <v>846</v>
+        <v>859</v>
       </c>
       <c r="G132" t="s">
-        <v>846</v>
+        <v>863</v>
       </c>
       <c r="H132" t="s">
-        <v>882</v>
+        <v>897</v>
       </c>
       <c r="I132" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -7295,28 +7392,28 @@
         <v>140</v>
       </c>
       <c r="B133" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C133" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="D133" t="s">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
       <c r="F133" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="G133" t="s">
-        <v>846</v>
+        <v>865</v>
       </c>
       <c r="H133" t="s">
-        <v>884</v>
+        <v>897</v>
       </c>
       <c r="I133" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -7324,28 +7421,28 @@
         <v>141</v>
       </c>
       <c r="B134" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C134" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="D134" t="s">
-        <v>642</v>
+        <v>651</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="F134" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G134" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="H134" t="s">
-        <v>881</v>
+        <v>897</v>
       </c>
       <c r="I134" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -7353,28 +7450,28 @@
         <v>142</v>
       </c>
       <c r="B135" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C135" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D135" t="s">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="F135" t="s">
-        <v>848</v>
+        <v>862</v>
       </c>
       <c r="G135" t="s">
-        <v>848</v>
+        <v>862</v>
       </c>
       <c r="H135" t="s">
-        <v>885</v>
+        <v>900</v>
       </c>
       <c r="I135" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -7382,28 +7479,28 @@
         <v>143</v>
       </c>
       <c r="B136" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C136" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="D136" t="s">
-        <v>644</v>
+        <v>653</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="F136" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="G136" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="H136" t="s">
-        <v>881</v>
+        <v>902</v>
       </c>
       <c r="I136" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -7411,28 +7508,28 @@
         <v>144</v>
       </c>
       <c r="B137" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C137" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="D137" t="s">
-        <v>645</v>
+        <v>654</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
       <c r="F137" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G137" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="H137" t="s">
-        <v>886</v>
+        <v>898</v>
       </c>
       <c r="I137" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -7440,28 +7537,28 @@
         <v>145</v>
       </c>
       <c r="B138" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C138" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="D138" t="s">
-        <v>646</v>
+        <v>655</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="F138" t="s">
-        <v>855</v>
+        <v>864</v>
       </c>
       <c r="G138" t="s">
-        <v>853</v>
+        <v>864</v>
       </c>
       <c r="H138" t="s">
-        <v>879</v>
+        <v>903</v>
       </c>
       <c r="I138" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -7469,28 +7566,28 @@
         <v>146</v>
       </c>
       <c r="B139" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C139" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="D139" t="s">
-        <v>647</v>
+        <v>656</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="F139" t="s">
-        <v>849</v>
+        <v>863</v>
       </c>
       <c r="G139" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="H139" t="s">
-        <v>891</v>
+        <v>903</v>
       </c>
       <c r="I139" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -7498,28 +7595,28 @@
         <v>147</v>
       </c>
       <c r="B140" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C140" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D140" t="s">
-        <v>648</v>
+        <v>657</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="F140" t="s">
-        <v>849</v>
+        <v>868</v>
       </c>
       <c r="G140" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="H140" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="I140" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -7527,28 +7624,28 @@
         <v>148</v>
       </c>
       <c r="B141" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C141" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="D141" t="s">
-        <v>649</v>
+        <v>658</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
       <c r="F141" t="s">
-        <v>849</v>
+        <v>871</v>
       </c>
       <c r="G141" t="s">
-        <v>860</v>
+        <v>869</v>
       </c>
       <c r="H141" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="I141" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -7556,28 +7653,28 @@
         <v>149</v>
       </c>
       <c r="B142" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C142" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="D142" t="s">
-        <v>650</v>
+        <v>659</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="F142" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G142" t="s">
-        <v>875</v>
+        <v>884</v>
       </c>
       <c r="H142" t="s">
-        <v>891</v>
+        <v>907</v>
       </c>
       <c r="I142" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -7585,28 +7682,28 @@
         <v>150</v>
       </c>
       <c r="B143" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C143" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="D143" t="s">
-        <v>651</v>
+        <v>660</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="F143" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G143" t="s">
-        <v>860</v>
+        <v>891</v>
       </c>
       <c r="H143" t="s">
-        <v>891</v>
+        <v>907</v>
       </c>
       <c r="I143" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -7614,28 +7711,28 @@
         <v>151</v>
       </c>
       <c r="B144" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C144" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="D144" t="s">
-        <v>652</v>
+        <v>661</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="F144" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="G144" t="s">
-        <v>863</v>
+        <v>876</v>
       </c>
       <c r="H144" t="s">
-        <v>895</v>
+        <v>907</v>
       </c>
       <c r="I144" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -7643,28 +7740,28 @@
         <v>152</v>
       </c>
       <c r="B145" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C145" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D145" t="s">
-        <v>653</v>
+        <v>662</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
       <c r="F145" t="s">
-        <v>848</v>
+        <v>882</v>
       </c>
       <c r="G145" t="s">
-        <v>848</v>
+        <v>892</v>
       </c>
       <c r="H145" t="s">
-        <v>885</v>
+        <v>907</v>
       </c>
       <c r="I145" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -7672,28 +7769,28 @@
         <v>153</v>
       </c>
       <c r="B146" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C146" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="D146" t="s">
-        <v>654</v>
+        <v>663</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="F146" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G146" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="H146" t="s">
-        <v>886</v>
+        <v>907</v>
       </c>
       <c r="I146" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -7701,28 +7798,28 @@
         <v>154</v>
       </c>
       <c r="B147" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C147" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="D147" t="s">
-        <v>655</v>
+        <v>664</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="F147" t="s">
-        <v>849</v>
+        <v>879</v>
       </c>
       <c r="G147" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="H147" t="s">
-        <v>885</v>
+        <v>897</v>
       </c>
       <c r="I147" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -7730,28 +7827,28 @@
         <v>155</v>
       </c>
       <c r="B148" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C148" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="D148" t="s">
-        <v>656</v>
+        <v>665</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="F148" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="G148" t="s">
-        <v>848</v>
+        <v>864</v>
       </c>
       <c r="H148" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="I148" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -7759,28 +7856,28 @@
         <v>156</v>
       </c>
       <c r="B149" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C149" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="D149" t="s">
-        <v>657</v>
+        <v>666</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="F149" t="s">
-        <v>852</v>
+        <v>865</v>
       </c>
       <c r="G149" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
       <c r="H149" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="I149" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -7788,28 +7885,28 @@
         <v>157</v>
       </c>
       <c r="B150" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C150" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D150" t="s">
-        <v>658</v>
+        <v>667</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="F150" t="s">
-        <v>859</v>
+        <v>865</v>
       </c>
       <c r="G150" t="s">
-        <v>874</v>
+        <v>893</v>
       </c>
       <c r="H150" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
       <c r="I150" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -7817,28 +7914,28 @@
         <v>158</v>
       </c>
       <c r="B151" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C151" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="D151" t="s">
-        <v>659</v>
+        <v>668</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="F151" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="G151" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
       <c r="H151" t="s">
-        <v>890</v>
+        <v>910</v>
       </c>
       <c r="I151" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -7846,28 +7943,28 @@
         <v>159</v>
       </c>
       <c r="B152" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C152" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="D152" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="F152" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="G152" t="s">
-        <v>852</v>
+        <v>868</v>
       </c>
       <c r="H152" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I152" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -7875,28 +7972,28 @@
         <v>160</v>
       </c>
       <c r="B153" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C153" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="D153" t="s">
-        <v>661</v>
+        <v>670</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
       <c r="F153" t="s">
-        <v>849</v>
+        <v>875</v>
       </c>
       <c r="G153" t="s">
-        <v>868</v>
+        <v>891</v>
       </c>
       <c r="H153" t="s">
-        <v>891</v>
+        <v>897</v>
       </c>
       <c r="I153" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -7904,28 +8001,28 @@
         <v>161</v>
       </c>
       <c r="B154" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C154" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="D154" t="s">
-        <v>662</v>
+        <v>671</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="F154" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="G154" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="H154" t="s">
-        <v>881</v>
+        <v>906</v>
       </c>
       <c r="I154" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -7933,28 +8030,28 @@
         <v>162</v>
       </c>
       <c r="B155" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C155" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="D155" t="s">
-        <v>663</v>
+        <v>672</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="F155" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="G155" t="s">
-        <v>846</v>
+        <v>868</v>
       </c>
       <c r="H155" t="s">
-        <v>890</v>
+        <v>906</v>
       </c>
       <c r="I155" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -7962,28 +8059,28 @@
         <v>163</v>
       </c>
       <c r="B156" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C156" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="D156" t="s">
-        <v>664</v>
+        <v>673</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="F156" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G156" t="s">
-        <v>860</v>
+        <v>884</v>
       </c>
       <c r="H156" t="s">
-        <v>892</v>
+        <v>907</v>
       </c>
       <c r="I156" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -7991,28 +8088,28 @@
         <v>164</v>
       </c>
       <c r="B157" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C157" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="D157" t="s">
-        <v>665</v>
+        <v>674</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
       <c r="F157" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="G157" t="s">
-        <v>849</v>
+        <v>862</v>
       </c>
       <c r="H157" t="s">
-        <v>892</v>
+        <v>898</v>
       </c>
       <c r="I157" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -8020,28 +8117,28 @@
         <v>165</v>
       </c>
       <c r="B158" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C158" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="D158" t="s">
-        <v>666</v>
+        <v>675</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="F158" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="G158" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="H158" t="s">
-        <v>889</v>
+        <v>906</v>
       </c>
       <c r="I158" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -8049,28 +8146,28 @@
         <v>166</v>
       </c>
       <c r="B159" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C159" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="D159" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="F159" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G159" t="s">
-        <v>860</v>
+        <v>876</v>
       </c>
       <c r="H159" t="s">
-        <v>880</v>
+        <v>909</v>
       </c>
       <c r="I159" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -8078,28 +8175,28 @@
         <v>167</v>
       </c>
       <c r="B160" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C160" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D160" t="s">
-        <v>668</v>
+        <v>677</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="F160" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="G160" t="s">
-        <v>878</v>
+        <v>865</v>
       </c>
       <c r="H160" t="s">
-        <v>882</v>
+        <v>909</v>
       </c>
       <c r="I160" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -8107,28 +8204,28 @@
         <v>168</v>
       </c>
       <c r="B161" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C161" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="D161" t="s">
-        <v>669</v>
+        <v>678</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
       <c r="F161" t="s">
-        <v>864</v>
+        <v>873</v>
       </c>
       <c r="G161" t="s">
-        <v>857</v>
+        <v>882</v>
       </c>
       <c r="H161" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="I161" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -8136,28 +8233,28 @@
         <v>169</v>
       </c>
       <c r="B162" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C162" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="D162" t="s">
-        <v>670</v>
+        <v>679</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="F162" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G162" t="s">
-        <v>849</v>
+        <v>876</v>
       </c>
       <c r="H162" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="I162" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -8165,28 +8262,28 @@
         <v>170</v>
       </c>
       <c r="B163" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="C163" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="D163" t="s">
-        <v>671</v>
+        <v>680</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="F163" t="s">
-        <v>849</v>
+        <v>864</v>
       </c>
       <c r="G163" t="s">
-        <v>873</v>
+        <v>894</v>
       </c>
       <c r="H163" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="I163" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="164" spans="1:9">
@@ -8194,28 +8291,28 @@
         <v>171</v>
       </c>
       <c r="B164" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C164" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D164" t="s">
-        <v>672</v>
+        <v>681</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="F164" t="s">
-        <v>848</v>
+        <v>880</v>
       </c>
       <c r="G164" t="s">
-        <v>848</v>
+        <v>873</v>
       </c>
       <c r="H164" t="s">
-        <v>885</v>
+        <v>908</v>
       </c>
       <c r="I164" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="165" spans="1:9">
@@ -8223,28 +8320,28 @@
         <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C165" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="D165" t="s">
-        <v>673</v>
+        <v>682</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
       <c r="F165" t="s">
-        <v>856</v>
+        <v>865</v>
       </c>
       <c r="G165" t="s">
-        <v>850</v>
+        <v>865</v>
       </c>
       <c r="H165" t="s">
-        <v>903</v>
+        <v>909</v>
       </c>
       <c r="I165" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="166" spans="1:9">
@@ -8252,28 +8349,28 @@
         <v>173</v>
       </c>
       <c r="B166" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C166" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="D166" t="s">
-        <v>674</v>
+        <v>683</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="F166" t="s">
-        <v>849</v>
+        <v>865</v>
       </c>
       <c r="G166" t="s">
-        <v>849</v>
+        <v>890</v>
       </c>
       <c r="H166" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="I166" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="167" spans="1:9">
@@ -8281,28 +8378,28 @@
         <v>174</v>
       </c>
       <c r="B167" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C167" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="D167" t="s">
-        <v>675</v>
+        <v>684</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="F167" t="s">
-        <v>845</v>
+        <v>864</v>
       </c>
       <c r="G167" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="H167" t="s">
-        <v>889</v>
+        <v>903</v>
       </c>
       <c r="I167" t="s">
-        <v>904</v>
+        <v>920</v>
       </c>
     </row>
     <row r="168" spans="1:9">
@@ -8310,28 +8407,115 @@
         <v>175</v>
       </c>
       <c r="B168" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C168" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D168" t="s">
-        <v>676</v>
+        <v>685</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="F168" t="s">
-        <v>849</v>
+        <v>872</v>
       </c>
       <c r="G168" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="H168" t="s">
-        <v>892</v>
+        <v>919</v>
       </c>
       <c r="I168" t="s">
-        <v>904</v>
+        <v>920</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9">
+      <c r="A169" t="s">
+        <v>176</v>
+      </c>
+      <c r="B169" t="s">
+        <v>346</v>
+      </c>
+      <c r="C169" t="s">
+        <v>516</v>
+      </c>
+      <c r="D169" t="s">
+        <v>686</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="F169" t="s">
+        <v>865</v>
+      </c>
+      <c r="G169" t="s">
+        <v>865</v>
+      </c>
+      <c r="H169" t="s">
+        <v>909</v>
+      </c>
+      <c r="I169" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" t="s">
+        <v>177</v>
+      </c>
+      <c r="B170" t="s">
+        <v>347</v>
+      </c>
+      <c r="C170" t="s">
+        <v>517</v>
+      </c>
+      <c r="D170" t="s">
+        <v>687</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="F170" t="s">
+        <v>860</v>
+      </c>
+      <c r="G170" t="s">
+        <v>886</v>
+      </c>
+      <c r="H170" t="s">
+        <v>905</v>
+      </c>
+      <c r="I170" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" t="s">
+        <v>178</v>
+      </c>
+      <c r="B171" t="s">
+        <v>348</v>
+      </c>
+      <c r="C171" t="s">
+        <v>518</v>
+      </c>
+      <c r="D171" t="s">
+        <v>688</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="F171" t="s">
+        <v>865</v>
+      </c>
+      <c r="G171" t="s">
+        <v>887</v>
+      </c>
+      <c r="H171" t="s">
+        <v>909</v>
+      </c>
+      <c r="I171" t="s">
+        <v>920</v>
       </c>
     </row>
   </sheetData>
@@ -8503,6 +8687,9 @@
     <hyperlink ref="E166" r:id="rId165"/>
     <hyperlink ref="E167" r:id="rId166"/>
     <hyperlink ref="E168" r:id="rId167"/>
+    <hyperlink ref="E169" r:id="rId168"/>
+    <hyperlink ref="E170" r:id="rId169"/>
+    <hyperlink ref="E171" r:id="rId170"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
